--- a/gstdatabase/GSTR-3B-2020-2021.xlsx
+++ b/gstdatabase/GSTR-3B-2020-2021.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3ACC16-C7E4-41BF-A280-FAF2E1949BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BECF9AD-D711-4F8C-829B-95DC2B261897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,10 +188,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -487,8 +487,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -496,17 +496,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -807,13 +807,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
     </row>
     <row r="2" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -823,10 +823,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="49"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -853,14 +853,14 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
     </row>
     <row r="8" spans="1:64" s="42" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="48" t="s">
@@ -952,7 +952,7 @@
       <c r="BJ8" s="48"/>
     </row>
     <row r="9" spans="1:64" s="42" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="50"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="48"/>
       <c r="C9" s="41" t="s">
         <v>3</v>
@@ -1449,14 +1449,14 @@
       </c>
       <c r="AD11" s="17">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>19520</v>
+        <v>19521</v>
       </c>
       <c r="AE11" s="40">
-        <v>84509</v>
+        <v>84510</v>
       </c>
       <c r="AF11" s="18">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.94550234951890799</v>
+        <v>0.94551353770418434</v>
       </c>
       <c r="AG11" s="16">
         <v>90577</v>
@@ -1517,14 +1517,14 @@
       </c>
       <c r="AX11" s="17">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>12433</v>
+        <v>12434</v>
       </c>
       <c r="AY11" s="19">
-        <v>36534</v>
+        <v>36535</v>
       </c>
       <c r="AZ11" s="18">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.90824114356743324</v>
+        <v>0.90826600372902422</v>
       </c>
       <c r="BA11" s="36">
         <v>39963</v>
@@ -1534,14 +1534,14 @@
       </c>
       <c r="BC11" s="17">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>10600</v>
+        <v>10601</v>
       </c>
       <c r="BD11" s="38">
-        <v>37728</v>
+        <v>37729</v>
       </c>
       <c r="BE11" s="18">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>0.94407326777268974</v>
+        <v>0.94409829091910014</v>
       </c>
       <c r="BF11" s="9">
         <v>90790</v>
@@ -1551,14 +1551,14 @@
       </c>
       <c r="BH11" s="17">
         <f t="shared" ref="BH11:BH48" si="22">BI11-BG11</f>
-        <v>23155</v>
+        <v>23156</v>
       </c>
       <c r="BI11" s="19">
-        <v>89283</v>
+        <v>89284</v>
       </c>
       <c r="BJ11" s="18">
         <f t="shared" ref="BJ11:BJ48" si="23">BI11/BF11</f>
-        <v>0.98340125564489478</v>
+        <v>0.98341227007379672</v>
       </c>
       <c r="BK11" s="2"/>
       <c r="BL11" s="2"/>
@@ -1578,14 +1578,14 @@
       </c>
       <c r="E12" s="17">
         <f t="shared" si="0"/>
-        <v>270112</v>
+        <v>270113</v>
       </c>
       <c r="F12" s="16">
-        <v>291587</v>
+        <v>291588</v>
       </c>
       <c r="G12" s="18">
         <f t="shared" si="1"/>
-        <v>0.93443894310115527</v>
+        <v>0.93444214776714896</v>
       </c>
       <c r="H12" s="7">
         <v>311421</v>
@@ -1595,14 +1595,14 @@
       </c>
       <c r="J12" s="17">
         <f t="shared" si="2"/>
-        <v>211655</v>
+        <v>211656</v>
       </c>
       <c r="K12" s="16">
-        <v>291494</v>
+        <v>291495</v>
       </c>
       <c r="L12" s="18">
         <f t="shared" si="3"/>
-        <v>0.93601266452808252</v>
+        <v>0.93601587561532462</v>
       </c>
       <c r="M12" s="7">
         <v>312776</v>
@@ -1612,14 +1612,14 @@
       </c>
       <c r="O12" s="17">
         <f t="shared" si="4"/>
-        <v>165094</v>
+        <v>165095</v>
       </c>
       <c r="P12" s="16">
-        <v>292497</v>
+        <v>292498</v>
       </c>
       <c r="Q12" s="18">
         <f t="shared" si="5"/>
-        <v>0.93516446274650233</v>
+        <v>0.93516765992275619</v>
       </c>
       <c r="R12" s="7">
         <v>313307</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="T12" s="17">
         <f t="shared" si="6"/>
-        <v>160588</v>
+        <v>160589</v>
       </c>
       <c r="U12" s="16">
-        <v>295226</v>
+        <v>295227</v>
       </c>
       <c r="V12" s="18">
         <f t="shared" si="7"/>
-        <v>0.94228983074109418</v>
+        <v>0.9422930224986994</v>
       </c>
       <c r="W12" s="7">
         <v>316396</v>
@@ -1646,14 +1646,14 @@
       </c>
       <c r="Y12" s="17">
         <f t="shared" si="8"/>
-        <v>116005</v>
+        <v>116006</v>
       </c>
       <c r="Z12" s="16">
-        <v>297517</v>
+        <v>297518</v>
       </c>
       <c r="AA12" s="18">
         <f t="shared" si="9"/>
-        <v>0.94033110405946974</v>
+        <v>0.94033426465568459</v>
       </c>
       <c r="AB12" s="28">
         <v>318929</v>
@@ -1663,14 +1663,14 @@
       </c>
       <c r="AD12" s="17">
         <f t="shared" si="10"/>
-        <v>60000</v>
+        <v>60001</v>
       </c>
       <c r="AE12" s="40">
-        <v>299265</v>
+        <v>299266</v>
       </c>
       <c r="AF12" s="18">
         <f t="shared" si="11"/>
-        <v>0.9383436438831213</v>
+        <v>0.93834677937722821</v>
       </c>
       <c r="AG12" s="16">
         <v>321958</v>
@@ -1680,14 +1680,14 @@
       </c>
       <c r="AI12" s="17">
         <f t="shared" si="12"/>
-        <v>53870</v>
+        <v>53871</v>
       </c>
       <c r="AJ12" s="16">
-        <v>301288</v>
+        <v>301289</v>
       </c>
       <c r="AK12" s="18">
         <f t="shared" si="13"/>
-        <v>0.93579907938302509</v>
+        <v>0.93580218537821702</v>
       </c>
       <c r="AL12" s="30">
         <v>323060</v>
@@ -1697,14 +1697,14 @@
       </c>
       <c r="AN12" s="17">
         <f t="shared" si="14"/>
-        <v>48755</v>
+        <v>48756</v>
       </c>
       <c r="AO12" s="16">
-        <v>302905</v>
+        <v>302906</v>
       </c>
       <c r="AP12" s="18">
         <f t="shared" si="15"/>
-        <v>0.93761220825852787</v>
+        <v>0.93761530365876311</v>
       </c>
       <c r="AQ12" s="32">
         <v>323550</v>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="AS12" s="17">
         <f t="shared" si="16"/>
-        <v>41153</v>
+        <v>41154</v>
       </c>
       <c r="AT12" s="16">
-        <v>304433</v>
+        <v>304434</v>
       </c>
       <c r="AU12" s="18">
         <f t="shared" si="17"/>
-        <v>0.94091485087312621</v>
+        <v>0.94091794158553543</v>
       </c>
       <c r="AV12" s="34">
         <v>144815</v>
@@ -1731,14 +1731,14 @@
       </c>
       <c r="AX12" s="17">
         <f t="shared" si="18"/>
-        <v>34988</v>
+        <v>34989</v>
       </c>
       <c r="AY12" s="19">
-        <v>130385</v>
+        <v>130386</v>
       </c>
       <c r="AZ12" s="18">
         <f t="shared" si="19"/>
-        <v>0.90035562614370057</v>
+        <v>0.90036253150571421</v>
       </c>
       <c r="BA12" s="36">
         <v>144139</v>
@@ -1748,14 +1748,14 @@
       </c>
       <c r="BC12" s="17">
         <f t="shared" si="20"/>
-        <v>29049</v>
+        <v>29050</v>
       </c>
       <c r="BD12" s="38">
-        <v>133015</v>
+        <v>133016</v>
       </c>
       <c r="BE12" s="18">
         <f t="shared" si="21"/>
-        <v>0.92282449579919379</v>
+        <v>0.92283143354678465</v>
       </c>
       <c r="BF12" s="9">
         <v>318519</v>
@@ -1765,14 +1765,14 @@
       </c>
       <c r="BH12" s="17">
         <f t="shared" si="22"/>
-        <v>63435</v>
+        <v>63436</v>
       </c>
       <c r="BI12" s="19">
-        <v>308494</v>
+        <v>308495</v>
       </c>
       <c r="BJ12" s="18">
         <f t="shared" si="23"/>
-        <v>0.96852621036735642</v>
+        <v>0.9685293498974944</v>
       </c>
       <c r="BK12" s="2"/>
       <c r="BL12" s="2"/>
@@ -2023,14 +2023,14 @@
       </c>
       <c r="J14" s="17">
         <f t="shared" si="2"/>
-        <v>83243</v>
+        <v>83244</v>
       </c>
       <c r="K14" s="16">
-        <v>119959</v>
+        <v>119960</v>
       </c>
       <c r="L14" s="18">
         <f t="shared" si="3"/>
-        <v>0.91976875244397083</v>
+        <v>0.91977641980325553</v>
       </c>
       <c r="M14" s="7">
         <v>130093</v>
@@ -2040,14 +2040,14 @@
       </c>
       <c r="O14" s="17">
         <f t="shared" si="4"/>
-        <v>74184</v>
+        <v>74185</v>
       </c>
       <c r="P14" s="16">
-        <v>121108</v>
+        <v>121109</v>
       </c>
       <c r="Q14" s="18">
         <f t="shared" si="5"/>
-        <v>0.93093402412120563</v>
+        <v>0.93094171092987321</v>
       </c>
       <c r="R14" s="7">
         <v>132671</v>
@@ -2057,14 +2057,14 @@
       </c>
       <c r="T14" s="17">
         <f t="shared" si="6"/>
-        <v>72117</v>
+        <v>72118</v>
       </c>
       <c r="U14" s="16">
-        <v>123207</v>
+        <v>123208</v>
       </c>
       <c r="V14" s="18">
         <f t="shared" si="7"/>
-        <v>0.92866564659948292</v>
+        <v>0.92867318404172727</v>
       </c>
       <c r="W14" s="7">
         <v>135332</v>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="Y14" s="17">
         <f t="shared" si="8"/>
-        <v>51642</v>
+        <v>51643</v>
       </c>
       <c r="Z14" s="16">
-        <v>124871</v>
+        <v>124872</v>
       </c>
       <c r="AA14" s="18">
         <f t="shared" si="9"/>
-        <v>0.92270120887890517</v>
+        <v>0.92270859811426709</v>
       </c>
       <c r="AB14" s="28">
         <v>138271</v>
@@ -2091,14 +2091,14 @@
       </c>
       <c r="AD14" s="17">
         <f t="shared" si="10"/>
-        <v>33731</v>
+        <v>33732</v>
       </c>
       <c r="AE14" s="40">
-        <v>126352</v>
+        <v>126353</v>
       </c>
       <c r="AF14" s="18">
         <f t="shared" si="11"/>
-        <v>0.91379971215945499</v>
+        <v>0.91380694433395293</v>
       </c>
       <c r="AG14" s="16">
         <v>140605</v>
@@ -2434,14 +2434,14 @@
       </c>
       <c r="E16" s="17">
         <f t="shared" si="0"/>
-        <v>593038</v>
+        <v>593039</v>
       </c>
       <c r="F16" s="16">
-        <v>643910</v>
+        <v>643911</v>
       </c>
       <c r="G16" s="18">
         <f t="shared" si="1"/>
-        <v>0.85766270230815445</v>
+        <v>0.85766403426868043</v>
       </c>
       <c r="H16" s="7">
         <v>738386</v>
@@ -2451,14 +2451,14 @@
       </c>
       <c r="J16" s="17">
         <f t="shared" si="2"/>
-        <v>484664</v>
+        <v>484665</v>
       </c>
       <c r="K16" s="16">
-        <v>642208</v>
+        <v>642209</v>
       </c>
       <c r="L16" s="18">
         <f t="shared" si="3"/>
-        <v>0.86974563439718522</v>
+        <v>0.86974698870238598</v>
       </c>
       <c r="M16" s="7">
         <v>735720</v>
@@ -2468,14 +2468,14 @@
       </c>
       <c r="O16" s="17">
         <f t="shared" si="4"/>
-        <v>403668</v>
+        <v>403669</v>
       </c>
       <c r="P16" s="16">
-        <v>645349</v>
+        <v>645350</v>
       </c>
       <c r="Q16" s="18">
         <f t="shared" si="5"/>
-        <v>0.877166585113902</v>
+        <v>0.87716794432664602</v>
       </c>
       <c r="R16" s="7">
         <v>744442</v>
@@ -2485,14 +2485,14 @@
       </c>
       <c r="T16" s="17">
         <f t="shared" si="6"/>
-        <v>390134</v>
+        <v>390135</v>
       </c>
       <c r="U16" s="16">
-        <v>650376</v>
+        <v>650377</v>
       </c>
       <c r="V16" s="18">
         <f t="shared" si="7"/>
-        <v>0.87364227166119057</v>
+        <v>0.87364361494918341</v>
       </c>
       <c r="W16" s="7">
         <v>756644</v>
@@ -2502,14 +2502,14 @@
       </c>
       <c r="Y16" s="17">
         <f t="shared" si="8"/>
-        <v>276811</v>
+        <v>276812</v>
       </c>
       <c r="Z16" s="16">
-        <v>658858</v>
+        <v>658859</v>
       </c>
       <c r="AA16" s="18">
         <f t="shared" si="9"/>
-        <v>0.87076352948017821</v>
+        <v>0.87076485110567192</v>
       </c>
       <c r="AB16" s="28">
         <v>764172</v>
@@ -2519,14 +2519,14 @@
       </c>
       <c r="AD16" s="17">
         <f t="shared" si="10"/>
-        <v>186675</v>
+        <v>186676</v>
       </c>
       <c r="AE16" s="40">
-        <v>664107</v>
+        <v>664108</v>
       </c>
       <c r="AF16" s="18">
         <f t="shared" si="11"/>
-        <v>0.86905434902090106</v>
+        <v>0.86905565762681702</v>
       </c>
       <c r="AG16" s="16">
         <v>777864</v>
@@ -2536,14 +2536,14 @@
       </c>
       <c r="AI16" s="17">
         <f t="shared" si="12"/>
-        <v>177857</v>
+        <v>177859</v>
       </c>
       <c r="AJ16" s="16">
-        <v>672057</v>
+        <v>672059</v>
       </c>
       <c r="AK16" s="18">
         <f t="shared" si="13"/>
-        <v>0.86397750763629633</v>
+        <v>0.86398007877983807</v>
       </c>
       <c r="AL16" s="30">
         <v>781370</v>
@@ -2553,14 +2553,14 @@
       </c>
       <c r="AN16" s="17">
         <f t="shared" si="14"/>
-        <v>145968</v>
+        <v>145970</v>
       </c>
       <c r="AO16" s="16">
-        <v>677854</v>
+        <v>677856</v>
       </c>
       <c r="AP16" s="18">
         <f t="shared" si="15"/>
-        <v>0.8675198689481296</v>
+        <v>0.86752242855497397</v>
       </c>
       <c r="AQ16" s="32">
         <v>767321</v>
@@ -2570,14 +2570,14 @@
       </c>
       <c r="AS16" s="17">
         <f t="shared" si="16"/>
-        <v>117271</v>
+        <v>117273</v>
       </c>
       <c r="AT16" s="16">
-        <v>681915</v>
+        <v>681917</v>
       </c>
       <c r="AU16" s="18">
         <f t="shared" si="17"/>
-        <v>0.8886958652245931</v>
+        <v>0.88869847169567884</v>
       </c>
       <c r="AV16" s="34">
         <v>376545</v>
@@ -2587,14 +2587,14 @@
       </c>
       <c r="AX16" s="17">
         <f t="shared" si="18"/>
-        <v>113469</v>
+        <v>113471</v>
       </c>
       <c r="AY16" s="19">
-        <v>318806</v>
+        <v>318808</v>
       </c>
       <c r="AZ16" s="18">
         <f t="shared" si="19"/>
-        <v>0.846661089644</v>
+        <v>0.84666640109415869</v>
       </c>
       <c r="BA16" s="36">
         <v>362039</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="BC16" s="17">
         <f t="shared" si="20"/>
-        <v>92491</v>
+        <v>92494</v>
       </c>
       <c r="BD16" s="38">
-        <v>322103</v>
+        <v>322106</v>
       </c>
       <c r="BE16" s="18">
         <f t="shared" si="21"/>
-        <v>0.88969144208220663</v>
+        <v>0.88969972848229062</v>
       </c>
       <c r="BF16" s="9">
         <v>717401</v>
@@ -2621,14 +2621,14 @@
       </c>
       <c r="BH16" s="17">
         <f t="shared" si="22"/>
-        <v>217654</v>
+        <v>217658</v>
       </c>
       <c r="BI16" s="19">
-        <v>681950</v>
+        <v>681954</v>
       </c>
       <c r="BJ16" s="18">
         <f t="shared" si="23"/>
-        <v>0.95058412240852741</v>
+        <v>0.950589698090747</v>
       </c>
       <c r="BK16" s="2"/>
       <c r="BL16" s="2"/>
@@ -2648,14 +2648,14 @@
       </c>
       <c r="E17" s="17">
         <f t="shared" si="0"/>
-        <v>477728</v>
+        <v>477733</v>
       </c>
       <c r="F17" s="16">
-        <v>517785</v>
+        <v>517790</v>
       </c>
       <c r="G17" s="18">
         <f t="shared" si="1"/>
-        <v>0.93887353670742857</v>
+        <v>0.93888260295632242</v>
       </c>
       <c r="H17" s="7">
         <v>550123</v>
@@ -2665,14 +2665,14 @@
       </c>
       <c r="J17" s="17">
         <f t="shared" si="2"/>
-        <v>371930</v>
+        <v>371933</v>
       </c>
       <c r="K17" s="16">
-        <v>518972</v>
+        <v>518975</v>
       </c>
       <c r="L17" s="18">
         <f t="shared" si="3"/>
-        <v>0.94337448170681826</v>
+        <v>0.94337993503271089</v>
       </c>
       <c r="M17" s="7">
         <v>556868</v>
@@ -2682,14 +2682,14 @@
       </c>
       <c r="O17" s="17">
         <f t="shared" si="4"/>
-        <v>312461</v>
+        <v>312464</v>
       </c>
       <c r="P17" s="16">
-        <v>525543</v>
+        <v>525546</v>
       </c>
       <c r="Q17" s="18">
         <f t="shared" si="5"/>
-        <v>0.94374788998470016</v>
+        <v>0.94375327725780611</v>
       </c>
       <c r="R17" s="7">
         <v>565483</v>
@@ -2699,14 +2699,14 @@
       </c>
       <c r="T17" s="17">
         <f t="shared" si="6"/>
-        <v>303763</v>
+        <v>303765</v>
       </c>
       <c r="U17" s="16">
-        <v>534247</v>
+        <v>534249</v>
       </c>
       <c r="V17" s="18">
         <f t="shared" si="7"/>
-        <v>0.94476226517861717</v>
+        <v>0.94476580197813198</v>
       </c>
       <c r="W17" s="7">
         <v>572250</v>
@@ -2716,14 +2716,14 @@
       </c>
       <c r="Y17" s="17">
         <f t="shared" si="8"/>
-        <v>209894</v>
+        <v>209897</v>
       </c>
       <c r="Z17" s="16">
-        <v>540707</v>
+        <v>540710</v>
       </c>
       <c r="AA17" s="18">
         <f t="shared" si="9"/>
-        <v>0.94487898645696811</v>
+        <v>0.94488422892092616</v>
       </c>
       <c r="AB17" s="28">
         <v>582052</v>
@@ -2733,14 +2733,14 @@
       </c>
       <c r="AD17" s="17">
         <f t="shared" si="10"/>
-        <v>129249</v>
+        <v>129251</v>
       </c>
       <c r="AE17" s="40">
-        <v>547719</v>
+        <v>547721</v>
       </c>
       <c r="AF17" s="18">
         <f t="shared" si="11"/>
-        <v>0.94101386130448827</v>
+        <v>0.94101729742359785</v>
       </c>
       <c r="AG17" s="16">
         <v>590940</v>
@@ -2750,14 +2750,14 @@
       </c>
       <c r="AI17" s="17">
         <f t="shared" si="12"/>
-        <v>125627</v>
+        <v>125629</v>
       </c>
       <c r="AJ17" s="16">
-        <v>555068</v>
+        <v>555070</v>
       </c>
       <c r="AK17" s="18">
         <f t="shared" si="13"/>
-        <v>0.93929671371035972</v>
+        <v>0.93930009814871218</v>
       </c>
       <c r="AL17" s="30">
         <v>594928</v>
@@ -2767,14 +2767,14 @@
       </c>
       <c r="AN17" s="17">
         <f t="shared" si="14"/>
-        <v>105364</v>
+        <v>105365</v>
       </c>
       <c r="AO17" s="16">
-        <v>560903</v>
+        <v>560904</v>
       </c>
       <c r="AP17" s="18">
         <f t="shared" si="15"/>
-        <v>0.94280820536266574</v>
+        <v>0.94280988623833473</v>
       </c>
       <c r="AQ17" s="32">
         <v>594970</v>
@@ -2784,14 +2784,14 @@
       </c>
       <c r="AS17" s="17">
         <f t="shared" si="16"/>
-        <v>92383</v>
+        <v>92386</v>
       </c>
       <c r="AT17" s="16">
-        <v>566741</v>
+        <v>566744</v>
       </c>
       <c r="AU17" s="18">
         <f t="shared" si="17"/>
-        <v>0.95255391028119063</v>
+        <v>0.95255895255222955</v>
       </c>
       <c r="AV17" s="34">
         <v>254311</v>
@@ -2801,14 +2801,14 @@
       </c>
       <c r="AX17" s="17">
         <f t="shared" si="18"/>
-        <v>80417</v>
+        <v>80419</v>
       </c>
       <c r="AY17" s="19">
-        <v>233770</v>
+        <v>233772</v>
       </c>
       <c r="AZ17" s="18">
         <f t="shared" si="19"/>
-        <v>0.91922881825795977</v>
+        <v>0.91923668264447866</v>
       </c>
       <c r="BA17" s="36">
         <v>253807</v>
@@ -2818,14 +2818,14 @@
       </c>
       <c r="BC17" s="17">
         <f t="shared" si="20"/>
-        <v>66013</v>
+        <v>66016</v>
       </c>
       <c r="BD17" s="38">
-        <v>242526</v>
+        <v>242529</v>
       </c>
       <c r="BE17" s="18">
         <f t="shared" si="21"/>
-        <v>0.95555284133219331</v>
+        <v>0.95556466133715778</v>
       </c>
       <c r="BF17" s="9">
         <v>590776</v>
@@ -2835,14 +2835,14 @@
       </c>
       <c r="BH17" s="17">
         <f t="shared" si="22"/>
-        <v>190038</v>
+        <v>190042</v>
       </c>
       <c r="BI17" s="19">
-        <v>582496</v>
+        <v>582500</v>
       </c>
       <c r="BJ17" s="18">
         <f t="shared" si="23"/>
-        <v>0.98598453559386301</v>
+        <v>0.98599130634961474</v>
       </c>
       <c r="BK17" s="2"/>
       <c r="BL17" s="2"/>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="E18" s="17">
         <f t="shared" si="0"/>
-        <v>955294</v>
+        <v>955301</v>
       </c>
       <c r="F18" s="16">
-        <v>1051995</v>
+        <v>1052002</v>
       </c>
       <c r="G18" s="18">
         <f t="shared" si="1"/>
-        <v>0.9130244599721058</v>
+        <v>0.91303053525879418</v>
       </c>
       <c r="H18" s="7">
         <v>1134246</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="J18" s="17">
         <f t="shared" si="2"/>
-        <v>754297</v>
+        <v>754305</v>
       </c>
       <c r="K18" s="16">
-        <v>1050540</v>
+        <v>1050548</v>
       </c>
       <c r="L18" s="18">
         <f t="shared" si="3"/>
-        <v>0.92620119444988125</v>
+        <v>0.92620824759355558</v>
       </c>
       <c r="M18" s="7">
         <v>1134575</v>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="O18" s="17">
         <f t="shared" si="4"/>
-        <v>647205</v>
+        <v>647213</v>
       </c>
       <c r="P18" s="16">
-        <v>1055860</v>
+        <v>1055868</v>
       </c>
       <c r="Q18" s="18">
         <f t="shared" si="5"/>
-        <v>0.9306215983958751</v>
+        <v>0.93062864949430402</v>
       </c>
       <c r="R18" s="7">
         <v>1163634</v>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="T18" s="17">
         <f t="shared" si="6"/>
-        <v>637389</v>
+        <v>637396</v>
       </c>
       <c r="U18" s="16">
-        <v>1078350</v>
+        <v>1078357</v>
       </c>
       <c r="V18" s="18">
         <f t="shared" si="7"/>
-        <v>0.92670891362748076</v>
+        <v>0.92671492926470012</v>
       </c>
       <c r="W18" s="7">
         <v>1186115</v>
@@ -2930,14 +2930,14 @@
       </c>
       <c r="Y18" s="17">
         <f t="shared" si="8"/>
-        <v>412856</v>
+        <v>412863</v>
       </c>
       <c r="Z18" s="16">
-        <v>1094113</v>
+        <v>1094120</v>
       </c>
       <c r="AA18" s="18">
         <f t="shared" si="9"/>
-        <v>0.92243416532123779</v>
+        <v>0.92244006694123248</v>
       </c>
       <c r="AB18" s="28">
         <v>1210642</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="AD18" s="17">
         <f t="shared" si="10"/>
-        <v>256973</v>
+        <v>256981</v>
       </c>
       <c r="AE18" s="40">
-        <v>1109541</v>
+        <v>1109549</v>
       </c>
       <c r="AF18" s="18">
         <f t="shared" si="11"/>
-        <v>0.91648976328262199</v>
+        <v>0.91649637134677309</v>
       </c>
       <c r="AG18" s="16">
         <v>1230797</v>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="AI18" s="17">
         <f t="shared" si="12"/>
-        <v>255657</v>
+        <v>255666</v>
       </c>
       <c r="AJ18" s="16">
-        <v>1126510</v>
+        <v>1126519</v>
       </c>
       <c r="AK18" s="18">
         <f t="shared" si="13"/>
-        <v>0.91526872424940908</v>
+        <v>0.91527603658442458</v>
       </c>
       <c r="AL18" s="30">
         <v>1235793</v>
@@ -2981,14 +2981,14 @@
       </c>
       <c r="AN18" s="17">
         <f t="shared" si="14"/>
-        <v>215672</v>
+        <v>215681</v>
       </c>
       <c r="AO18" s="16">
-        <v>1138619</v>
+        <v>1138628</v>
       </c>
       <c r="AP18" s="18">
         <f t="shared" si="15"/>
-        <v>0.92136708979578297</v>
+        <v>0.92137437256886878</v>
       </c>
       <c r="AQ18" s="32">
         <v>1231355</v>
@@ -2998,14 +2998,14 @@
       </c>
       <c r="AS18" s="17">
         <f t="shared" si="16"/>
-        <v>183786</v>
+        <v>183795</v>
       </c>
       <c r="AT18" s="16">
-        <v>1149640</v>
+        <v>1149649</v>
       </c>
       <c r="AU18" s="18">
         <f t="shared" si="17"/>
-        <v>0.93363814659460509</v>
+        <v>0.93364545561596779</v>
       </c>
       <c r="AV18" s="34">
         <v>676084</v>
@@ -3015,14 +3015,14 @@
       </c>
       <c r="AX18" s="17">
         <f t="shared" si="18"/>
-        <v>184436</v>
+        <v>184443</v>
       </c>
       <c r="AY18" s="19">
-        <v>606968</v>
+        <v>606975</v>
       </c>
       <c r="AZ18" s="18">
         <f t="shared" si="19"/>
-        <v>0.89777009957342579</v>
+        <v>0.89778045331645184</v>
       </c>
       <c r="BA18" s="36">
         <v>651597</v>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="BC18" s="17">
         <f t="shared" si="20"/>
-        <v>154163</v>
+        <v>154171</v>
       </c>
       <c r="BD18" s="38">
-        <v>620504</v>
+        <v>620512</v>
       </c>
       <c r="BE18" s="18">
         <f t="shared" si="21"/>
-        <v>0.9522818551957728</v>
+        <v>0.95229413272314023</v>
       </c>
       <c r="BF18" s="9">
         <v>1203078</v>
@@ -3049,14 +3049,14 @@
       </c>
       <c r="BH18" s="17">
         <f t="shared" si="22"/>
-        <v>356587</v>
+        <v>356595</v>
       </c>
       <c r="BI18" s="19">
-        <v>1175735</v>
+        <v>1175743</v>
       </c>
       <c r="BJ18" s="18">
         <f t="shared" si="23"/>
-        <v>0.97727246279958568</v>
+        <v>0.97727911241000165</v>
       </c>
       <c r="BK18" s="2"/>
       <c r="BL18" s="2"/>
@@ -3076,14 +3076,14 @@
       </c>
       <c r="E19" s="17">
         <f t="shared" si="0"/>
-        <v>264719</v>
+        <v>264721</v>
       </c>
       <c r="F19" s="16">
-        <v>291696</v>
+        <v>291698</v>
       </c>
       <c r="G19" s="18">
         <f t="shared" si="1"/>
-        <v>0.9134968902473396</v>
+        <v>0.91350315359610168</v>
       </c>
       <c r="H19" s="7">
         <v>318723</v>
@@ -3093,14 +3093,14 @@
       </c>
       <c r="J19" s="17">
         <f t="shared" si="2"/>
-        <v>219282</v>
+        <v>219284</v>
       </c>
       <c r="K19" s="16">
-        <v>293361</v>
+        <v>293363</v>
       </c>
       <c r="L19" s="18">
         <f t="shared" si="3"/>
-        <v>0.92042620080759785</v>
+        <v>0.92043247584893462</v>
       </c>
       <c r="M19" s="7">
         <v>326795</v>
@@ -3110,14 +3110,14 @@
       </c>
       <c r="O19" s="17">
         <f t="shared" si="4"/>
-        <v>226817</v>
+        <v>226819</v>
       </c>
       <c r="P19" s="16">
-        <v>299513</v>
+        <v>299515</v>
       </c>
       <c r="Q19" s="18">
         <f t="shared" si="5"/>
-        <v>0.91651647057023511</v>
+        <v>0.91652259061491148</v>
       </c>
       <c r="R19" s="7">
         <v>336400</v>
@@ -3127,14 +3127,14 @@
       </c>
       <c r="T19" s="17">
         <f t="shared" si="6"/>
-        <v>220412</v>
+        <v>220415</v>
       </c>
       <c r="U19" s="16">
-        <v>305004</v>
+        <v>305007</v>
       </c>
       <c r="V19" s="18">
         <f t="shared" si="7"/>
-        <v>0.90667063020214034</v>
+        <v>0.90667954815695595</v>
       </c>
       <c r="W19" s="7">
         <v>343478</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="Y19" s="17">
         <f t="shared" si="8"/>
-        <v>151048</v>
+        <v>151051</v>
       </c>
       <c r="Z19" s="16">
-        <v>309566</v>
+        <v>309569</v>
       </c>
       <c r="AA19" s="18">
         <f t="shared" si="9"/>
-        <v>0.90126878577376135</v>
+        <v>0.90127751995761007</v>
       </c>
       <c r="AB19" s="28">
         <v>355383</v>
@@ -3161,14 +3161,14 @@
       </c>
       <c r="AD19" s="17">
         <f t="shared" si="10"/>
-        <v>93724</v>
+        <v>93727</v>
       </c>
       <c r="AE19" s="40">
-        <v>315645</v>
+        <v>315648</v>
       </c>
       <c r="AF19" s="18">
         <f t="shared" si="11"/>
-        <v>0.88818260862224696</v>
+        <v>0.88819105021905942</v>
       </c>
       <c r="AG19" s="16">
         <v>365633</v>
@@ -3178,14 +3178,14 @@
       </c>
       <c r="AI19" s="17">
         <f t="shared" si="12"/>
-        <v>109284</v>
+        <v>109287</v>
       </c>
       <c r="AJ19" s="16">
-        <v>321341</v>
+        <v>321344</v>
       </c>
       <c r="AK19" s="18">
         <f t="shared" si="13"/>
-        <v>0.87886213771732857</v>
+        <v>0.87887034266600661</v>
       </c>
       <c r="AL19" s="30">
         <v>370137</v>
@@ -3195,14 +3195,14 @@
       </c>
       <c r="AN19" s="17">
         <f t="shared" si="14"/>
-        <v>84848</v>
+        <v>84851</v>
       </c>
       <c r="AO19" s="16">
-        <v>324809</v>
+        <v>324812</v>
       </c>
       <c r="AP19" s="18">
         <f t="shared" si="15"/>
-        <v>0.87753723621253754</v>
+        <v>0.87754534131956541</v>
       </c>
       <c r="AQ19" s="32">
         <v>372999</v>
@@ -3212,14 +3212,14 @@
       </c>
       <c r="AS19" s="17">
         <f t="shared" si="16"/>
-        <v>67753</v>
+        <v>67757</v>
       </c>
       <c r="AT19" s="16">
-        <v>329620</v>
+        <v>329624</v>
       </c>
       <c r="AU19" s="18">
         <f t="shared" si="17"/>
-        <v>0.88370210107801894</v>
+        <v>0.88371282496735915</v>
       </c>
       <c r="AV19" s="34">
         <v>223052</v>
@@ -3229,14 +3229,14 @@
       </c>
       <c r="AX19" s="17">
         <f t="shared" si="18"/>
-        <v>71732</v>
+        <v>71735</v>
       </c>
       <c r="AY19" s="19">
-        <v>180724</v>
+        <v>180727</v>
       </c>
       <c r="AZ19" s="18">
         <f t="shared" si="19"/>
-        <v>0.8102325915033266</v>
+        <v>0.81024604128185351</v>
       </c>
       <c r="BA19" s="36">
         <v>218640</v>
@@ -3246,14 +3246,14 @@
       </c>
       <c r="BC19" s="17">
         <f t="shared" si="20"/>
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="BD19" s="38">
-        <v>187538</v>
+        <v>187541</v>
       </c>
       <c r="BE19" s="18">
         <f t="shared" si="21"/>
-        <v>0.85774789608488844</v>
+        <v>0.85776161727039879</v>
       </c>
       <c r="BF19" s="9">
         <v>376756</v>
@@ -3263,14 +3263,14 @@
       </c>
       <c r="BH19" s="17">
         <f t="shared" si="22"/>
-        <v>121131</v>
+        <v>121134</v>
       </c>
       <c r="BI19" s="19">
-        <v>346114</v>
+        <v>346117</v>
       </c>
       <c r="BJ19" s="18">
         <f t="shared" si="23"/>
-        <v>0.91866884668061022</v>
+        <v>0.9186768093938783</v>
       </c>
       <c r="BK19" s="2"/>
       <c r="BL19" s="2"/>
@@ -3477,14 +3477,14 @@
       </c>
       <c r="BH20" s="17">
         <f t="shared" si="22"/>
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="BI20" s="19">
-        <v>7260</v>
+        <v>7261</v>
       </c>
       <c r="BJ20" s="18">
         <f t="shared" si="23"/>
-        <v>0.92073557387444516</v>
+        <v>0.92086239695624605</v>
       </c>
       <c r="BK20" s="2"/>
       <c r="BL20" s="2"/>
@@ -3504,14 +3504,14 @@
       </c>
       <c r="E21" s="17">
         <f t="shared" si="0"/>
-        <v>8229</v>
+        <v>8230</v>
       </c>
       <c r="F21" s="16">
-        <v>9547</v>
+        <v>9548</v>
       </c>
       <c r="G21" s="18">
         <f t="shared" si="1"/>
-        <v>0.76750542648122844</v>
+        <v>0.76758581879572307</v>
       </c>
       <c r="H21" s="7">
         <v>11980</v>
@@ -3691,14 +3691,14 @@
       </c>
       <c r="BH21" s="17">
         <f t="shared" si="22"/>
-        <v>5105</v>
+        <v>5106</v>
       </c>
       <c r="BI21" s="19">
-        <v>10388</v>
+        <v>10389</v>
       </c>
       <c r="BJ21" s="18">
         <f t="shared" si="23"/>
-        <v>0.81763085399449031</v>
+        <v>0.81770956316410859</v>
       </c>
       <c r="BK21" s="2"/>
       <c r="BL21" s="2"/>
@@ -3718,14 +3718,14 @@
       </c>
       <c r="E22" s="17">
         <f t="shared" si="0"/>
-        <v>4686</v>
+        <v>4687</v>
       </c>
       <c r="F22" s="16">
-        <v>5610</v>
+        <v>5611</v>
       </c>
       <c r="G22" s="18">
         <f t="shared" si="1"/>
-        <v>0.83793876026885739</v>
+        <v>0.83808812546676625</v>
       </c>
       <c r="H22" s="7">
         <v>6654</v>
@@ -3735,14 +3735,14 @@
       </c>
       <c r="J22" s="17">
         <f t="shared" si="2"/>
-        <v>4203</v>
+        <v>4204</v>
       </c>
       <c r="K22" s="16">
-        <v>5609</v>
+        <v>5610</v>
       </c>
       <c r="L22" s="18">
         <f t="shared" si="3"/>
-        <v>0.84295160805530511</v>
+        <v>0.84310189359783594</v>
       </c>
       <c r="M22" s="7">
         <v>6636</v>
@@ -3752,14 +3752,14 @@
       </c>
       <c r="O22" s="17">
         <f t="shared" si="4"/>
-        <v>3735</v>
+        <v>3736</v>
       </c>
       <c r="P22" s="16">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="Q22" s="18">
         <f t="shared" si="5"/>
-        <v>0.84825195901145267</v>
+        <v>0.84840265220012057</v>
       </c>
       <c r="R22" s="7">
         <v>6730</v>
@@ -3769,14 +3769,14 @@
       </c>
       <c r="T22" s="17">
         <f t="shared" si="6"/>
-        <v>3929</v>
+        <v>3930</v>
       </c>
       <c r="U22" s="16">
-        <v>5688</v>
+        <v>5689</v>
       </c>
       <c r="V22" s="18">
         <f t="shared" si="7"/>
-        <v>0.84517087667161961</v>
+        <v>0.84531946508172362</v>
       </c>
       <c r="W22" s="7">
         <v>6785</v>
@@ -3786,14 +3786,14 @@
       </c>
       <c r="Y22" s="17">
         <f t="shared" si="8"/>
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="Z22" s="16">
-        <v>5745</v>
+        <v>5746</v>
       </c>
       <c r="AA22" s="18">
         <f t="shared" si="9"/>
-        <v>0.84672070744288874</v>
+        <v>0.84686809137803976</v>
       </c>
       <c r="AB22" s="28">
         <v>6814</v>
@@ -3803,14 +3803,14 @@
       </c>
       <c r="AD22" s="17">
         <f t="shared" si="10"/>
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="AE22" s="40">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="AF22" s="18">
         <f t="shared" si="11"/>
-        <v>0.84928089228059878</v>
+        <v>0.84942764895802758</v>
       </c>
       <c r="AG22" s="16">
         <v>6964</v>
@@ -3820,14 +3820,14 @@
       </c>
       <c r="AI22" s="17">
         <f t="shared" si="12"/>
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="AJ22" s="16">
-        <v>5860</v>
+        <v>5862</v>
       </c>
       <c r="AK22" s="18">
         <f t="shared" si="13"/>
-        <v>0.84147041929925326</v>
+        <v>0.84175761056863874</v>
       </c>
       <c r="AL22" s="30">
         <v>7048</v>
@@ -3837,14 +3837,14 @@
       </c>
       <c r="AN22" s="17">
         <f t="shared" si="14"/>
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="AO22" s="16">
-        <v>5950</v>
+        <v>5951</v>
       </c>
       <c r="AP22" s="18">
         <f t="shared" si="15"/>
-        <v>0.84421112372304197</v>
+        <v>0.84435300794551649</v>
       </c>
       <c r="AQ22" s="32">
         <v>7088</v>
@@ -3854,14 +3854,14 @@
       </c>
       <c r="AS22" s="17">
         <f t="shared" si="16"/>
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AT22" s="16">
-        <v>6008</v>
+        <v>6009</v>
       </c>
       <c r="AU22" s="18">
         <f t="shared" si="17"/>
-        <v>0.84762979683972917</v>
+        <v>0.84777088036117376</v>
       </c>
       <c r="AV22" s="34">
         <v>5686</v>
@@ -3871,14 +3871,14 @@
       </c>
       <c r="AX22" s="17">
         <f t="shared" si="18"/>
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="AY22" s="19">
-        <v>4655</v>
+        <v>4656</v>
       </c>
       <c r="AZ22" s="18">
         <f t="shared" si="19"/>
-        <v>0.81867745339430176</v>
+        <v>0.81885332395357013</v>
       </c>
       <c r="BA22" s="36">
         <v>5621</v>
@@ -3888,14 +3888,14 @@
       </c>
       <c r="BC22" s="17">
         <f t="shared" si="20"/>
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="BD22" s="38">
-        <v>4738</v>
+        <v>4739</v>
       </c>
       <c r="BE22" s="18">
         <f t="shared" si="21"/>
-        <v>0.84291051414339091</v>
+        <v>0.84308841843088422</v>
       </c>
       <c r="BF22" s="9">
         <v>6948</v>
@@ -3905,14 +3905,14 @@
       </c>
       <c r="BH22" s="17">
         <f t="shared" si="22"/>
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="BI22" s="19">
-        <v>6132</v>
+        <v>6133</v>
       </c>
       <c r="BJ22" s="18">
         <f t="shared" si="23"/>
-        <v>0.88255613126079446</v>
+        <v>0.88270005757052394</v>
       </c>
       <c r="BK22" s="2"/>
       <c r="BL22" s="2"/>
@@ -4445,14 +4445,14 @@
       </c>
       <c r="AD25" s="17">
         <f t="shared" si="10"/>
-        <v>5645</v>
+        <v>5646</v>
       </c>
       <c r="AE25" s="40">
-        <v>22061</v>
+        <v>22062</v>
       </c>
       <c r="AF25" s="18">
         <f t="shared" si="11"/>
-        <v>0.87018775639002843</v>
+        <v>0.87022720100978224</v>
       </c>
       <c r="AG25" s="16">
         <v>25657</v>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="E27" s="17">
         <f t="shared" si="0"/>
-        <v>115188</v>
+        <v>115192</v>
       </c>
       <c r="F27" s="16">
-        <v>129446</v>
+        <v>129450</v>
       </c>
       <c r="G27" s="18">
         <f t="shared" si="1"/>
-        <v>0.88855787645609241</v>
+        <v>0.8885853337085825</v>
       </c>
       <c r="H27" s="7">
         <v>145010</v>
@@ -4805,14 +4805,14 @@
       </c>
       <c r="J27" s="17">
         <f t="shared" si="2"/>
-        <v>98109</v>
+        <v>98112</v>
       </c>
       <c r="K27" s="16">
-        <v>129421</v>
+        <v>129424</v>
       </c>
       <c r="L27" s="18">
         <f t="shared" si="3"/>
-        <v>0.8924970691676436</v>
+        <v>0.89251775739604167</v>
       </c>
       <c r="M27" s="7">
         <v>146684</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="O27" s="17">
         <f t="shared" si="4"/>
-        <v>98013</v>
+        <v>98017</v>
       </c>
       <c r="P27" s="16">
-        <v>130609</v>
+        <v>130613</v>
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="5"/>
-        <v>0.89041067873796731</v>
+        <v>0.89043794824248046</v>
       </c>
       <c r="R27" s="7">
         <v>151002</v>
@@ -4839,14 +4839,14 @@
       </c>
       <c r="T27" s="17">
         <f t="shared" si="6"/>
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="U27" s="16">
-        <v>133156</v>
+        <v>133161</v>
       </c>
       <c r="V27" s="18">
         <f t="shared" si="7"/>
-        <v>0.88181613488563071</v>
+        <v>0.88184924702984069</v>
       </c>
       <c r="W27" s="7">
         <v>153079</v>
@@ -4856,14 +4856,14 @@
       </c>
       <c r="Y27" s="17">
         <f t="shared" si="8"/>
-        <v>73988</v>
+        <v>73993</v>
       </c>
       <c r="Z27" s="16">
-        <v>135041</v>
+        <v>135046</v>
       </c>
       <c r="AA27" s="18">
         <f t="shared" si="9"/>
-        <v>0.88216541785613967</v>
+        <v>0.88219808072955797</v>
       </c>
       <c r="AB27" s="28">
         <v>156081</v>
@@ -4873,14 +4873,14 @@
       </c>
       <c r="AD27" s="17">
         <f t="shared" si="10"/>
-        <v>52673</v>
+        <v>52681</v>
       </c>
       <c r="AE27" s="40">
-        <v>135648</v>
+        <v>135656</v>
       </c>
       <c r="AF27" s="18">
         <f t="shared" si="11"/>
-        <v>0.86908720472062584</v>
+        <v>0.86913846015850749</v>
       </c>
       <c r="AG27" s="16">
         <v>159400</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="AI27" s="17">
         <f t="shared" si="12"/>
-        <v>49908</v>
+        <v>49916</v>
       </c>
       <c r="AJ27" s="16">
-        <v>137419</v>
+        <v>137427</v>
       </c>
       <c r="AK27" s="18">
         <f t="shared" si="13"/>
-        <v>0.86210163111668758</v>
+        <v>0.86215181932245921</v>
       </c>
       <c r="AL27" s="30">
         <v>161009</v>
@@ -4907,14 +4907,14 @@
       </c>
       <c r="AN27" s="17">
         <f t="shared" si="14"/>
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="AO27" s="16">
-        <v>138956</v>
+        <v>138964</v>
       </c>
       <c r="AP27" s="18">
         <f t="shared" si="15"/>
-        <v>0.86303250128874787</v>
+        <v>0.86308218795222624</v>
       </c>
       <c r="AQ27" s="32">
         <v>161396</v>
@@ -4924,14 +4924,14 @@
       </c>
       <c r="AS27" s="17">
         <f t="shared" si="16"/>
-        <v>42491</v>
+        <v>42499</v>
       </c>
       <c r="AT27" s="16">
-        <v>140865</v>
+        <v>140873</v>
       </c>
       <c r="AU27" s="18">
         <f t="shared" si="17"/>
-        <v>0.87279114724032814</v>
+        <v>0.87284071476368685</v>
       </c>
       <c r="AV27" s="34">
         <v>108346</v>
@@ -4941,14 +4941,14 @@
       </c>
       <c r="AX27" s="17">
         <f t="shared" si="18"/>
-        <v>41816</v>
+        <v>41825</v>
       </c>
       <c r="AY27" s="19">
-        <v>89117</v>
+        <v>89126</v>
       </c>
       <c r="AZ27" s="18">
         <f t="shared" si="19"/>
-        <v>0.82252228970151187</v>
+        <v>0.82260535691211489</v>
       </c>
       <c r="BA27" s="36">
         <v>101792</v>
@@ -4958,14 +4958,14 @@
       </c>
       <c r="BC27" s="17">
         <f t="shared" si="20"/>
-        <v>36638</v>
+        <v>36646</v>
       </c>
       <c r="BD27" s="38">
-        <v>91012</v>
+        <v>91020</v>
       </c>
       <c r="BE27" s="18">
         <f t="shared" si="21"/>
-        <v>0.89409776799748508</v>
+        <v>0.89417635963533482</v>
       </c>
       <c r="BF27" s="9">
         <v>155251</v>
@@ -4975,14 +4975,14 @@
       </c>
       <c r="BH27" s="17">
         <f t="shared" si="22"/>
-        <v>64479</v>
+        <v>64489</v>
       </c>
       <c r="BI27" s="19">
-        <v>145204</v>
+        <v>145214</v>
       </c>
       <c r="BJ27" s="18">
         <f t="shared" si="23"/>
-        <v>0.93528544099554911</v>
+        <v>0.93534985281898342</v>
       </c>
       <c r="BK27" s="2"/>
       <c r="BL27" s="2"/>
@@ -5002,14 +5002,14 @@
       </c>
       <c r="E28" s="17">
         <f t="shared" si="0"/>
-        <v>501097</v>
+        <v>501101</v>
       </c>
       <c r="F28" s="16">
-        <v>545521</v>
+        <v>545525</v>
       </c>
       <c r="G28" s="18">
         <f t="shared" si="1"/>
-        <v>0.89257157068551107</v>
+        <v>0.89257811541299681</v>
       </c>
       <c r="H28" s="7">
         <v>606429</v>
@@ -5019,14 +5019,14 @@
       </c>
       <c r="J28" s="17">
         <f t="shared" si="2"/>
-        <v>399816</v>
+        <v>399819</v>
       </c>
       <c r="K28" s="16">
-        <v>544358</v>
+        <v>544361</v>
       </c>
       <c r="L28" s="18">
         <f t="shared" si="3"/>
-        <v>0.89764506644636055</v>
+        <v>0.89765001343933093</v>
       </c>
       <c r="M28" s="7">
         <v>606073</v>
@@ -5036,14 +5036,14 @@
       </c>
       <c r="O28" s="17">
         <f t="shared" si="4"/>
-        <v>359407</v>
+        <v>359409</v>
       </c>
       <c r="P28" s="16">
-        <v>545057</v>
+        <v>545059</v>
       </c>
       <c r="Q28" s="18">
         <f t="shared" si="5"/>
-        <v>0.8993256587902777</v>
+        <v>0.89932895872279417</v>
       </c>
       <c r="R28" s="7">
         <v>610188</v>
@@ -5053,14 +5053,14 @@
       </c>
       <c r="T28" s="17">
         <f t="shared" si="6"/>
-        <v>358941</v>
+        <v>358943</v>
       </c>
       <c r="U28" s="16">
-        <v>548640</v>
+        <v>548642</v>
       </c>
       <c r="V28" s="18">
         <f t="shared" si="7"/>
-        <v>0.89913272630730201</v>
+        <v>0.89913600398565685</v>
       </c>
       <c r="W28" s="7">
         <v>613926</v>
@@ -5070,14 +5070,14 @@
       </c>
       <c r="Y28" s="17">
         <f t="shared" si="8"/>
-        <v>240223</v>
+        <v>240225</v>
       </c>
       <c r="Z28" s="16">
-        <v>551011</v>
+        <v>551013</v>
       </c>
       <c r="AA28" s="18">
         <f t="shared" si="9"/>
-        <v>0.89752022230692297</v>
+        <v>0.89752348002853766</v>
       </c>
       <c r="AB28" s="28">
         <v>616763</v>
@@ -5087,14 +5087,14 @@
       </c>
       <c r="AD28" s="17">
         <f t="shared" si="10"/>
-        <v>147646</v>
+        <v>147648</v>
       </c>
       <c r="AE28" s="40">
-        <v>552214</v>
+        <v>552216</v>
       </c>
       <c r="AF28" s="18">
         <f t="shared" si="11"/>
-        <v>0.89534229517659136</v>
+        <v>0.89534553791326654</v>
       </c>
       <c r="AG28" s="16">
         <v>621241</v>
@@ -5104,14 +5104,14 @@
       </c>
       <c r="AI28" s="17">
         <f t="shared" si="12"/>
-        <v>134841</v>
+        <v>134843</v>
       </c>
       <c r="AJ28" s="16">
-        <v>554813</v>
+        <v>554815</v>
       </c>
       <c r="AK28" s="18">
         <f t="shared" si="13"/>
-        <v>0.89307209279490563</v>
+        <v>0.89307531215743974</v>
       </c>
       <c r="AL28" s="30">
         <v>624748</v>
@@ -5121,14 +5121,14 @@
       </c>
       <c r="AN28" s="17">
         <f t="shared" si="14"/>
-        <v>120278</v>
+        <v>120280</v>
       </c>
       <c r="AO28" s="16">
-        <v>558522</v>
+        <v>558524</v>
       </c>
       <c r="AP28" s="18">
         <f t="shared" si="15"/>
-        <v>0.89399565904972889</v>
+        <v>0.89399886034048925</v>
       </c>
       <c r="AQ28" s="32">
         <v>625592</v>
@@ -5138,14 +5138,14 @@
       </c>
       <c r="AS28" s="17">
         <f t="shared" si="16"/>
-        <v>106900</v>
+        <v>106902</v>
       </c>
       <c r="AT28" s="16">
-        <v>561981</v>
+        <v>561983</v>
       </c>
       <c r="AU28" s="18">
         <f t="shared" si="17"/>
-        <v>0.89831871251550532</v>
+        <v>0.89832190948733359</v>
       </c>
       <c r="AV28" s="34">
         <v>329721</v>
@@ -5155,14 +5155,14 @@
       </c>
       <c r="AX28" s="17">
         <f t="shared" si="18"/>
-        <v>102393</v>
+        <v>102396</v>
       </c>
       <c r="AY28" s="19">
-        <v>269581</v>
+        <v>269584</v>
       </c>
       <c r="AZ28" s="18">
         <f t="shared" si="19"/>
-        <v>0.81760336769571851</v>
+        <v>0.81761246629726347</v>
       </c>
       <c r="BA28" s="36">
         <v>323065</v>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="BC28" s="17">
         <f t="shared" si="20"/>
-        <v>82760</v>
+        <v>82763</v>
       </c>
       <c r="BD28" s="38">
-        <v>273170</v>
+        <v>273173</v>
       </c>
       <c r="BE28" s="18">
         <f t="shared" si="21"/>
-        <v>0.84555739557055076</v>
+        <v>0.84556668162753623</v>
       </c>
       <c r="BF28" s="9">
         <v>619161</v>
@@ -5189,14 +5189,14 @@
       </c>
       <c r="BH28" s="17">
         <f t="shared" si="22"/>
-        <v>148330</v>
+        <v>148333</v>
       </c>
       <c r="BI28" s="19">
-        <v>569185</v>
+        <v>569188</v>
       </c>
       <c r="BJ28" s="18">
         <f t="shared" si="23"/>
-        <v>0.91928432184843689</v>
+        <v>0.91928916711485376</v>
       </c>
       <c r="BK28" s="2"/>
       <c r="BL28" s="2"/>
@@ -5369,14 +5369,14 @@
       </c>
       <c r="AX29" s="17">
         <f t="shared" si="18"/>
-        <v>30575</v>
+        <v>30576</v>
       </c>
       <c r="AY29" s="19">
-        <v>88072</v>
+        <v>88073</v>
       </c>
       <c r="AZ29" s="18">
         <f t="shared" si="19"/>
-        <v>0.91731155805064002</v>
+        <v>0.91732197352386702</v>
       </c>
       <c r="BA29" s="36">
         <v>92769</v>
@@ -5430,14 +5430,14 @@
       </c>
       <c r="E30" s="17">
         <f t="shared" si="0"/>
-        <v>183088</v>
+        <v>183091</v>
       </c>
       <c r="F30" s="16">
-        <v>212363</v>
+        <v>212366</v>
       </c>
       <c r="G30" s="18">
         <f t="shared" si="1"/>
-        <v>0.95280889802181434</v>
+        <v>0.95282235811935512</v>
       </c>
       <c r="H30" s="7">
         <v>223846</v>
@@ -5447,14 +5447,14 @@
       </c>
       <c r="J30" s="17">
         <f t="shared" si="2"/>
-        <v>151617</v>
+        <v>151619</v>
       </c>
       <c r="K30" s="16">
-        <v>213095</v>
+        <v>213097</v>
       </c>
       <c r="L30" s="18">
         <f t="shared" si="3"/>
-        <v>0.95197144465391381</v>
+        <v>0.95198037936795832</v>
       </c>
       <c r="M30" s="7">
         <v>227236</v>
@@ -5464,14 +5464,14 @@
       </c>
       <c r="O30" s="17">
         <f t="shared" si="4"/>
-        <v>148652</v>
+        <v>148653</v>
       </c>
       <c r="P30" s="16">
-        <v>215563</v>
+        <v>215564</v>
       </c>
       <c r="Q30" s="18">
         <f t="shared" si="5"/>
-        <v>0.94863049868858806</v>
+        <v>0.94863489939974299</v>
       </c>
       <c r="R30" s="7">
         <v>232779</v>
@@ -5481,14 +5481,14 @@
       </c>
       <c r="T30" s="17">
         <f t="shared" si="6"/>
-        <v>146417</v>
+        <v>146418</v>
       </c>
       <c r="U30" s="16">
-        <v>218438</v>
+        <v>218439</v>
       </c>
       <c r="V30" s="18">
         <f t="shared" si="7"/>
-        <v>0.9383922089191894</v>
+        <v>0.93839650483935411</v>
       </c>
       <c r="W30" s="7">
         <v>236990</v>
@@ -5498,14 +5498,14 @@
       </c>
       <c r="Y30" s="17">
         <f t="shared" si="8"/>
-        <v>97441</v>
+        <v>97442</v>
       </c>
       <c r="Z30" s="16">
-        <v>220884</v>
+        <v>220885</v>
       </c>
       <c r="AA30" s="18">
         <f t="shared" si="9"/>
-        <v>0.93203932655386301</v>
+        <v>0.93204354614118734</v>
       </c>
       <c r="AB30" s="28">
         <v>242455</v>
@@ -5515,14 +5515,14 @@
       </c>
       <c r="AD30" s="17">
         <f t="shared" si="10"/>
-        <v>59881</v>
+        <v>59885</v>
       </c>
       <c r="AE30" s="40">
-        <v>223565</v>
+        <v>223569</v>
       </c>
       <c r="AF30" s="18">
         <f t="shared" si="11"/>
-        <v>0.92208863500443383</v>
+        <v>0.92210513291126184</v>
       </c>
       <c r="AG30" s="16">
         <v>245898</v>
@@ -5532,14 +5532,14 @@
       </c>
       <c r="AI30" s="17">
         <f t="shared" si="12"/>
-        <v>55594</v>
+        <v>55598</v>
       </c>
       <c r="AJ30" s="16">
-        <v>226474</v>
+        <v>226478</v>
       </c>
       <c r="AK30" s="18">
         <f t="shared" si="13"/>
-        <v>0.92100789758355095</v>
+        <v>0.9210241644909678</v>
       </c>
       <c r="AL30" s="30">
         <v>247799</v>
@@ -5549,14 +5549,14 @@
       </c>
       <c r="AN30" s="17">
         <f t="shared" si="14"/>
-        <v>51256</v>
+        <v>51260</v>
       </c>
       <c r="AO30" s="16">
-        <v>229601</v>
+        <v>229605</v>
       </c>
       <c r="AP30" s="18">
         <f t="shared" si="15"/>
-        <v>0.92656144697920495</v>
+        <v>0.92657758909438703</v>
       </c>
       <c r="AQ30" s="32">
         <v>248265</v>
@@ -5566,14 +5566,14 @@
       </c>
       <c r="AS30" s="17">
         <f t="shared" si="16"/>
-        <v>46749</v>
+        <v>46753</v>
       </c>
       <c r="AT30" s="16">
-        <v>232654</v>
+        <v>232658</v>
       </c>
       <c r="AU30" s="18">
         <f t="shared" si="17"/>
-        <v>0.93711961009405276</v>
+        <v>0.93713572191005579</v>
       </c>
       <c r="AV30" s="34">
         <v>136662</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="AX30" s="17">
         <f t="shared" si="18"/>
-        <v>48122</v>
+        <v>48127</v>
       </c>
       <c r="AY30" s="19">
-        <v>121212</v>
+        <v>121217</v>
       </c>
       <c r="AZ30" s="18">
         <f t="shared" si="19"/>
-        <v>0.88694735917811829</v>
+        <v>0.886983945793271</v>
       </c>
       <c r="BA30" s="36">
         <v>130439</v>
@@ -5600,14 +5600,14 @@
       </c>
       <c r="BC30" s="17">
         <f t="shared" si="20"/>
-        <v>39066</v>
+        <v>39072</v>
       </c>
       <c r="BD30" s="38">
-        <v>124149</v>
+        <v>124155</v>
       </c>
       <c r="BE30" s="18">
         <f t="shared" si="21"/>
-        <v>0.9517782258373646</v>
+        <v>0.9518242243500793</v>
       </c>
       <c r="BF30" s="9">
         <v>245647</v>
@@ -5617,14 +5617,14 @@
       </c>
       <c r="BH30" s="17">
         <f t="shared" si="22"/>
-        <v>73626</v>
+        <v>73632</v>
       </c>
       <c r="BI30" s="19">
-        <v>239369</v>
+        <v>239375</v>
       </c>
       <c r="BJ30" s="18">
         <f t="shared" si="23"/>
-        <v>0.97444300154286434</v>
+        <v>0.97446742683606968</v>
       </c>
       <c r="BK30" s="2"/>
       <c r="BL30" s="2"/>
@@ -5644,14 +5644,14 @@
       </c>
       <c r="E31" s="17">
         <f t="shared" si="0"/>
-        <v>91676</v>
+        <v>91678</v>
       </c>
       <c r="F31" s="16">
-        <v>101334</v>
+        <v>101336</v>
       </c>
       <c r="G31" s="18">
         <f t="shared" si="1"/>
-        <v>0.9478085189965767</v>
+        <v>0.9478272256205923</v>
       </c>
       <c r="H31" s="7">
         <v>106827</v>
@@ -5661,14 +5661,14 @@
       </c>
       <c r="J31" s="17">
         <f t="shared" si="2"/>
-        <v>81394</v>
+        <v>81396</v>
       </c>
       <c r="K31" s="16">
-        <v>101519</v>
+        <v>101521</v>
       </c>
       <c r="L31" s="18">
         <f t="shared" si="3"/>
-        <v>0.95031218699392472</v>
+        <v>0.95033090885263094</v>
       </c>
       <c r="M31" s="7">
         <v>107995</v>
@@ -5678,14 +5678,14 @@
       </c>
       <c r="O31" s="17">
         <f t="shared" si="4"/>
-        <v>67606</v>
+        <v>67608</v>
       </c>
       <c r="P31" s="16">
-        <v>102501</v>
+        <v>102503</v>
       </c>
       <c r="Q31" s="18">
         <f t="shared" si="5"/>
-        <v>0.94912727441085232</v>
+        <v>0.94914579378674935</v>
       </c>
       <c r="R31" s="7">
         <v>110315</v>
@@ -5695,14 +5695,14 @@
       </c>
       <c r="T31" s="17">
         <f t="shared" si="6"/>
-        <v>69316</v>
+        <v>69318</v>
       </c>
       <c r="U31" s="16">
-        <v>104142</v>
+        <v>104144</v>
       </c>
       <c r="V31" s="18">
         <f t="shared" si="7"/>
-        <v>0.94404206136971403</v>
+        <v>0.94406019127045282</v>
       </c>
       <c r="W31" s="7">
         <v>111481</v>
@@ -5712,14 +5712,14 @@
       </c>
       <c r="Y31" s="17">
         <f t="shared" si="8"/>
-        <v>58147</v>
+        <v>58149</v>
       </c>
       <c r="Z31" s="16">
-        <v>105280</v>
+        <v>105282</v>
       </c>
       <c r="AA31" s="18">
         <f t="shared" si="9"/>
-        <v>0.94437617172432975</v>
+        <v>0.9443941120011482</v>
       </c>
       <c r="AB31" s="28">
         <v>113499</v>
@@ -5729,14 +5729,14 @@
       </c>
       <c r="AD31" s="17">
         <f t="shared" si="10"/>
-        <v>42486</v>
+        <v>42489</v>
       </c>
       <c r="AE31" s="40">
-        <v>106233</v>
+        <v>106236</v>
       </c>
       <c r="AF31" s="18">
         <f t="shared" si="11"/>
-        <v>0.93598181481775167</v>
+        <v>0.93600824676869399</v>
       </c>
       <c r="AG31" s="16">
         <v>114692</v>
@@ -5746,14 +5746,14 @@
       </c>
       <c r="AI31" s="17">
         <f t="shared" si="12"/>
-        <v>42960</v>
+        <v>42963</v>
       </c>
       <c r="AJ31" s="16">
-        <v>107131</v>
+        <v>107134</v>
       </c>
       <c r="AK31" s="18">
         <f t="shared" si="13"/>
-        <v>0.9340756112021763</v>
+        <v>0.93410176821399926</v>
       </c>
       <c r="AL31" s="30">
         <v>115249</v>
@@ -5763,14 +5763,14 @@
       </c>
       <c r="AN31" s="17">
         <f t="shared" si="14"/>
-        <v>37322</v>
+        <v>37324</v>
       </c>
       <c r="AO31" s="16">
-        <v>108063</v>
+        <v>108065</v>
       </c>
       <c r="AP31" s="18">
         <f t="shared" si="15"/>
-        <v>0.93764804900693277</v>
+        <v>0.9376654027366832</v>
       </c>
       <c r="AQ31" s="32">
         <v>115872</v>
@@ -5780,14 +5780,14 @@
       </c>
       <c r="AS31" s="17">
         <f t="shared" si="16"/>
-        <v>30093</v>
+        <v>30094</v>
       </c>
       <c r="AT31" s="16">
-        <v>109484</v>
+        <v>109485</v>
       </c>
       <c r="AU31" s="18">
         <f t="shared" si="17"/>
-        <v>0.94487020160176749</v>
+        <v>0.9448788318144159</v>
       </c>
       <c r="AV31" s="34">
         <v>66168</v>
@@ -5797,14 +5797,14 @@
       </c>
       <c r="AX31" s="17">
         <f t="shared" si="18"/>
-        <v>26438</v>
+        <v>26440</v>
       </c>
       <c r="AY31" s="19">
-        <v>61143</v>
+        <v>61145</v>
       </c>
       <c r="AZ31" s="18">
         <f t="shared" si="19"/>
-        <v>0.92405694595574905</v>
+        <v>0.92408717204691093</v>
       </c>
       <c r="BA31" s="36">
         <v>65704</v>
@@ -5814,14 +5814,14 @@
       </c>
       <c r="BC31" s="17">
         <f t="shared" si="20"/>
-        <v>24450</v>
+        <v>24451</v>
       </c>
       <c r="BD31" s="38">
-        <v>63429</v>
+        <v>63430</v>
       </c>
       <c r="BE31" s="18">
         <f t="shared" si="21"/>
-        <v>0.96537501521977354</v>
+        <v>0.96539023499330334</v>
       </c>
       <c r="BF31" s="9">
         <v>116311</v>
@@ -5831,14 +5831,14 @@
       </c>
       <c r="BH31" s="17">
         <f t="shared" si="22"/>
-        <v>67312</v>
+        <v>67313</v>
       </c>
       <c r="BI31" s="19">
-        <v>114380</v>
+        <v>114381</v>
       </c>
       <c r="BJ31" s="18">
         <f t="shared" si="23"/>
-        <v>0.98339795892048043</v>
+        <v>0.98340655655956877</v>
       </c>
       <c r="BK31" s="2"/>
       <c r="BL31" s="2"/>
@@ -5858,14 +5858,14 @@
       </c>
       <c r="E32" s="17">
         <f t="shared" si="0"/>
-        <v>317970</v>
+        <v>317971</v>
       </c>
       <c r="F32" s="16">
-        <v>342986</v>
+        <v>342987</v>
       </c>
       <c r="G32" s="18">
         <f t="shared" si="1"/>
-        <v>0.97689533976268739</v>
+        <v>0.97689818797031025</v>
       </c>
       <c r="H32" s="7">
         <v>350849</v>
@@ -5909,14 +5909,14 @@
       </c>
       <c r="T32" s="17">
         <f t="shared" si="6"/>
-        <v>217456</v>
+        <v>217457</v>
       </c>
       <c r="U32" s="16">
-        <v>350014</v>
+        <v>350015</v>
       </c>
       <c r="V32" s="18">
         <f t="shared" si="7"/>
-        <v>0.97146235317627727</v>
+        <v>0.97146512867198087</v>
       </c>
       <c r="W32" s="7">
         <v>365792</v>
@@ -5926,14 +5926,14 @@
       </c>
       <c r="Y32" s="17">
         <f t="shared" si="8"/>
-        <v>157703</v>
+        <v>157705</v>
       </c>
       <c r="Z32" s="16">
-        <v>353407</v>
+        <v>353409</v>
       </c>
       <c r="AA32" s="18">
         <f t="shared" si="9"/>
-        <v>0.96614196045840262</v>
+        <v>0.96614742804654008</v>
       </c>
       <c r="AB32" s="28">
         <v>374326</v>
@@ -6072,14 +6072,14 @@
       </c>
       <c r="E33" s="17">
         <f t="shared" si="0"/>
-        <v>808064</v>
+        <v>808066</v>
       </c>
       <c r="F33" s="16">
-        <v>845885</v>
+        <v>845887</v>
       </c>
       <c r="G33" s="18">
         <f t="shared" si="1"/>
-        <v>0.9478828858105276</v>
+        <v>0.94788512697306349</v>
       </c>
       <c r="H33" s="7">
         <v>888497</v>
@@ -6089,14 +6089,14 @@
       </c>
       <c r="J33" s="17">
         <f t="shared" si="2"/>
-        <v>639075</v>
+        <v>639077</v>
       </c>
       <c r="K33" s="16">
-        <v>846054</v>
+        <v>846056</v>
       </c>
       <c r="L33" s="18">
         <f t="shared" si="3"/>
-        <v>0.95223056465019018</v>
+        <v>0.95223281564259643</v>
       </c>
       <c r="M33" s="7">
         <v>888717</v>
@@ -6106,14 +6106,14 @@
       </c>
       <c r="O33" s="17">
         <f t="shared" si="4"/>
-        <v>454201</v>
+        <v>454203</v>
       </c>
       <c r="P33" s="16">
-        <v>850264</v>
+        <v>850266</v>
       </c>
       <c r="Q33" s="18">
         <f t="shared" si="5"/>
-        <v>0.95673200805205705</v>
+        <v>0.95673425848723492</v>
       </c>
       <c r="R33" s="7">
         <v>899174</v>
@@ -6123,14 +6123,14 @@
       </c>
       <c r="T33" s="17">
         <f t="shared" si="6"/>
-        <v>425242</v>
+        <v>425245</v>
       </c>
       <c r="U33" s="16">
-        <v>858917</v>
+        <v>858920</v>
       </c>
       <c r="V33" s="18">
         <f t="shared" si="7"/>
-        <v>0.95522891008859245</v>
+        <v>0.9552322464839953</v>
       </c>
       <c r="W33" s="7">
         <v>909355</v>
@@ -6140,14 +6140,14 @@
       </c>
       <c r="Y33" s="17">
         <f t="shared" si="8"/>
-        <v>280853</v>
+        <v>280855</v>
       </c>
       <c r="Z33" s="16">
-        <v>867293</v>
+        <v>867295</v>
       </c>
       <c r="AA33" s="18">
         <f t="shared" si="9"/>
-        <v>0.95374523700864899</v>
+        <v>0.95374743636973458</v>
       </c>
       <c r="AB33" s="28">
         <v>919225</v>
@@ -6157,14 +6157,14 @@
       </c>
       <c r="AD33" s="17">
         <f t="shared" si="10"/>
-        <v>196753</v>
+        <v>196756</v>
       </c>
       <c r="AE33" s="40">
-        <v>876677</v>
+        <v>876680</v>
       </c>
       <c r="AF33" s="18">
         <f t="shared" si="11"/>
-        <v>0.95371318230030733</v>
+        <v>0.95371644591911664</v>
       </c>
       <c r="AG33" s="16">
         <v>928340</v>
@@ -6174,14 +6174,14 @@
       </c>
       <c r="AI33" s="17">
         <f t="shared" si="12"/>
-        <v>235379</v>
+        <v>235382</v>
       </c>
       <c r="AJ33" s="16">
-        <v>884844</v>
+        <v>884847</v>
       </c>
       <c r="AK33" s="18">
         <f t="shared" si="13"/>
-        <v>0.95314647650645234</v>
+        <v>0.95314970808109101</v>
       </c>
       <c r="AL33" s="30">
         <v>932930</v>
@@ -6191,14 +6191,14 @@
       </c>
       <c r="AN33" s="17">
         <f t="shared" si="14"/>
-        <v>167610</v>
+        <v>167614</v>
       </c>
       <c r="AO33" s="16">
-        <v>892486</v>
+        <v>892490</v>
       </c>
       <c r="AP33" s="18">
         <f t="shared" si="15"/>
-        <v>0.95664840877664992</v>
+        <v>0.95665269634377714</v>
       </c>
       <c r="AQ33" s="32">
         <v>933808</v>
@@ -6208,14 +6208,14 @@
       </c>
       <c r="AS33" s="17">
         <f t="shared" si="16"/>
-        <v>132951</v>
+        <v>132954</v>
       </c>
       <c r="AT33" s="16">
-        <v>901469</v>
+        <v>901472</v>
       </c>
       <c r="AU33" s="18">
         <f t="shared" si="17"/>
-        <v>0.96536868392646025</v>
+        <v>0.96537189657831157</v>
       </c>
       <c r="AV33" s="34">
         <v>471009</v>
@@ -6225,14 +6225,14 @@
       </c>
       <c r="AX33" s="17">
         <f t="shared" si="18"/>
-        <v>112007</v>
+        <v>112008</v>
       </c>
       <c r="AY33" s="19">
-        <v>443841</v>
+        <v>443842</v>
       </c>
       <c r="AZ33" s="18">
         <f t="shared" si="19"/>
-        <v>0.94231957351133422</v>
+        <v>0.9423216966130159</v>
       </c>
       <c r="BA33" s="36">
         <v>469149</v>
@@ -6242,14 +6242,14 @@
       </c>
       <c r="BC33" s="17">
         <f t="shared" si="20"/>
-        <v>98006</v>
+        <v>98007</v>
       </c>
       <c r="BD33" s="38">
-        <v>454669</v>
+        <v>454670</v>
       </c>
       <c r="BE33" s="18">
         <f t="shared" si="21"/>
-        <v>0.96913560510626684</v>
+        <v>0.96913773662525127</v>
       </c>
       <c r="BF33" s="9">
         <v>935950</v>
@@ -6259,14 +6259,14 @@
       </c>
       <c r="BH33" s="17">
         <f t="shared" si="22"/>
-        <v>222953</v>
+        <v>222957</v>
       </c>
       <c r="BI33" s="19">
-        <v>922569</v>
+        <v>922573</v>
       </c>
       <c r="BJ33" s="18">
         <f t="shared" si="23"/>
-        <v>0.98570329611624552</v>
+        <v>0.98570756984881669</v>
       </c>
       <c r="BK33" s="2"/>
       <c r="BL33" s="2"/>
@@ -6698,14 +6698,14 @@
       </c>
       <c r="E36" s="17">
         <f t="shared" si="0"/>
-        <v>1190277</v>
+        <v>1190285</v>
       </c>
       <c r="F36" s="16">
-        <v>1261892</v>
+        <v>1261900</v>
       </c>
       <c r="G36" s="18">
         <f t="shared" si="1"/>
-        <v>0.91462525422524898</v>
+        <v>0.91463105266286004</v>
       </c>
       <c r="H36" s="7">
         <v>1370063</v>
@@ -6715,14 +6715,14 @@
       </c>
       <c r="J36" s="17">
         <f t="shared" si="2"/>
-        <v>1054960</v>
+        <v>1054967</v>
       </c>
       <c r="K36" s="16">
-        <v>1261855</v>
+        <v>1261862</v>
       </c>
       <c r="L36" s="18">
         <f t="shared" si="3"/>
-        <v>0.92101969033540798</v>
+        <v>0.92102479958950789</v>
       </c>
       <c r="M36" s="7">
         <v>1376699</v>
@@ -6732,14 +6732,14 @@
       </c>
       <c r="O36" s="17">
         <f t="shared" si="4"/>
-        <v>909584</v>
+        <v>909592</v>
       </c>
       <c r="P36" s="16">
-        <v>1267341</v>
+        <v>1267349</v>
       </c>
       <c r="Q36" s="18">
         <f t="shared" si="5"/>
-        <v>0.92056506178910569</v>
+        <v>0.92057087279063909</v>
       </c>
       <c r="R36" s="7">
         <v>1386159</v>
@@ -6749,14 +6749,14 @@
       </c>
       <c r="T36" s="17">
         <f t="shared" si="6"/>
-        <v>856791</v>
+        <v>856800</v>
       </c>
       <c r="U36" s="16">
-        <v>1274708</v>
+        <v>1274717</v>
       </c>
       <c r="V36" s="18">
         <f t="shared" si="7"/>
-        <v>0.91959724678049204</v>
+        <v>0.91960373954214492</v>
       </c>
       <c r="W36" s="7">
         <v>1395892</v>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="Y36" s="17">
         <f t="shared" si="8"/>
-        <v>663030</v>
+        <v>663042</v>
       </c>
       <c r="Z36" s="16">
-        <v>1283913</v>
+        <v>1283925</v>
       </c>
       <c r="AA36" s="18">
         <f t="shared" si="9"/>
-        <v>0.91977961045696943</v>
+        <v>0.91978820711057874</v>
       </c>
       <c r="AB36" s="28">
         <v>1408098</v>
@@ -6783,14 +6783,14 @@
       </c>
       <c r="AD36" s="17">
         <f t="shared" si="10"/>
-        <v>434744</v>
+        <v>434753</v>
       </c>
       <c r="AE36" s="40">
-        <v>1290844</v>
+        <v>1290853</v>
       </c>
       <c r="AF36" s="18">
         <f t="shared" si="11"/>
-        <v>0.91672880722790606</v>
+        <v>0.91673519882849064</v>
       </c>
       <c r="AG36" s="16">
         <v>1413160</v>
@@ -6800,14 +6800,14 @@
       </c>
       <c r="AI36" s="17">
         <f t="shared" si="12"/>
-        <v>420923</v>
+        <v>420936</v>
       </c>
       <c r="AJ36" s="16">
-        <v>1299752</v>
+        <v>1299765</v>
       </c>
       <c r="AK36" s="18">
         <f t="shared" si="13"/>
-        <v>0.91974864841914572</v>
+        <v>0.91975784766056212</v>
       </c>
       <c r="AL36" s="30">
         <v>1410829</v>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="AN36" s="17">
         <f t="shared" si="14"/>
-        <v>358663</v>
+        <v>358677</v>
       </c>
       <c r="AO36" s="16">
-        <v>1310031</v>
+        <v>1310045</v>
       </c>
       <c r="AP36" s="18">
         <f t="shared" si="15"/>
-        <v>0.92855406289493625</v>
+        <v>0.9285639861386461</v>
       </c>
       <c r="AQ36" s="32">
         <v>1406326</v>
@@ -6834,14 +6834,14 @@
       </c>
       <c r="AS36" s="17">
         <f t="shared" si="16"/>
-        <v>299722</v>
+        <v>299735</v>
       </c>
       <c r="AT36" s="16">
-        <v>1321845</v>
+        <v>1321858</v>
       </c>
       <c r="AU36" s="18">
         <f t="shared" si="17"/>
-        <v>0.93992786878718027</v>
+        <v>0.93993711273204084</v>
       </c>
       <c r="AV36" s="34">
         <v>685252</v>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="AX36" s="17">
         <f t="shared" si="18"/>
-        <v>251666</v>
+        <v>251677</v>
       </c>
       <c r="AY36" s="19">
-        <v>635308</v>
+        <v>635319</v>
       </c>
       <c r="AZ36" s="18">
         <f t="shared" si="19"/>
-        <v>0.92711586394494283</v>
+        <v>0.92713191643366233</v>
       </c>
       <c r="BA36" s="36">
         <v>667048</v>
@@ -6868,14 +6868,14 @@
       </c>
       <c r="BC36" s="17">
         <f t="shared" si="20"/>
-        <v>222469</v>
+        <v>222478</v>
       </c>
       <c r="BD36" s="38">
-        <v>648488</v>
+        <v>648497</v>
       </c>
       <c r="BE36" s="18">
         <f t="shared" si="21"/>
-        <v>0.97217591537640469</v>
+        <v>0.97218940765881912</v>
       </c>
       <c r="BF36" s="9">
         <v>1363993</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="BH36" s="17">
         <f t="shared" si="22"/>
-        <v>477173</v>
+        <v>477183</v>
       </c>
       <c r="BI36" s="19">
-        <v>1343298</v>
+        <v>1343308</v>
       </c>
       <c r="BJ36" s="18">
         <f t="shared" si="23"/>
-        <v>0.98482763474592616</v>
+        <v>0.98483496616184985</v>
       </c>
       <c r="BK36" s="2"/>
       <c r="BL36" s="2"/>
@@ -6912,14 +6912,14 @@
       </c>
       <c r="E37" s="17">
         <f t="shared" si="0"/>
-        <v>576551</v>
+        <v>576554</v>
       </c>
       <c r="F37" s="16">
-        <v>676211</v>
+        <v>676214</v>
       </c>
       <c r="G37" s="18">
         <f t="shared" si="1"/>
-        <v>0.92146925760383736</v>
+        <v>0.92147334568843342</v>
       </c>
       <c r="H37" s="7">
         <v>729493</v>
@@ -6929,14 +6929,14 @@
       </c>
       <c r="J37" s="17">
         <f t="shared" si="2"/>
-        <v>474087</v>
+        <v>474088</v>
       </c>
       <c r="K37" s="16">
-        <v>677780</v>
+        <v>677781</v>
       </c>
       <c r="L37" s="18">
         <f t="shared" si="3"/>
-        <v>0.92911104013335288</v>
+        <v>0.92911241094842578</v>
       </c>
       <c r="M37" s="7">
         <v>737436</v>
@@ -6946,14 +6946,14 @@
       </c>
       <c r="O37" s="17">
         <f t="shared" si="4"/>
-        <v>446524</v>
+        <v>446525</v>
       </c>
       <c r="P37" s="16">
-        <v>683924</v>
+        <v>683925</v>
       </c>
       <c r="Q37" s="18">
         <f t="shared" si="5"/>
-        <v>0.9274350587712018</v>
+        <v>0.92743641482108274</v>
       </c>
       <c r="R37" s="7">
         <v>746987</v>
@@ -6963,14 +6963,14 @@
       </c>
       <c r="T37" s="17">
         <f t="shared" si="6"/>
-        <v>392166</v>
+        <v>392168</v>
       </c>
       <c r="U37" s="16">
-        <v>689282</v>
+        <v>689284</v>
       </c>
       <c r="V37" s="18">
         <f t="shared" si="7"/>
-        <v>0.92274965963263078</v>
+        <v>0.92275233705539716</v>
       </c>
       <c r="W37" s="7">
         <v>758127</v>
@@ -6980,14 +6980,14 @@
       </c>
       <c r="Y37" s="17">
         <f t="shared" si="8"/>
-        <v>268430</v>
+        <v>268432</v>
       </c>
       <c r="Z37" s="16">
-        <v>695636</v>
+        <v>695638</v>
       </c>
       <c r="AA37" s="18">
         <f t="shared" si="9"/>
-        <v>0.91757185801323526</v>
+        <v>0.91757449609366237</v>
       </c>
       <c r="AB37" s="28">
         <v>768520</v>
@@ -6997,14 +6997,14 @@
       </c>
       <c r="AD37" s="17">
         <f t="shared" si="10"/>
-        <v>196238</v>
+        <v>196240</v>
       </c>
       <c r="AE37" s="40">
-        <v>701720</v>
+        <v>701722</v>
       </c>
       <c r="AF37" s="18">
         <f t="shared" si="11"/>
-        <v>0.91307968562952169</v>
+        <v>0.9130822880341436</v>
       </c>
       <c r="AG37" s="16">
         <v>770579</v>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="AI37" s="17">
         <f t="shared" si="12"/>
-        <v>189644</v>
+        <v>189646</v>
       </c>
       <c r="AJ37" s="16">
-        <v>707545</v>
+        <v>707547</v>
       </c>
       <c r="AK37" s="18">
         <f t="shared" si="13"/>
-        <v>0.91819917231069104</v>
+        <v>0.91820176776164419</v>
       </c>
       <c r="AL37" s="30">
         <v>769439</v>
@@ -7031,14 +7031,14 @@
       </c>
       <c r="AN37" s="17">
         <f t="shared" si="14"/>
-        <v>166234</v>
+        <v>166238</v>
       </c>
       <c r="AO37" s="16">
-        <v>715091</v>
+        <v>715095</v>
       </c>
       <c r="AP37" s="18">
         <f t="shared" si="15"/>
-        <v>0.92936672042877988</v>
+        <v>0.92937191902152083</v>
       </c>
       <c r="AQ37" s="32">
         <v>769503</v>
@@ -7048,14 +7048,14 @@
       </c>
       <c r="AS37" s="17">
         <f t="shared" si="16"/>
-        <v>134990</v>
+        <v>134994</v>
       </c>
       <c r="AT37" s="16">
-        <v>720383</v>
+        <v>720387</v>
       </c>
       <c r="AU37" s="18">
         <f t="shared" si="17"/>
-        <v>0.93616659064357122</v>
+        <v>0.93617178880394225</v>
       </c>
       <c r="AV37" s="34">
         <v>526548</v>
@@ -7065,14 +7065,14 @@
       </c>
       <c r="AX37" s="17">
         <f t="shared" si="18"/>
-        <v>135676</v>
+        <v>135681</v>
       </c>
       <c r="AY37" s="19">
-        <v>487943</v>
+        <v>487948</v>
       </c>
       <c r="AZ37" s="18">
         <f t="shared" si="19"/>
-        <v>0.92668284752767083</v>
+        <v>0.92669234333811923</v>
       </c>
       <c r="BA37" s="36">
         <v>525083</v>
@@ -7082,14 +7082,14 @@
       </c>
       <c r="BC37" s="17">
         <f t="shared" si="20"/>
-        <v>117155</v>
+        <v>117161</v>
       </c>
       <c r="BD37" s="38">
-        <v>495935</v>
+        <v>495941</v>
       </c>
       <c r="BE37" s="18">
         <f t="shared" si="21"/>
-        <v>0.94448877606016568</v>
+        <v>0.94450020282507718</v>
       </c>
       <c r="BF37" s="9">
         <v>765317</v>
@@ -7099,14 +7099,14 @@
       </c>
       <c r="BH37" s="17">
         <f t="shared" si="22"/>
-        <v>198981</v>
+        <v>198987</v>
       </c>
       <c r="BI37" s="19">
-        <v>738854</v>
+        <v>738860</v>
       </c>
       <c r="BJ37" s="18">
         <f t="shared" si="23"/>
-        <v>0.96542217146620291</v>
+        <v>0.96543001135477191</v>
       </c>
       <c r="BK37" s="2"/>
       <c r="BL37" s="2"/>
@@ -7126,14 +7126,14 @@
       </c>
       <c r="E38" s="17">
         <f t="shared" si="0"/>
-        <v>25864</v>
+        <v>25865</v>
       </c>
       <c r="F38" s="16">
-        <v>30116</v>
+        <v>30117</v>
       </c>
       <c r="G38" s="18">
         <f t="shared" si="1"/>
-        <v>0.8362071359155907</v>
+        <v>0.836234902124115</v>
       </c>
       <c r="H38" s="7">
         <v>35551</v>
@@ -7143,14 +7143,14 @@
       </c>
       <c r="J38" s="17">
         <f t="shared" si="2"/>
-        <v>22893</v>
+        <v>22894</v>
       </c>
       <c r="K38" s="16">
-        <v>30163</v>
+        <v>30164</v>
       </c>
       <c r="L38" s="18">
         <f t="shared" si="3"/>
-        <v>0.84844308176985173</v>
+        <v>0.84847121037382911</v>
       </c>
       <c r="M38" s="7">
         <v>35630</v>
@@ -7160,14 +7160,14 @@
       </c>
       <c r="O38" s="17">
         <f t="shared" si="4"/>
-        <v>19957</v>
+        <v>19958</v>
       </c>
       <c r="P38" s="16">
-        <v>30326</v>
+        <v>30327</v>
       </c>
       <c r="Q38" s="18">
         <f t="shared" si="5"/>
-        <v>0.85113668257086728</v>
+        <v>0.85116474880718496</v>
       </c>
       <c r="R38" s="7">
         <v>35883</v>
@@ -7177,14 +7177,14 @@
       </c>
       <c r="T38" s="17">
         <f t="shared" si="6"/>
-        <v>19437</v>
+        <v>19438</v>
       </c>
       <c r="U38" s="16">
-        <v>30450</v>
+        <v>30451</v>
       </c>
       <c r="V38" s="18">
         <f t="shared" si="7"/>
-        <v>0.84859125491179666</v>
+        <v>0.84861912326171163</v>
       </c>
       <c r="W38" s="7">
         <v>36112</v>
@@ -7194,14 +7194,14 @@
       </c>
       <c r="Y38" s="17">
         <f t="shared" si="8"/>
-        <v>15476</v>
+        <v>15477</v>
       </c>
       <c r="Z38" s="16">
-        <v>30617</v>
+        <v>30618</v>
       </c>
       <c r="AA38" s="18">
         <f t="shared" si="9"/>
-        <v>0.84783451484271155</v>
+        <v>0.84786220646876387</v>
       </c>
       <c r="AB38" s="28">
         <v>36289</v>
@@ -7211,14 +7211,14 @@
       </c>
       <c r="AD38" s="17">
         <f t="shared" si="10"/>
-        <v>11715</v>
+        <v>11716</v>
       </c>
       <c r="AE38" s="40">
-        <v>30687</v>
+        <v>30688</v>
       </c>
       <c r="AF38" s="18">
         <f t="shared" si="11"/>
-        <v>0.84562815178153161</v>
+        <v>0.84565570834137072</v>
       </c>
       <c r="AG38" s="16">
         <v>36624</v>
@@ -7228,14 +7228,14 @@
       </c>
       <c r="AI38" s="17">
         <f t="shared" si="12"/>
-        <v>11377</v>
+        <v>11378</v>
       </c>
       <c r="AJ38" s="16">
-        <v>30898</v>
+        <v>30899</v>
       </c>
       <c r="AK38" s="18">
         <f t="shared" si="13"/>
-        <v>0.84365443425076447</v>
+        <v>0.84368173875054608</v>
       </c>
       <c r="AL38" s="30">
         <v>36792</v>
@@ -7245,14 +7245,14 @@
       </c>
       <c r="AN38" s="17">
         <f t="shared" si="14"/>
-        <v>10820</v>
+        <v>10821</v>
       </c>
       <c r="AO38" s="16">
-        <v>31118</v>
+        <v>31119</v>
       </c>
       <c r="AP38" s="18">
         <f t="shared" si="15"/>
-        <v>0.8457816916721026</v>
+        <v>0.84580887149380302</v>
       </c>
       <c r="AQ38" s="32">
         <v>36918</v>
@@ -7262,14 +7262,14 @@
       </c>
       <c r="AS38" s="17">
         <f t="shared" si="16"/>
-        <v>8674</v>
+        <v>8675</v>
       </c>
       <c r="AT38" s="16">
-        <v>31352</v>
+        <v>31353</v>
       </c>
       <c r="AU38" s="18">
         <f t="shared" si="17"/>
-        <v>0.84923343626415304</v>
+        <v>0.84926052332195678</v>
       </c>
       <c r="AV38" s="34">
         <v>23509</v>
@@ -7279,14 +7279,14 @@
       </c>
       <c r="AX38" s="17">
         <f t="shared" si="18"/>
-        <v>7899</v>
+        <v>7900</v>
       </c>
       <c r="AY38" s="19">
-        <v>18387</v>
+        <v>18388</v>
       </c>
       <c r="AZ38" s="18">
         <f t="shared" si="19"/>
-        <v>0.78212599430005525</v>
+        <v>0.78216853120081675</v>
       </c>
       <c r="BA38" s="36">
         <v>22626</v>
@@ -7605,14 +7605,14 @@
       </c>
       <c r="T40" s="17">
         <f t="shared" si="6"/>
-        <v>201463</v>
+        <v>201464</v>
       </c>
       <c r="U40" s="16">
-        <v>282759</v>
+        <v>282760</v>
       </c>
       <c r="V40" s="18">
         <f t="shared" si="7"/>
-        <v>0.92440851180687911</v>
+        <v>0.92441178105210853</v>
       </c>
       <c r="W40" s="7">
         <v>309941</v>
@@ -7622,14 +7622,14 @@
       </c>
       <c r="Y40" s="17">
         <f t="shared" si="8"/>
-        <v>162283</v>
+        <v>162284</v>
       </c>
       <c r="Z40" s="16">
-        <v>286100</v>
+        <v>286101</v>
       </c>
       <c r="AA40" s="18">
         <f t="shared" si="9"/>
-        <v>0.92307890856646913</v>
+        <v>0.92308213498698144</v>
       </c>
       <c r="AB40" s="28">
         <v>313197</v>
@@ -7656,14 +7656,14 @@
       </c>
       <c r="AI40" s="17">
         <f t="shared" si="12"/>
-        <v>93352</v>
+        <v>93354</v>
       </c>
       <c r="AJ40" s="16">
-        <v>291252</v>
+        <v>291254</v>
       </c>
       <c r="AK40" s="18">
         <f t="shared" si="13"/>
-        <v>0.91914716352344161</v>
+        <v>0.91915347522027824</v>
       </c>
       <c r="AL40" s="30">
         <v>319591</v>
@@ -7673,14 +7673,14 @@
       </c>
       <c r="AN40" s="17">
         <f t="shared" si="14"/>
-        <v>85453</v>
+        <v>85454</v>
       </c>
       <c r="AO40" s="16">
-        <v>294966</v>
+        <v>294967</v>
       </c>
       <c r="AP40" s="18">
         <f t="shared" si="15"/>
-        <v>0.92294839341533397</v>
+        <v>0.92295152241458611</v>
       </c>
       <c r="AQ40" s="32">
         <v>320883</v>
@@ -7690,14 +7690,14 @@
       </c>
       <c r="AS40" s="17">
         <f t="shared" si="16"/>
-        <v>70106</v>
+        <v>70107</v>
       </c>
       <c r="AT40" s="16">
-        <v>298153</v>
+        <v>298154</v>
       </c>
       <c r="AU40" s="18">
         <f t="shared" si="17"/>
-        <v>0.92916421250112968</v>
+        <v>0.92916732890181153</v>
       </c>
       <c r="AV40" s="34">
         <v>237285</v>
@@ -7707,14 +7707,14 @@
       </c>
       <c r="AX40" s="17">
         <f t="shared" si="18"/>
-        <v>72821</v>
+        <v>72823</v>
       </c>
       <c r="AY40" s="19">
-        <v>218383</v>
+        <v>218385</v>
       </c>
       <c r="AZ40" s="18">
         <f t="shared" si="19"/>
-        <v>0.92034051878542678</v>
+        <v>0.92034894746823437</v>
       </c>
       <c r="BA40" s="36">
         <v>231667</v>
@@ -7724,14 +7724,14 @@
       </c>
       <c r="BC40" s="17">
         <f t="shared" si="20"/>
-        <v>66783</v>
+        <v>66785</v>
       </c>
       <c r="BD40" s="38">
-        <v>220881</v>
+        <v>220883</v>
       </c>
       <c r="BE40" s="18">
         <f t="shared" si="21"/>
-        <v>0.95344179360893011</v>
+        <v>0.95345042669003355</v>
       </c>
       <c r="BF40" s="9">
         <v>314391</v>
@@ -7741,14 +7741,14 @@
       </c>
       <c r="BH40" s="17">
         <f t="shared" si="22"/>
-        <v>110211</v>
+        <v>110212</v>
       </c>
       <c r="BI40" s="19">
-        <v>305160</v>
+        <v>305161</v>
       </c>
       <c r="BJ40" s="18">
         <f t="shared" si="23"/>
-        <v>0.97063847247535717</v>
+        <v>0.97064165322798679</v>
       </c>
       <c r="BK40" s="2"/>
       <c r="BL40" s="2"/>
@@ -7768,14 +7768,14 @@
       </c>
       <c r="E41" s="17">
         <f t="shared" si="0"/>
-        <v>721623</v>
+        <v>721650</v>
       </c>
       <c r="F41" s="16">
-        <v>811805</v>
+        <v>811832</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="1"/>
-        <v>0.92689156417411478</v>
+        <v>0.92692239186331693</v>
       </c>
       <c r="H41" s="7">
         <v>872102</v>
@@ -7785,14 +7785,14 @@
       </c>
       <c r="J41" s="17">
         <f t="shared" si="2"/>
-        <v>601107</v>
+        <v>601134</v>
       </c>
       <c r="K41" s="16">
-        <v>812758</v>
+        <v>812785</v>
       </c>
       <c r="L41" s="18">
         <f t="shared" si="3"/>
-        <v>0.93195291376467426</v>
+        <v>0.93198387344599598</v>
       </c>
       <c r="M41" s="7">
         <v>879453</v>
@@ -7802,14 +7802,14 @@
       </c>
       <c r="O41" s="17">
         <f t="shared" si="4"/>
-        <v>529760</v>
+        <v>529786</v>
       </c>
       <c r="P41" s="16">
-        <v>817846</v>
+        <v>817872</v>
       </c>
       <c r="Q41" s="18">
         <f t="shared" si="5"/>
-        <v>0.92994850208027036</v>
+        <v>0.92997806591142451</v>
       </c>
       <c r="R41" s="7">
         <v>900135</v>
@@ -7819,14 +7819,14 @@
       </c>
       <c r="T41" s="17">
         <f t="shared" si="6"/>
-        <v>493839</v>
+        <v>493867</v>
       </c>
       <c r="U41" s="16">
-        <v>829304</v>
+        <v>829332</v>
       </c>
       <c r="V41" s="18">
         <f t="shared" si="7"/>
-        <v>0.92131069228504614</v>
+        <v>0.92134179873019051</v>
       </c>
       <c r="W41" s="7">
         <v>916182</v>
@@ -7836,14 +7836,14 @@
       </c>
       <c r="Y41" s="17">
         <f t="shared" si="8"/>
-        <v>333076</v>
+        <v>333103</v>
       </c>
       <c r="Z41" s="16">
-        <v>837122</v>
+        <v>837149</v>
       </c>
       <c r="AA41" s="18">
         <f t="shared" si="9"/>
-        <v>0.91370710186404014</v>
+        <v>0.91373657199115454</v>
       </c>
       <c r="AB41" s="28">
         <v>928683</v>
@@ -7853,14 +7853,14 @@
       </c>
       <c r="AD41" s="17">
         <f t="shared" si="10"/>
-        <v>228026</v>
+        <v>228052</v>
       </c>
       <c r="AE41" s="40">
-        <v>842813</v>
+        <v>842839</v>
       </c>
       <c r="AF41" s="18">
         <f t="shared" si="11"/>
-        <v>0.90753572532284965</v>
+        <v>0.90756372195894619</v>
       </c>
       <c r="AG41" s="16">
         <v>933135</v>
@@ -7870,14 +7870,14 @@
       </c>
       <c r="AI41" s="17">
         <f t="shared" si="12"/>
-        <v>223105</v>
+        <v>223134</v>
       </c>
       <c r="AJ41" s="16">
-        <v>851053</v>
+        <v>851082</v>
       </c>
       <c r="AK41" s="18">
         <f t="shared" si="13"/>
-        <v>0.91203630771538957</v>
+        <v>0.91206738574804291</v>
       </c>
       <c r="AL41" s="30">
         <v>933314</v>
@@ -7887,14 +7887,14 @@
       </c>
       <c r="AN41" s="17">
         <f t="shared" si="14"/>
-        <v>186829</v>
+        <v>186854</v>
       </c>
       <c r="AO41" s="16">
-        <v>858712</v>
+        <v>858737</v>
       </c>
       <c r="AP41" s="18">
         <f t="shared" si="15"/>
-        <v>0.92006762997233515</v>
+        <v>0.92009441624147925</v>
       </c>
       <c r="AQ41" s="32">
         <v>923873</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="AS41" s="17">
         <f t="shared" si="16"/>
-        <v>168452</v>
+        <v>168473</v>
       </c>
       <c r="AT41" s="16">
-        <v>867847</v>
+        <v>867868</v>
       </c>
       <c r="AU41" s="18">
         <f t="shared" si="17"/>
-        <v>0.93935746579887058</v>
+        <v>0.93938019619579749</v>
       </c>
       <c r="AV41" s="34">
         <v>726285</v>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="AX41" s="17">
         <f t="shared" si="18"/>
-        <v>161014</v>
+        <v>161035</v>
       </c>
       <c r="AY41" s="19">
-        <v>680651</v>
+        <v>680672</v>
       </c>
       <c r="AZ41" s="18">
         <f t="shared" si="19"/>
-        <v>0.93716791617615669</v>
+        <v>0.93719683044534863</v>
       </c>
       <c r="BA41" s="36">
         <v>715063</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="BC41" s="17">
         <f t="shared" si="20"/>
-        <v>142425</v>
+        <v>142443</v>
       </c>
       <c r="BD41" s="38">
-        <v>688332</v>
+        <v>688350</v>
       </c>
       <c r="BE41" s="18">
         <f t="shared" si="21"/>
-        <v>0.96261727987603884</v>
+        <v>0.96264245248320779</v>
       </c>
       <c r="BF41" s="9">
         <v>910875</v>
@@ -7955,14 +7955,14 @@
       </c>
       <c r="BH41" s="17">
         <f t="shared" si="22"/>
-        <v>228658</v>
+        <v>228675</v>
       </c>
       <c r="BI41" s="19">
-        <v>887967</v>
+        <v>887984</v>
       </c>
       <c r="BJ41" s="18">
         <f t="shared" si="23"/>
-        <v>0.97485055578427338</v>
+        <v>0.97486921915740354</v>
       </c>
       <c r="BK41" s="2"/>
       <c r="BL41" s="2"/>
@@ -7982,14 +7982,14 @@
       </c>
       <c r="E42" s="17">
         <f t="shared" si="0"/>
-        <v>14857</v>
+        <v>14858</v>
       </c>
       <c r="F42" s="16">
-        <v>17691</v>
+        <v>17692</v>
       </c>
       <c r="G42" s="18">
         <f t="shared" si="1"/>
-        <v>0.90030534351145042</v>
+        <v>0.90035623409669208</v>
       </c>
       <c r="H42" s="7">
         <v>19392</v>
@@ -7999,14 +7999,14 @@
       </c>
       <c r="J42" s="17">
         <f t="shared" si="2"/>
-        <v>12812</v>
+        <v>12813</v>
       </c>
       <c r="K42" s="16">
-        <v>17612</v>
+        <v>17613</v>
       </c>
       <c r="L42" s="18">
         <f t="shared" si="3"/>
-        <v>0.90820957095709576</v>
+        <v>0.90826113861386137</v>
       </c>
       <c r="M42" s="7">
         <v>19399</v>
@@ -8169,14 +8169,14 @@
       </c>
       <c r="BH42" s="17">
         <f t="shared" si="22"/>
-        <v>5372</v>
+        <v>5374</v>
       </c>
       <c r="BI42" s="19">
-        <v>18640</v>
+        <v>18642</v>
       </c>
       <c r="BJ42" s="18">
         <f t="shared" si="23"/>
-        <v>0.94508948942858595</v>
+        <v>0.94519089388024136</v>
       </c>
       <c r="BK42" s="2"/>
       <c r="BL42" s="2"/>
@@ -8410,14 +8410,14 @@
       </c>
       <c r="E44" s="17">
         <f t="shared" si="0"/>
-        <v>260725</v>
+        <v>260726</v>
       </c>
       <c r="F44" s="16">
-        <v>302637</v>
+        <v>302638</v>
       </c>
       <c r="G44" s="18">
         <f t="shared" si="1"/>
-        <v>0.84689477233740684</v>
+        <v>0.84689757072217919</v>
       </c>
       <c r="H44" s="7">
         <v>355488</v>
@@ -8427,14 +8427,14 @@
       </c>
       <c r="J44" s="17">
         <f t="shared" si="2"/>
-        <v>218363</v>
+        <v>218365</v>
       </c>
       <c r="K44" s="16">
-        <v>302995</v>
+        <v>302997</v>
       </c>
       <c r="L44" s="18">
         <f t="shared" si="3"/>
-        <v>0.85233538122243224</v>
+        <v>0.8523410072913854</v>
       </c>
       <c r="M44" s="7">
         <v>358237</v>
@@ -8444,14 +8444,14 @@
       </c>
       <c r="O44" s="17">
         <f t="shared" si="4"/>
-        <v>188413</v>
+        <v>188415</v>
       </c>
       <c r="P44" s="16">
-        <v>305082</v>
+        <v>305084</v>
       </c>
       <c r="Q44" s="18">
         <f t="shared" si="5"/>
-        <v>0.85162057520579948</v>
+        <v>0.85162615810203857</v>
       </c>
       <c r="R44" s="7">
         <v>364550</v>
@@ -8461,14 +8461,14 @@
       </c>
       <c r="T44" s="17">
         <f t="shared" si="6"/>
-        <v>191970</v>
+        <v>191972</v>
       </c>
       <c r="U44" s="16">
-        <v>309028</v>
+        <v>309030</v>
       </c>
       <c r="V44" s="18">
         <f t="shared" si="7"/>
-        <v>0.84769716088328073</v>
+        <v>0.84770264709916332</v>
       </c>
       <c r="W44" s="7">
         <v>368236</v>
@@ -8478,14 +8478,14 @@
       </c>
       <c r="Y44" s="17">
         <f t="shared" si="8"/>
-        <v>140612</v>
+        <v>140614</v>
       </c>
       <c r="Z44" s="16">
-        <v>311929</v>
+        <v>311931</v>
       </c>
       <c r="AA44" s="18">
         <f t="shared" si="9"/>
-        <v>0.84708990973180243</v>
+        <v>0.84709534103129513</v>
       </c>
       <c r="AB44" s="28">
         <v>371659</v>
@@ -8495,14 +8495,14 @@
       </c>
       <c r="AD44" s="17">
         <f t="shared" si="10"/>
-        <v>118499</v>
+        <v>118501</v>
       </c>
       <c r="AE44" s="40">
-        <v>314148</v>
+        <v>314150</v>
       </c>
       <c r="AF44" s="18">
         <f t="shared" si="11"/>
-        <v>0.84525869143489063</v>
+        <v>0.84526407271181381</v>
       </c>
       <c r="AG44" s="16">
         <v>376783</v>
@@ -8512,14 +8512,14 @@
       </c>
       <c r="AI44" s="17">
         <f t="shared" si="12"/>
-        <v>113630</v>
+        <v>113633</v>
       </c>
       <c r="AJ44" s="16">
-        <v>317574</v>
+        <v>317577</v>
       </c>
       <c r="AK44" s="18">
         <f t="shared" si="13"/>
-        <v>0.84285649830273657</v>
+        <v>0.84286446044540231</v>
       </c>
       <c r="AL44" s="30">
         <v>379786</v>
@@ -8529,14 +8529,14 @@
       </c>
       <c r="AN44" s="17">
         <f t="shared" si="14"/>
-        <v>102484</v>
+        <v>102487</v>
       </c>
       <c r="AO44" s="16">
-        <v>321776</v>
+        <v>321779</v>
       </c>
       <c r="AP44" s="18">
         <f t="shared" si="15"/>
-        <v>0.84725608632229732</v>
+        <v>0.84726398550762794</v>
       </c>
       <c r="AQ44" s="32">
         <v>381213</v>
@@ -8546,14 +8546,14 @@
       </c>
       <c r="AS44" s="17">
         <f t="shared" si="16"/>
-        <v>84195</v>
+        <v>84197</v>
       </c>
       <c r="AT44" s="16">
-        <v>325854</v>
+        <v>325856</v>
       </c>
       <c r="AU44" s="18">
         <f t="shared" si="17"/>
-        <v>0.85478197228321173</v>
+        <v>0.85478721869401098</v>
       </c>
       <c r="AV44" s="34">
         <v>286191</v>
@@ -8563,14 +8563,14 @@
       </c>
       <c r="AX44" s="17">
         <f t="shared" si="18"/>
-        <v>80534</v>
+        <v>80536</v>
       </c>
       <c r="AY44" s="19">
-        <v>240005</v>
+        <v>240007</v>
       </c>
       <c r="AZ44" s="18">
         <f t="shared" si="19"/>
-        <v>0.83861826542413986</v>
+        <v>0.83862525376409458</v>
       </c>
       <c r="BA44" s="36">
         <v>282649</v>
@@ -8580,14 +8580,14 @@
       </c>
       <c r="BC44" s="17">
         <f t="shared" si="20"/>
-        <v>73132</v>
+        <v>73134</v>
       </c>
       <c r="BD44" s="38">
-        <v>244079</v>
+        <v>244081</v>
       </c>
       <c r="BE44" s="18">
         <f t="shared" si="21"/>
-        <v>0.8635409996143627</v>
+        <v>0.86354807552830537</v>
       </c>
       <c r="BF44" s="9">
         <v>372165</v>
@@ -8597,14 +8597,14 @@
       </c>
       <c r="BH44" s="17">
         <f t="shared" si="22"/>
-        <v>115085</v>
+        <v>115087</v>
       </c>
       <c r="BI44" s="19">
-        <v>334883</v>
+        <v>334885</v>
       </c>
       <c r="BJ44" s="18">
         <f t="shared" si="23"/>
-        <v>0.8998240027944594</v>
+        <v>0.89982937675493402</v>
       </c>
       <c r="BK44" s="2"/>
       <c r="BL44" s="2"/>
@@ -8624,14 +8624,14 @@
       </c>
       <c r="E45" s="17">
         <f t="shared" si="0"/>
-        <v>221915</v>
+        <v>221917</v>
       </c>
       <c r="F45" s="16">
-        <v>252282</v>
+        <v>252284</v>
       </c>
       <c r="G45" s="18">
         <f t="shared" si="1"/>
-        <v>0.89268287504732657</v>
+        <v>0.89268995191269984</v>
       </c>
       <c r="H45" s="7">
         <v>279976</v>
@@ -8641,14 +8641,14 @@
       </c>
       <c r="J45" s="17">
         <f t="shared" si="2"/>
-        <v>181837</v>
+        <v>181839</v>
       </c>
       <c r="K45" s="16">
-        <v>252344</v>
+        <v>252346</v>
       </c>
       <c r="L45" s="18">
         <f t="shared" si="3"/>
-        <v>0.9013058262136755</v>
+        <v>0.90131296968311569</v>
       </c>
       <c r="M45" s="7">
         <v>281786</v>
@@ -8658,14 +8658,14 @@
       </c>
       <c r="O45" s="17">
         <f t="shared" si="4"/>
-        <v>162268</v>
+        <v>162269</v>
       </c>
       <c r="P45" s="16">
-        <v>254133</v>
+        <v>254134</v>
       </c>
       <c r="Q45" s="18">
         <f t="shared" si="5"/>
-        <v>0.90186524525703904</v>
+        <v>0.90186879404938503</v>
       </c>
       <c r="R45" s="7">
         <v>285895</v>
@@ -8675,14 +8675,14 @@
       </c>
       <c r="T45" s="17">
         <f t="shared" si="6"/>
-        <v>161919</v>
+        <v>161920</v>
       </c>
       <c r="U45" s="16">
-        <v>256511</v>
+        <v>256512</v>
       </c>
       <c r="V45" s="18">
         <f t="shared" si="7"/>
-        <v>0.89722100771262181</v>
+        <v>0.89722450550027111</v>
       </c>
       <c r="W45" s="7">
         <v>289101</v>
@@ -8692,14 +8692,14 @@
       </c>
       <c r="Y45" s="17">
         <f t="shared" si="8"/>
-        <v>106876</v>
+        <v>106877</v>
       </c>
       <c r="Z45" s="16">
-        <v>258049</v>
+        <v>258050</v>
       </c>
       <c r="AA45" s="18">
         <f t="shared" si="9"/>
-        <v>0.89259117055976978</v>
+        <v>0.89259462955852797</v>
       </c>
       <c r="AB45" s="28">
         <v>291802</v>
@@ -8709,14 +8709,14 @@
       </c>
       <c r="AD45" s="17">
         <f t="shared" si="10"/>
-        <v>82913</v>
+        <v>82914</v>
       </c>
       <c r="AE45" s="40">
-        <v>259334</v>
+        <v>259335</v>
       </c>
       <c r="AF45" s="18">
         <f t="shared" si="11"/>
-        <v>0.88873277085146773</v>
+        <v>0.88873619783277702</v>
       </c>
       <c r="AG45" s="16">
         <v>295238</v>
@@ -8726,14 +8726,14 @@
       </c>
       <c r="AI45" s="17">
         <f t="shared" si="12"/>
-        <v>74364</v>
+        <v>74365</v>
       </c>
       <c r="AJ45" s="16">
-        <v>261947</v>
+        <v>261948</v>
       </c>
       <c r="AK45" s="18">
         <f t="shared" si="13"/>
-        <v>0.88724012491616933</v>
+        <v>0.88724351201403617</v>
       </c>
       <c r="AL45" s="30">
         <v>296582</v>
@@ -8743,14 +8743,14 @@
       </c>
       <c r="AN45" s="17">
         <f t="shared" si="14"/>
-        <v>68835</v>
+        <v>68836</v>
       </c>
       <c r="AO45" s="16">
-        <v>264665</v>
+        <v>264666</v>
       </c>
       <c r="AP45" s="18">
         <f t="shared" si="15"/>
-        <v>0.89238389383037409</v>
+        <v>0.89238726557916526</v>
       </c>
       <c r="AQ45" s="32">
         <v>297340</v>
@@ -8760,14 +8760,14 @@
       </c>
       <c r="AS45" s="17">
         <f t="shared" si="16"/>
-        <v>61444</v>
+        <v>61445</v>
       </c>
       <c r="AT45" s="16">
-        <v>267850</v>
+        <v>267851</v>
       </c>
       <c r="AU45" s="18">
         <f t="shared" si="17"/>
-        <v>0.9008206094033766</v>
+        <v>0.90082397255666913</v>
       </c>
       <c r="AV45" s="34">
         <v>215259</v>
@@ -8777,14 +8777,14 @@
       </c>
       <c r="AX45" s="17">
         <f t="shared" si="18"/>
-        <v>55041</v>
+        <v>55042</v>
       </c>
       <c r="AY45" s="19">
-        <v>190305</v>
+        <v>190306</v>
       </c>
       <c r="AZ45" s="18">
         <f t="shared" si="19"/>
-        <v>0.8840745334689839</v>
+        <v>0.88407917903548749</v>
       </c>
       <c r="BA45" s="36">
         <v>211045</v>
@@ -8794,14 +8794,14 @@
       </c>
       <c r="BC45" s="17">
         <f t="shared" si="20"/>
-        <v>49613</v>
+        <v>49614</v>
       </c>
       <c r="BD45" s="38">
-        <v>192714</v>
+        <v>192715</v>
       </c>
       <c r="BE45" s="18">
         <f t="shared" si="21"/>
-        <v>0.91314174702077755</v>
+        <v>0.91314648534672704</v>
       </c>
       <c r="BF45" s="9">
         <v>290704</v>
@@ -8811,14 +8811,14 @@
       </c>
       <c r="BH45" s="17">
         <f t="shared" si="22"/>
-        <v>88681</v>
+        <v>88682</v>
       </c>
       <c r="BI45" s="19">
-        <v>272421</v>
+        <v>272422</v>
       </c>
       <c r="BJ45" s="18">
         <f t="shared" si="23"/>
-        <v>0.93710784853321594</v>
+        <v>0.93711128845836311</v>
       </c>
       <c r="BK45" s="2"/>
       <c r="BL45" s="2"/>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="E46" s="17">
         <f t="shared" si="0"/>
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="F46" s="16">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G46" s="18">
         <f t="shared" si="1"/>
-        <v>1.0269790557330494</v>
+        <v>1.0273340433084841</v>
       </c>
       <c r="H46" s="7">
         <v>3040</v>
@@ -8855,14 +8855,14 @@
       </c>
       <c r="J46" s="17">
         <f t="shared" si="2"/>
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="K46" s="16">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="L46" s="18">
         <f t="shared" si="3"/>
-        <v>0.95888157894736847</v>
+        <v>0.95921052631578951</v>
       </c>
       <c r="M46" s="7">
         <v>3108</v>
@@ -8872,14 +8872,14 @@
       </c>
       <c r="O46" s="17">
         <f t="shared" si="4"/>
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="P46" s="16">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="Q46" s="18">
         <f t="shared" si="5"/>
-        <v>0.95141570141570142</v>
+        <v>0.95173745173745172</v>
       </c>
       <c r="R46" s="7">
         <v>3245</v>
@@ -8923,14 +8923,14 @@
       </c>
       <c r="AD46" s="17">
         <f t="shared" si="10"/>
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="AE46" s="40">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="AF46" s="18">
         <f t="shared" si="11"/>
-        <v>0.94940306992609436</v>
+        <v>0.94968732234223996</v>
       </c>
       <c r="AG46" s="16">
         <v>3623</v>
@@ -8940,14 +8940,14 @@
       </c>
       <c r="AI46" s="17">
         <f t="shared" si="12"/>
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="AJ46" s="16">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="AK46" s="18">
         <f t="shared" si="13"/>
-        <v>0.94948937344741924</v>
+        <v>0.94976538780016562</v>
       </c>
       <c r="AL46" s="30">
         <v>3714</v>
@@ -8957,14 +8957,14 @@
       </c>
       <c r="AN46" s="17">
         <f t="shared" si="14"/>
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="AO46" s="16">
-        <v>3529</v>
+        <v>3530</v>
       </c>
       <c r="AP46" s="18">
         <f t="shared" si="15"/>
-        <v>0.95018847603661816</v>
+        <v>0.95045772751750135</v>
       </c>
       <c r="AQ46" s="32">
         <v>3842</v>
@@ -9252,10 +9252,10 @@
       <c r="BL47" s="2"/>
     </row>
     <row r="48" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A48" s="52" t="s">
+      <c r="A48" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="52"/>
+      <c r="B48" s="49"/>
       <c r="C48" s="27">
         <f>SUM(C10:C47)</f>
         <v>10414263</v>
@@ -9266,15 +9266,15 @@
       </c>
       <c r="E48" s="24">
         <f>F48-D48</f>
-        <v>8669593</v>
+        <v>8669671</v>
       </c>
       <c r="F48" s="25">
         <f>SUM(F10:F47)</f>
-        <v>9532762</v>
+        <v>9532840</v>
       </c>
       <c r="G48" s="26">
         <f>F48/C48</f>
-        <v>0.9153563723136241</v>
+        <v>0.91536386204189391</v>
       </c>
       <c r="H48" s="27">
         <f>SUM(H10:H47)</f>
@@ -9286,15 +9286,15 @@
       </c>
       <c r="J48" s="24">
         <f t="shared" si="2"/>
-        <v>7138686</v>
+        <v>7138757</v>
       </c>
       <c r="K48" s="25">
         <f>SUM(K10:K47)</f>
-        <v>9536198</v>
+        <v>9536269</v>
       </c>
       <c r="L48" s="26">
         <f t="shared" si="3"/>
-        <v>0.92201229646488725</v>
+        <v>0.92201916113706039</v>
       </c>
       <c r="M48" s="27">
         <f>SUM(M10:M47)</f>
@@ -9306,15 +9306,15 @@
       </c>
       <c r="O48" s="24">
         <f t="shared" si="4"/>
-        <v>6148730</v>
+        <v>6148798</v>
       </c>
       <c r="P48" s="25">
         <f>SUM(P10:P47)</f>
-        <v>9600011</v>
+        <v>9600079</v>
       </c>
       <c r="Q48" s="26">
         <f t="shared" si="5"/>
-        <v>0.92324673962038639</v>
+        <v>0.92325327927729872</v>
       </c>
       <c r="R48" s="27">
         <f>SUM(R10:R47)</f>
@@ -9326,15 +9326,15 @@
       </c>
       <c r="T48" s="24">
         <f t="shared" si="6"/>
-        <v>5910992</v>
+        <v>5911066</v>
       </c>
       <c r="U48" s="25">
         <f>SUM(U10:U47)</f>
-        <v>9713540</v>
+        <v>9713614</v>
       </c>
       <c r="V48" s="26">
         <f t="shared" si="7"/>
-        <v>0.91932089689612762</v>
+        <v>0.91932790049588331</v>
       </c>
       <c r="W48" s="27">
         <f>SUM(W10:W47)</f>
@@ -9346,15 +9346,15 @@
       </c>
       <c r="Y48" s="24">
         <f t="shared" si="8"/>
-        <v>4169124</v>
+        <v>4169201</v>
       </c>
       <c r="Z48" s="25">
         <f>SUM(Z10:Z47)</f>
-        <v>9814725</v>
+        <v>9814802</v>
       </c>
       <c r="AA48" s="26">
         <f t="shared" si="9"/>
-        <v>0.91688201308277351</v>
+        <v>0.91688920634748627</v>
       </c>
       <c r="AB48" s="27">
         <f>SUM(AB10:AB47)</f>
@@ -9366,15 +9366,15 @@
       </c>
       <c r="AD48" s="24">
         <f t="shared" si="10"/>
-        <v>2784051</v>
+        <v>2784132</v>
       </c>
       <c r="AE48" s="25">
         <f>SUM(AE10:AE47)</f>
-        <v>9901847</v>
+        <v>9901928</v>
       </c>
       <c r="AF48" s="26">
         <f t="shared" si="11"/>
-        <v>0.91252801813951623</v>
+        <v>0.91253548288518138</v>
       </c>
       <c r="AG48" s="23">
         <f>SUM(AG10:AG47)</f>
@@ -9386,15 +9386,15 @@
       </c>
       <c r="AI48" s="24">
         <f t="shared" si="12"/>
-        <v>2740548</v>
+        <v>2740639</v>
       </c>
       <c r="AJ48" s="25">
         <f>SUM(AJ10:AJ47)</f>
-        <v>10005518</v>
+        <v>10005609</v>
       </c>
       <c r="AK48" s="26">
         <f t="shared" si="13"/>
-        <v>0.9119327306473376</v>
+        <v>0.91194102465855109</v>
       </c>
       <c r="AL48" s="27">
         <f>SUM(AL10:AL47)</f>
@@ -9406,15 +9406,15 @@
       </c>
       <c r="AN48" s="24">
         <f t="shared" si="14"/>
-        <v>2318026</v>
+        <v>2318113</v>
       </c>
       <c r="AO48" s="25">
         <f>SUM(AO10:AO47)</f>
-        <v>10099787</v>
+        <v>10099874</v>
       </c>
       <c r="AP48" s="26">
         <f t="shared" si="15"/>
-        <v>0.91728119748227344</v>
+        <v>0.91728909898199618</v>
       </c>
       <c r="AQ48" s="27">
         <f>SUM(AQ10:AQ47)</f>
@@ -9426,15 +9426,15 @@
       </c>
       <c r="AS48" s="24">
         <f t="shared" si="16"/>
-        <v>1958602</v>
+        <v>1958683</v>
       </c>
       <c r="AT48" s="25">
         <f>SUM(AT10:AT47)</f>
-        <v>10194047</v>
+        <v>10194128</v>
       </c>
       <c r="AU48" s="26">
         <f t="shared" si="17"/>
-        <v>0.92806340080409944</v>
+        <v>0.92807077502313773</v>
       </c>
       <c r="AV48" s="27">
         <f>SUM(AV10:AV47)</f>
@@ -9446,15 +9446,15 @@
       </c>
       <c r="AX48" s="24">
         <f t="shared" si="18"/>
-        <v>1826706</v>
+        <v>1826787</v>
       </c>
       <c r="AY48" s="25">
         <f>SUM(AY10:AY47)</f>
-        <v>5622605</v>
+        <v>5622686</v>
       </c>
       <c r="AZ48" s="26">
         <f t="shared" si="19"/>
-        <v>0.8980702511818448</v>
+        <v>0.89808318890205552</v>
       </c>
       <c r="BA48" s="27">
         <f>SUM(BA10:BA47)</f>
@@ -9466,15 +9466,15 @@
       </c>
       <c r="BC48" s="24">
         <f t="shared" si="20"/>
-        <v>1571051</v>
+        <v>1571128</v>
       </c>
       <c r="BD48" s="25">
         <f>SUM(BD10:BD47)</f>
-        <v>5731923</v>
+        <v>5732000</v>
       </c>
       <c r="BE48" s="26">
         <f t="shared" si="21"/>
-        <v>0.93466792182144631</v>
+        <v>0.93468047771760554</v>
       </c>
       <c r="BF48" s="27">
         <f>SUM(BF10:BF47)</f>
@@ -9486,15 +9486,15 @@
       </c>
       <c r="BH48" s="24">
         <f t="shared" si="22"/>
-        <v>3236073</v>
+        <v>3236160</v>
       </c>
       <c r="BI48" s="25">
         <f>SUM(BI10:BI47)</f>
-        <v>10407997</v>
+        <v>10408084</v>
       </c>
       <c r="BJ48" s="26">
         <f t="shared" si="23"/>
-        <v>0.96552872221495023</v>
+        <v>0.96553679302807915</v>
       </c>
       <c r="BK48" s="10"/>
       <c r="BL48" s="10"/>
@@ -9504,17 +9504,25 @@
       <c r="AM57" s="4"/>
     </row>
     <row r="58" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A58" s="51" t="s">
+      <c r="A58" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
+      <c r="B58" s="46"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
       <c r="F58" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="BF8:BJ8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:L8"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9526,14 +9534,6 @@
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="BF8:BJ8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2020-2021.xlsx
+++ b/gstdatabase/GSTR-3B-2020-2021.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BECF9AD-D711-4F8C-829B-95DC2B261897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF21157-2E2A-40A5-8AC3-B87159334DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,10 +188,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -487,8 +487,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -496,17 +496,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -807,13 +807,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
     </row>
     <row r="2" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -823,10 +823,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="51"/>
+      <c r="B3" s="49"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -853,14 +853,14 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
     </row>
     <row r="8" spans="1:64" s="42" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="50" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="48" t="s">
@@ -952,7 +952,7 @@
       <c r="BJ8" s="48"/>
     </row>
     <row r="9" spans="1:64" s="42" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="52"/>
+      <c r="A9" s="50"/>
       <c r="B9" s="48"/>
       <c r="C9" s="41" t="s">
         <v>3</v>
@@ -1364,14 +1364,14 @@
       </c>
       <c r="E11" s="17">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>72575</v>
+        <v>72576</v>
       </c>
       <c r="F11" s="16">
-        <v>80931</v>
+        <v>80932</v>
       </c>
       <c r="G11" s="18">
         <f t="shared" ref="G11:G47" si="1">F11/C11</f>
-        <v>0.94215366705471482</v>
+        <v>0.94216530849825375</v>
       </c>
       <c r="H11" s="7">
         <v>85444</v>
@@ -1381,14 +1381,14 @@
       </c>
       <c r="J11" s="17">
         <f t="shared" ref="J11:J48" si="2">K11-I11</f>
-        <v>57589</v>
+        <v>57590</v>
       </c>
       <c r="K11" s="16">
-        <v>80943</v>
+        <v>80944</v>
       </c>
       <c r="L11" s="18">
         <f t="shared" ref="L11:L48" si="3">K11/H11</f>
-        <v>0.94732222274238098</v>
+        <v>0.94733392631431113</v>
       </c>
       <c r="M11" s="7">
         <v>85305</v>
@@ -1398,14 +1398,14 @@
       </c>
       <c r="O11" s="17">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>47919</v>
+        <v>47920</v>
       </c>
       <c r="P11" s="16">
-        <v>81596</v>
+        <v>81597</v>
       </c>
       <c r="Q11" s="18">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.95652071977023623</v>
+        <v>0.95653244241251978</v>
       </c>
       <c r="R11" s="7">
         <v>86772</v>
@@ -1415,14 +1415,14 @@
       </c>
       <c r="T11" s="17">
         <f t="shared" ref="T11:T48" si="6">U11-S11</f>
-        <v>47606</v>
+        <v>47607</v>
       </c>
       <c r="U11" s="16">
-        <v>82629</v>
+        <v>82630</v>
       </c>
       <c r="V11" s="18">
         <f t="shared" ref="V11:V48" si="7">U11/R11</f>
-        <v>0.95225418337712631</v>
+        <v>0.95226570783201958</v>
       </c>
       <c r="W11" s="7">
         <v>88104</v>
@@ -1432,14 +1432,14 @@
       </c>
       <c r="Y11" s="17">
         <f t="shared" ref="Y11:Y48" si="8">Z11-X11</f>
-        <v>31752</v>
+        <v>31753</v>
       </c>
       <c r="Z11" s="16">
-        <v>83658</v>
+        <v>83659</v>
       </c>
       <c r="AA11" s="18">
         <f t="shared" ref="AA11:AA48" si="9">Z11/W11</f>
-        <v>0.94953691092345405</v>
+        <v>0.9495482611459185</v>
       </c>
       <c r="AB11" s="28">
         <v>89380</v>
@@ -1449,14 +1449,14 @@
       </c>
       <c r="AD11" s="17">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>19521</v>
+        <v>19522</v>
       </c>
       <c r="AE11" s="40">
-        <v>84510</v>
+        <v>84511</v>
       </c>
       <c r="AF11" s="18">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.94551353770418434</v>
+        <v>0.94552472588946068</v>
       </c>
       <c r="AG11" s="16">
         <v>90577</v>
@@ -1466,14 +1466,14 @@
       </c>
       <c r="AI11" s="17">
         <f t="shared" ref="AI11:AI48" si="12">AJ11-AH11</f>
-        <v>18514</v>
+        <v>18515</v>
       </c>
       <c r="AJ11" s="16">
-        <v>85430</v>
+        <v>85431</v>
       </c>
       <c r="AK11" s="18">
         <f t="shared" ref="AK11:AK48" si="13">AJ11/AG11</f>
-        <v>0.94317541980856068</v>
+        <v>0.94318646013888741</v>
       </c>
       <c r="AL11" s="30">
         <v>90998</v>
@@ -2040,14 +2040,14 @@
       </c>
       <c r="O14" s="17">
         <f t="shared" si="4"/>
-        <v>74185</v>
+        <v>74186</v>
       </c>
       <c r="P14" s="16">
-        <v>121109</v>
+        <v>121110</v>
       </c>
       <c r="Q14" s="18">
         <f t="shared" si="5"/>
-        <v>0.93094171092987321</v>
+        <v>0.93094939773854091</v>
       </c>
       <c r="R14" s="7">
         <v>132671</v>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="Y14" s="17">
         <f t="shared" si="8"/>
-        <v>51643</v>
+        <v>51644</v>
       </c>
       <c r="Z14" s="16">
-        <v>124872</v>
+        <v>124873</v>
       </c>
       <c r="AA14" s="18">
         <f t="shared" si="9"/>
-        <v>0.92270859811426709</v>
+        <v>0.92271598734962901</v>
       </c>
       <c r="AB14" s="28">
         <v>138271</v>
@@ -2091,14 +2091,14 @@
       </c>
       <c r="AD14" s="17">
         <f t="shared" si="10"/>
-        <v>33732</v>
+        <v>33733</v>
       </c>
       <c r="AE14" s="40">
-        <v>126353</v>
+        <v>126354</v>
       </c>
       <c r="AF14" s="18">
         <f t="shared" si="11"/>
-        <v>0.91380694433395293</v>
+        <v>0.91381417650845076</v>
       </c>
       <c r="AG14" s="16">
         <v>140605</v>
@@ -2108,14 +2108,14 @@
       </c>
       <c r="AI14" s="17">
         <f t="shared" si="12"/>
-        <v>33107</v>
+        <v>33108</v>
       </c>
       <c r="AJ14" s="16">
-        <v>128346</v>
+        <v>128347</v>
       </c>
       <c r="AK14" s="18">
         <f t="shared" si="13"/>
-        <v>0.91281248888730837</v>
+        <v>0.91281960100992143</v>
       </c>
       <c r="AL14" s="30">
         <v>141075</v>
@@ -2125,14 +2125,14 @@
       </c>
       <c r="AN14" s="17">
         <f t="shared" si="14"/>
-        <v>27276</v>
+        <v>27277</v>
       </c>
       <c r="AO14" s="16">
-        <v>129920</v>
+        <v>129921</v>
       </c>
       <c r="AP14" s="18">
         <f t="shared" si="15"/>
-        <v>0.92092858408647882</v>
+        <v>0.92093567251461983</v>
       </c>
       <c r="AQ14" s="32">
         <v>140248</v>
@@ -2142,14 +2142,14 @@
       </c>
       <c r="AS14" s="17">
         <f t="shared" si="16"/>
-        <v>25063</v>
+        <v>25064</v>
       </c>
       <c r="AT14" s="16">
-        <v>131361</v>
+        <v>131362</v>
       </c>
       <c r="AU14" s="18">
         <f t="shared" si="17"/>
-        <v>0.93663367748559689</v>
+        <v>0.93664080771205294</v>
       </c>
       <c r="AV14" s="34">
         <v>71169</v>
@@ -2159,14 +2159,14 @@
       </c>
       <c r="AX14" s="17">
         <f t="shared" si="18"/>
-        <v>24130</v>
+        <v>24132</v>
       </c>
       <c r="AY14" s="19">
-        <v>63724</v>
+        <v>63726</v>
       </c>
       <c r="AZ14" s="18">
         <f t="shared" si="19"/>
-        <v>0.89538984670291843</v>
+        <v>0.89541794882603376</v>
       </c>
       <c r="BA14" s="36">
         <v>69125</v>
@@ -2176,14 +2176,14 @@
       </c>
       <c r="BC14" s="17">
         <f t="shared" si="20"/>
-        <v>20953</v>
+        <v>20954</v>
       </c>
       <c r="BD14" s="38">
-        <v>65361</v>
+        <v>65362</v>
       </c>
       <c r="BE14" s="18">
         <f t="shared" si="21"/>
-        <v>0.94554792043399638</v>
+        <v>0.94556238698010853</v>
       </c>
       <c r="BF14" s="9">
         <v>138667</v>
@@ -2193,14 +2193,14 @@
       </c>
       <c r="BH14" s="17">
         <f t="shared" si="22"/>
-        <v>41160</v>
+        <v>41161</v>
       </c>
       <c r="BI14" s="19">
-        <v>134843</v>
+        <v>134844</v>
       </c>
       <c r="BJ14" s="18">
         <f t="shared" si="23"/>
-        <v>0.97242314321359802</v>
+        <v>0.97243035473472417</v>
       </c>
       <c r="BK14" s="2"/>
       <c r="BL14" s="2"/>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="E18" s="17">
         <f t="shared" si="0"/>
-        <v>955301</v>
+        <v>955304</v>
       </c>
       <c r="F18" s="16">
-        <v>1052002</v>
+        <v>1052005</v>
       </c>
       <c r="G18" s="18">
         <f t="shared" si="1"/>
-        <v>0.91303053525879418</v>
+        <v>0.91303313895308924</v>
       </c>
       <c r="H18" s="7">
         <v>1134246</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="J18" s="17">
         <f t="shared" si="2"/>
-        <v>754305</v>
+        <v>754308</v>
       </c>
       <c r="K18" s="16">
-        <v>1050548</v>
+        <v>1050551</v>
       </c>
       <c r="L18" s="18">
         <f t="shared" si="3"/>
-        <v>0.92620824759355558</v>
+        <v>0.92621089252243338</v>
       </c>
       <c r="M18" s="7">
         <v>1134575</v>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="O18" s="17">
         <f t="shared" si="4"/>
-        <v>647213</v>
+        <v>647216</v>
       </c>
       <c r="P18" s="16">
-        <v>1055868</v>
+        <v>1055871</v>
       </c>
       <c r="Q18" s="18">
         <f t="shared" si="5"/>
-        <v>0.93062864949430402</v>
+        <v>0.93063129365621489</v>
       </c>
       <c r="R18" s="7">
         <v>1163634</v>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="T18" s="17">
         <f t="shared" si="6"/>
-        <v>637396</v>
+        <v>637399</v>
       </c>
       <c r="U18" s="16">
-        <v>1078357</v>
+        <v>1078360</v>
       </c>
       <c r="V18" s="18">
         <f t="shared" si="7"/>
-        <v>0.92671492926470012</v>
+        <v>0.92671750739493686</v>
       </c>
       <c r="W18" s="7">
         <v>1186115</v>
@@ -2930,14 +2930,14 @@
       </c>
       <c r="Y18" s="17">
         <f t="shared" si="8"/>
-        <v>412863</v>
+        <v>412866</v>
       </c>
       <c r="Z18" s="16">
-        <v>1094120</v>
+        <v>1094123</v>
       </c>
       <c r="AA18" s="18">
         <f t="shared" si="9"/>
-        <v>0.92244006694123248</v>
+        <v>0.92244259620694447</v>
       </c>
       <c r="AB18" s="28">
         <v>1210642</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="AD18" s="17">
         <f t="shared" si="10"/>
-        <v>256981</v>
+        <v>256984</v>
       </c>
       <c r="AE18" s="40">
-        <v>1109549</v>
+        <v>1109552</v>
       </c>
       <c r="AF18" s="18">
         <f t="shared" si="11"/>
-        <v>0.91649637134677309</v>
+        <v>0.9164988493708297</v>
       </c>
       <c r="AG18" s="16">
         <v>1230797</v>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="AI18" s="17">
         <f t="shared" si="12"/>
-        <v>255666</v>
+        <v>255670</v>
       </c>
       <c r="AJ18" s="16">
-        <v>1126519</v>
+        <v>1126523</v>
       </c>
       <c r="AK18" s="18">
         <f t="shared" si="13"/>
-        <v>0.91527603658442458</v>
+        <v>0.91527928651109813</v>
       </c>
       <c r="AL18" s="30">
         <v>1235793</v>
@@ -2981,14 +2981,14 @@
       </c>
       <c r="AN18" s="17">
         <f t="shared" si="14"/>
-        <v>215681</v>
+        <v>215685</v>
       </c>
       <c r="AO18" s="16">
-        <v>1138628</v>
+        <v>1138632</v>
       </c>
       <c r="AP18" s="18">
         <f t="shared" si="15"/>
-        <v>0.92137437256886878</v>
+        <v>0.92137760935690682</v>
       </c>
       <c r="AQ18" s="32">
         <v>1231355</v>
@@ -2998,14 +2998,14 @@
       </c>
       <c r="AS18" s="17">
         <f t="shared" si="16"/>
-        <v>183795</v>
+        <v>183799</v>
       </c>
       <c r="AT18" s="16">
-        <v>1149649</v>
+        <v>1149653</v>
       </c>
       <c r="AU18" s="18">
         <f t="shared" si="17"/>
-        <v>0.93364545561596779</v>
+        <v>0.93364870406990674</v>
       </c>
       <c r="AV18" s="34">
         <v>676084</v>
@@ -3015,14 +3015,14 @@
       </c>
       <c r="AX18" s="17">
         <f t="shared" si="18"/>
-        <v>184443</v>
+        <v>184448</v>
       </c>
       <c r="AY18" s="19">
-        <v>606975</v>
+        <v>606980</v>
       </c>
       <c r="AZ18" s="18">
         <f t="shared" si="19"/>
-        <v>0.89778045331645184</v>
+        <v>0.89778784884718466</v>
       </c>
       <c r="BA18" s="36">
         <v>651597</v>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="BC18" s="17">
         <f t="shared" si="20"/>
-        <v>154171</v>
+        <v>154175</v>
       </c>
       <c r="BD18" s="38">
-        <v>620512</v>
+        <v>620516</v>
       </c>
       <c r="BE18" s="18">
         <f t="shared" si="21"/>
-        <v>0.95229413272314023</v>
+        <v>0.95230027148682395</v>
       </c>
       <c r="BF18" s="9">
         <v>1203078</v>
@@ -3049,14 +3049,14 @@
       </c>
       <c r="BH18" s="17">
         <f t="shared" si="22"/>
-        <v>356595</v>
+        <v>356598</v>
       </c>
       <c r="BI18" s="19">
-        <v>1175743</v>
+        <v>1175746</v>
       </c>
       <c r="BJ18" s="18">
         <f t="shared" si="23"/>
-        <v>0.97727911241000165</v>
+        <v>0.97728160601390768</v>
       </c>
       <c r="BK18" s="2"/>
       <c r="BL18" s="2"/>
@@ -3127,14 +3127,14 @@
       </c>
       <c r="T19" s="17">
         <f t="shared" si="6"/>
-        <v>220415</v>
+        <v>220416</v>
       </c>
       <c r="U19" s="16">
-        <v>305007</v>
+        <v>305008</v>
       </c>
       <c r="V19" s="18">
         <f t="shared" si="7"/>
-        <v>0.90667954815695595</v>
+        <v>0.90668252080856127</v>
       </c>
       <c r="W19" s="7">
         <v>343478</v>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="Y19" s="17">
         <f t="shared" si="8"/>
-        <v>151051</v>
+        <v>151053</v>
       </c>
       <c r="Z19" s="16">
-        <v>309569</v>
+        <v>309571</v>
       </c>
       <c r="AA19" s="18">
         <f t="shared" si="9"/>
-        <v>0.90127751995761007</v>
+        <v>0.90128334274684263</v>
       </c>
       <c r="AB19" s="28">
         <v>355383</v>
@@ -3161,14 +3161,14 @@
       </c>
       <c r="AD19" s="17">
         <f t="shared" si="10"/>
-        <v>93727</v>
+        <v>93728</v>
       </c>
       <c r="AE19" s="40">
-        <v>315648</v>
+        <v>315649</v>
       </c>
       <c r="AF19" s="18">
         <f t="shared" si="11"/>
-        <v>0.88819105021905942</v>
+        <v>0.88819386408466361</v>
       </c>
       <c r="AG19" s="16">
         <v>365633</v>
@@ -3178,14 +3178,14 @@
       </c>
       <c r="AI19" s="17">
         <f t="shared" si="12"/>
-        <v>109287</v>
+        <v>109289</v>
       </c>
       <c r="AJ19" s="16">
-        <v>321344</v>
+        <v>321346</v>
       </c>
       <c r="AK19" s="18">
         <f t="shared" si="13"/>
-        <v>0.87887034266600661</v>
+        <v>0.87887581263179204</v>
       </c>
       <c r="AL19" s="30">
         <v>370137</v>
@@ -3229,14 +3229,14 @@
       </c>
       <c r="AX19" s="17">
         <f t="shared" si="18"/>
-        <v>71735</v>
+        <v>71736</v>
       </c>
       <c r="AY19" s="19">
-        <v>180727</v>
+        <v>180728</v>
       </c>
       <c r="AZ19" s="18">
         <f t="shared" si="19"/>
-        <v>0.81024604128185351</v>
+        <v>0.81025052454136259</v>
       </c>
       <c r="BA19" s="36">
         <v>218640</v>
@@ -3246,14 +3246,14 @@
       </c>
       <c r="BC19" s="17">
         <f t="shared" si="20"/>
-        <v>58334</v>
+        <v>58335</v>
       </c>
       <c r="BD19" s="38">
-        <v>187541</v>
+        <v>187542</v>
       </c>
       <c r="BE19" s="18">
         <f t="shared" si="21"/>
-        <v>0.85776161727039879</v>
+        <v>0.85776619099890228</v>
       </c>
       <c r="BF19" s="9">
         <v>376756</v>
@@ -3263,14 +3263,14 @@
       </c>
       <c r="BH19" s="17">
         <f t="shared" si="22"/>
-        <v>121134</v>
+        <v>121136</v>
       </c>
       <c r="BI19" s="19">
-        <v>346117</v>
+        <v>346119</v>
       </c>
       <c r="BJ19" s="18">
         <f t="shared" si="23"/>
-        <v>0.9186768093938783</v>
+        <v>0.91868211786939025</v>
       </c>
       <c r="BK19" s="2"/>
       <c r="BL19" s="2"/>
@@ -3837,14 +3837,14 @@
       </c>
       <c r="AN22" s="17">
         <f t="shared" si="14"/>
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="AO22" s="16">
-        <v>5951</v>
+        <v>5952</v>
       </c>
       <c r="AP22" s="18">
         <f t="shared" si="15"/>
-        <v>0.84435300794551649</v>
+        <v>0.8444948921679909</v>
       </c>
       <c r="AQ22" s="32">
         <v>7088</v>
@@ -3854,14 +3854,14 @@
       </c>
       <c r="AS22" s="17">
         <f t="shared" si="16"/>
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="AT22" s="16">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="AU22" s="18">
         <f t="shared" si="17"/>
-        <v>0.84777088036117376</v>
+        <v>0.84791196388261847</v>
       </c>
       <c r="AV22" s="34">
         <v>5686</v>
@@ -3871,14 +3871,14 @@
       </c>
       <c r="AX22" s="17">
         <f t="shared" si="18"/>
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="AY22" s="19">
-        <v>4656</v>
+        <v>4657</v>
       </c>
       <c r="AZ22" s="18">
         <f t="shared" si="19"/>
-        <v>0.81885332395357013</v>
+        <v>0.81902919451283851</v>
       </c>
       <c r="BA22" s="36">
         <v>5621</v>
@@ -3888,14 +3888,14 @@
       </c>
       <c r="BC22" s="17">
         <f t="shared" si="20"/>
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="BD22" s="38">
-        <v>4739</v>
+        <v>4740</v>
       </c>
       <c r="BE22" s="18">
         <f t="shared" si="21"/>
-        <v>0.84308841843088422</v>
+        <v>0.84326632271837754</v>
       </c>
       <c r="BF22" s="9">
         <v>6948</v>
@@ -3905,14 +3905,14 @@
       </c>
       <c r="BH22" s="17">
         <f t="shared" si="22"/>
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="BI22" s="19">
-        <v>6133</v>
+        <v>6134</v>
       </c>
       <c r="BJ22" s="18">
         <f t="shared" si="23"/>
-        <v>0.88270005757052394</v>
+        <v>0.88284398388025331</v>
       </c>
       <c r="BK22" s="2"/>
       <c r="BL22" s="2"/>
@@ -4231,14 +4231,14 @@
       </c>
       <c r="AD24" s="17">
         <f t="shared" si="10"/>
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="AE24" s="40">
-        <v>4973</v>
+        <v>4974</v>
       </c>
       <c r="AF24" s="18">
         <f t="shared" si="11"/>
-        <v>0.74636049827405071</v>
+        <v>0.74651058081945065</v>
       </c>
       <c r="AG24" s="16">
         <v>6801</v>
@@ -4462,14 +4462,14 @@
       </c>
       <c r="AI25" s="17">
         <f t="shared" si="12"/>
-        <v>5216</v>
+        <v>5217</v>
       </c>
       <c r="AJ25" s="16">
-        <v>22280</v>
+        <v>22281</v>
       </c>
       <c r="AK25" s="18">
         <f t="shared" si="13"/>
-        <v>0.86837899988307288</v>
+        <v>0.86841797560120049</v>
       </c>
       <c r="AL25" s="30">
         <v>25765</v>
@@ -4479,14 +4479,14 @@
       </c>
       <c r="AN25" s="17">
         <f t="shared" si="14"/>
-        <v>4889</v>
+        <v>4890</v>
       </c>
       <c r="AO25" s="16">
-        <v>22437</v>
+        <v>22438</v>
       </c>
       <c r="AP25" s="18">
         <f t="shared" si="15"/>
-        <v>0.87083252474286821</v>
+        <v>0.87087133708519304</v>
       </c>
       <c r="AQ25" s="32">
         <v>25839</v>
@@ -4496,14 +4496,14 @@
       </c>
       <c r="AS25" s="17">
         <f t="shared" si="16"/>
-        <v>4564</v>
+        <v>4565</v>
       </c>
       <c r="AT25" s="16">
-        <v>22714</v>
+        <v>22715</v>
       </c>
       <c r="AU25" s="18">
         <f t="shared" si="17"/>
-        <v>0.87905878710476415</v>
+        <v>0.87909748829289058</v>
       </c>
       <c r="AV25" s="34">
         <v>15838</v>
@@ -4513,14 +4513,14 @@
       </c>
       <c r="AX25" s="17">
         <f t="shared" si="18"/>
-        <v>4559</v>
+        <v>4560</v>
       </c>
       <c r="AY25" s="19">
-        <v>12865</v>
+        <v>12866</v>
       </c>
       <c r="AZ25" s="18">
         <f t="shared" si="19"/>
-        <v>0.81228690491223643</v>
+        <v>0.81235004419749968</v>
       </c>
       <c r="BA25" s="36">
         <v>15495</v>
@@ -4574,14 +4574,14 @@
       </c>
       <c r="E26" s="17">
         <f t="shared" si="0"/>
-        <v>16270</v>
+        <v>16271</v>
       </c>
       <c r="F26" s="16">
-        <v>20805</v>
+        <v>20806</v>
       </c>
       <c r="G26" s="18">
         <f t="shared" si="1"/>
-        <v>0.78184892897406988</v>
+        <v>0.78188650883126642</v>
       </c>
       <c r="H26" s="7">
         <v>26470</v>
@@ -4591,14 +4591,14 @@
       </c>
       <c r="J26" s="17">
         <f t="shared" si="2"/>
-        <v>12056</v>
+        <v>12057</v>
       </c>
       <c r="K26" s="16">
-        <v>20758</v>
+        <v>20759</v>
       </c>
       <c r="L26" s="18">
         <f t="shared" si="3"/>
-        <v>0.78420853796751044</v>
+        <v>0.78424631658481303</v>
       </c>
       <c r="M26" s="7">
         <v>25760</v>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="O26" s="17">
         <f t="shared" si="4"/>
-        <v>11613</v>
+        <v>11614</v>
       </c>
       <c r="P26" s="16">
-        <v>20696</v>
+        <v>20697</v>
       </c>
       <c r="Q26" s="18">
         <f t="shared" si="5"/>
-        <v>0.80341614906832293</v>
+        <v>0.8034549689440994</v>
       </c>
       <c r="R26" s="7">
         <v>25696</v>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="T26" s="17">
         <f t="shared" si="6"/>
-        <v>11885</v>
+        <v>11886</v>
       </c>
       <c r="U26" s="16">
-        <v>20951</v>
+        <v>20952</v>
       </c>
       <c r="V26" s="18">
         <f t="shared" si="7"/>
-        <v>0.81534090909090906</v>
+        <v>0.8153798256537983</v>
       </c>
       <c r="W26" s="7">
         <v>25913</v>
@@ -4642,14 +4642,14 @@
       </c>
       <c r="Y26" s="17">
         <f t="shared" si="8"/>
-        <v>7600</v>
+        <v>7601</v>
       </c>
       <c r="Z26" s="16">
-        <v>21086</v>
+        <v>21087</v>
       </c>
       <c r="AA26" s="18">
         <f t="shared" si="9"/>
-        <v>0.81372284181684873</v>
+        <v>0.81376143248562494</v>
       </c>
       <c r="AB26" s="28">
         <v>25659</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="AD26" s="17">
         <f t="shared" si="10"/>
-        <v>6303</v>
+        <v>6304</v>
       </c>
       <c r="AE26" s="40">
-        <v>21121</v>
+        <v>21122</v>
       </c>
       <c r="AF26" s="18">
         <f t="shared" si="11"/>
-        <v>0.82314197747379092</v>
+        <v>0.8231809501539421</v>
       </c>
       <c r="AG26" s="16">
         <v>26031</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="AI26" s="17">
         <f t="shared" si="12"/>
-        <v>6207</v>
+        <v>6208</v>
       </c>
       <c r="AJ26" s="16">
-        <v>21364</v>
+        <v>21365</v>
       </c>
       <c r="AK26" s="18">
         <f t="shared" si="13"/>
-        <v>0.82071376435788101</v>
+        <v>0.82075218009296613</v>
       </c>
       <c r="AL26" s="30">
         <v>26186</v>
@@ -4693,14 +4693,14 @@
       </c>
       <c r="AN26" s="17">
         <f t="shared" si="14"/>
-        <v>5712</v>
+        <v>5714</v>
       </c>
       <c r="AO26" s="16">
-        <v>21524</v>
+        <v>21526</v>
       </c>
       <c r="AP26" s="18">
         <f t="shared" si="15"/>
-        <v>0.82196593599633394</v>
+        <v>0.82204231268616823</v>
       </c>
       <c r="AQ26" s="32">
         <v>26317</v>
@@ -4710,14 +4710,14 @@
       </c>
       <c r="AS26" s="17">
         <f t="shared" si="16"/>
-        <v>5044</v>
+        <v>5045</v>
       </c>
       <c r="AT26" s="16">
-        <v>21711</v>
+        <v>21712</v>
       </c>
       <c r="AU26" s="18">
         <f t="shared" si="17"/>
-        <v>0.8249800509176578</v>
+        <v>0.8250180491697382</v>
       </c>
       <c r="AV26" s="34">
         <v>16878</v>
@@ -4727,14 +4727,14 @@
       </c>
       <c r="AX26" s="17">
         <f t="shared" si="18"/>
-        <v>4825</v>
+        <v>4826</v>
       </c>
       <c r="AY26" s="19">
-        <v>12421</v>
+        <v>12422</v>
       </c>
       <c r="AZ26" s="18">
         <f t="shared" si="19"/>
-        <v>0.73592842753880794</v>
+        <v>0.73598767626496031</v>
       </c>
       <c r="BA26" s="36">
         <v>16504</v>
@@ -4744,14 +4744,14 @@
       </c>
       <c r="BC26" s="17">
         <f t="shared" si="20"/>
-        <v>4227</v>
+        <v>4228</v>
       </c>
       <c r="BD26" s="38">
-        <v>12481</v>
+        <v>12482</v>
       </c>
       <c r="BE26" s="18">
         <f t="shared" si="21"/>
-        <v>0.75624091129423165</v>
+        <v>0.75630150266602036</v>
       </c>
       <c r="BF26" s="9">
         <v>25358</v>
@@ -4761,14 +4761,14 @@
       </c>
       <c r="BH26" s="17">
         <f t="shared" si="22"/>
-        <v>6169</v>
+        <v>6170</v>
       </c>
       <c r="BI26" s="19">
-        <v>21811</v>
+        <v>21812</v>
       </c>
       <c r="BJ26" s="18">
         <f t="shared" si="23"/>
-        <v>0.86012303809448698</v>
+        <v>0.86016247338118146</v>
       </c>
       <c r="BK26" s="2"/>
       <c r="BL26" s="2"/>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="E27" s="17">
         <f t="shared" si="0"/>
-        <v>115192</v>
+        <v>115193</v>
       </c>
       <c r="F27" s="16">
-        <v>129450</v>
+        <v>129451</v>
       </c>
       <c r="G27" s="18">
         <f t="shared" si="1"/>
-        <v>0.8885853337085825</v>
+        <v>0.88859219802170497</v>
       </c>
       <c r="H27" s="7">
         <v>145010</v>
@@ -4805,14 +4805,14 @@
       </c>
       <c r="J27" s="17">
         <f t="shared" si="2"/>
-        <v>98112</v>
+        <v>98113</v>
       </c>
       <c r="K27" s="16">
-        <v>129424</v>
+        <v>129425</v>
       </c>
       <c r="L27" s="18">
         <f t="shared" si="3"/>
-        <v>0.89251775739604167</v>
+        <v>0.89252465347217436</v>
       </c>
       <c r="M27" s="7">
         <v>146684</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="O27" s="17">
         <f t="shared" si="4"/>
-        <v>98017</v>
+        <v>98018</v>
       </c>
       <c r="P27" s="16">
-        <v>130613</v>
+        <v>130614</v>
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="5"/>
-        <v>0.89043794824248046</v>
+        <v>0.89044476561860875</v>
       </c>
       <c r="R27" s="7">
         <v>151002</v>
@@ -4839,14 +4839,14 @@
       </c>
       <c r="T27" s="17">
         <f t="shared" si="6"/>
-        <v>96120</v>
+        <v>96122</v>
       </c>
       <c r="U27" s="16">
-        <v>133161</v>
+        <v>133163</v>
       </c>
       <c r="V27" s="18">
         <f t="shared" si="7"/>
-        <v>0.88184924702984069</v>
+        <v>0.88186249188752464</v>
       </c>
       <c r="W27" s="7">
         <v>153079</v>
@@ -4856,14 +4856,14 @@
       </c>
       <c r="Y27" s="17">
         <f t="shared" si="8"/>
-        <v>73993</v>
+        <v>73995</v>
       </c>
       <c r="Z27" s="16">
-        <v>135046</v>
+        <v>135048</v>
       </c>
       <c r="AA27" s="18">
         <f t="shared" si="9"/>
-        <v>0.88219808072955797</v>
+        <v>0.88221114587892524</v>
       </c>
       <c r="AB27" s="28">
         <v>156081</v>
@@ -4873,14 +4873,14 @@
       </c>
       <c r="AD27" s="17">
         <f t="shared" si="10"/>
-        <v>52681</v>
+        <v>52683</v>
       </c>
       <c r="AE27" s="40">
-        <v>135656</v>
+        <v>135658</v>
       </c>
       <c r="AF27" s="18">
         <f t="shared" si="11"/>
-        <v>0.86913846015850749</v>
+        <v>0.86915127401797787</v>
       </c>
       <c r="AG27" s="16">
         <v>159400</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="AI27" s="17">
         <f t="shared" si="12"/>
-        <v>49916</v>
+        <v>49918</v>
       </c>
       <c r="AJ27" s="16">
-        <v>137427</v>
+        <v>137429</v>
       </c>
       <c r="AK27" s="18">
         <f t="shared" si="13"/>
-        <v>0.86215181932245921</v>
+        <v>0.86216436637390215</v>
       </c>
       <c r="AL27" s="30">
         <v>161009</v>
@@ -4907,14 +4907,14 @@
       </c>
       <c r="AN27" s="17">
         <f t="shared" si="14"/>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="AO27" s="16">
-        <v>138964</v>
+        <v>138966</v>
       </c>
       <c r="AP27" s="18">
         <f t="shared" si="15"/>
-        <v>0.86308218795222624</v>
+        <v>0.86309460961809592</v>
       </c>
       <c r="AQ27" s="32">
         <v>161396</v>
@@ -4924,14 +4924,14 @@
       </c>
       <c r="AS27" s="17">
         <f t="shared" si="16"/>
-        <v>42499</v>
+        <v>42501</v>
       </c>
       <c r="AT27" s="16">
-        <v>140873</v>
+        <v>140875</v>
       </c>
       <c r="AU27" s="18">
         <f t="shared" si="17"/>
-        <v>0.87284071476368685</v>
+        <v>0.87285310664452653</v>
       </c>
       <c r="AV27" s="34">
         <v>108346</v>
@@ -4941,14 +4941,14 @@
       </c>
       <c r="AX27" s="17">
         <f t="shared" si="18"/>
-        <v>41825</v>
+        <v>41827</v>
       </c>
       <c r="AY27" s="19">
-        <v>89126</v>
+        <v>89128</v>
       </c>
       <c r="AZ27" s="18">
         <f t="shared" si="19"/>
-        <v>0.82260535691211489</v>
+        <v>0.8226238162922489</v>
       </c>
       <c r="BA27" s="36">
         <v>101792</v>
@@ -4958,14 +4958,14 @@
       </c>
       <c r="BC27" s="17">
         <f t="shared" si="20"/>
-        <v>36646</v>
+        <v>36649</v>
       </c>
       <c r="BD27" s="38">
-        <v>91020</v>
+        <v>91023</v>
       </c>
       <c r="BE27" s="18">
         <f t="shared" si="21"/>
-        <v>0.89417635963533482</v>
+        <v>0.89420583149952848</v>
       </c>
       <c r="BF27" s="9">
         <v>155251</v>
@@ -4975,14 +4975,14 @@
       </c>
       <c r="BH27" s="17">
         <f t="shared" si="22"/>
-        <v>64489</v>
+        <v>64494</v>
       </c>
       <c r="BI27" s="19">
-        <v>145214</v>
+        <v>145219</v>
       </c>
       <c r="BJ27" s="18">
         <f t="shared" si="23"/>
-        <v>0.93534985281898342</v>
+        <v>0.93538205873070057</v>
       </c>
       <c r="BK27" s="2"/>
       <c r="BL27" s="2"/>
@@ -5036,14 +5036,14 @@
       </c>
       <c r="O28" s="17">
         <f t="shared" si="4"/>
-        <v>359409</v>
+        <v>359411</v>
       </c>
       <c r="P28" s="16">
-        <v>545059</v>
+        <v>545061</v>
       </c>
       <c r="Q28" s="18">
         <f t="shared" si="5"/>
-        <v>0.89932895872279417</v>
+        <v>0.89933225865531052</v>
       </c>
       <c r="R28" s="7">
         <v>610188</v>
@@ -5053,14 +5053,14 @@
       </c>
       <c r="T28" s="17">
         <f t="shared" si="6"/>
-        <v>358943</v>
+        <v>358945</v>
       </c>
       <c r="U28" s="16">
-        <v>548642</v>
+        <v>548644</v>
       </c>
       <c r="V28" s="18">
         <f t="shared" si="7"/>
-        <v>0.89913600398565685</v>
+        <v>0.8991392816640118</v>
       </c>
       <c r="W28" s="7">
         <v>613926</v>
@@ -5070,14 +5070,14 @@
       </c>
       <c r="Y28" s="17">
         <f t="shared" si="8"/>
-        <v>240225</v>
+        <v>240227</v>
       </c>
       <c r="Z28" s="16">
-        <v>551013</v>
+        <v>551015</v>
       </c>
       <c r="AA28" s="18">
         <f t="shared" si="9"/>
-        <v>0.89752348002853766</v>
+        <v>0.89752673775015235</v>
       </c>
       <c r="AB28" s="28">
         <v>616763</v>
@@ -5087,14 +5087,14 @@
       </c>
       <c r="AD28" s="17">
         <f t="shared" si="10"/>
-        <v>147648</v>
+        <v>147650</v>
       </c>
       <c r="AE28" s="40">
-        <v>552216</v>
+        <v>552218</v>
       </c>
       <c r="AF28" s="18">
         <f t="shared" si="11"/>
-        <v>0.89534553791326654</v>
+        <v>0.89534878064994172</v>
       </c>
       <c r="AG28" s="16">
         <v>621241</v>
@@ -5104,14 +5104,14 @@
       </c>
       <c r="AI28" s="17">
         <f t="shared" si="12"/>
-        <v>134843</v>
+        <v>134845</v>
       </c>
       <c r="AJ28" s="16">
-        <v>554815</v>
+        <v>554817</v>
       </c>
       <c r="AK28" s="18">
         <f t="shared" si="13"/>
-        <v>0.89307531215743974</v>
+        <v>0.89307853151997374</v>
       </c>
       <c r="AL28" s="30">
         <v>624748</v>
@@ -5121,14 +5121,14 @@
       </c>
       <c r="AN28" s="17">
         <f t="shared" si="14"/>
-        <v>120280</v>
+        <v>120282</v>
       </c>
       <c r="AO28" s="16">
-        <v>558524</v>
+        <v>558526</v>
       </c>
       <c r="AP28" s="18">
         <f t="shared" si="15"/>
-        <v>0.89399886034048925</v>
+        <v>0.89400206163124973</v>
       </c>
       <c r="AQ28" s="32">
         <v>625592</v>
@@ -5138,14 +5138,14 @@
       </c>
       <c r="AS28" s="17">
         <f t="shared" si="16"/>
-        <v>106902</v>
+        <v>106904</v>
       </c>
       <c r="AT28" s="16">
-        <v>561983</v>
+        <v>561985</v>
       </c>
       <c r="AU28" s="18">
         <f t="shared" si="17"/>
-        <v>0.89832190948733359</v>
+        <v>0.89832510645916186</v>
       </c>
       <c r="AV28" s="34">
         <v>329721</v>
@@ -5155,14 +5155,14 @@
       </c>
       <c r="AX28" s="17">
         <f t="shared" si="18"/>
-        <v>102396</v>
+        <v>102398</v>
       </c>
       <c r="AY28" s="19">
-        <v>269584</v>
+        <v>269586</v>
       </c>
       <c r="AZ28" s="18">
         <f t="shared" si="19"/>
-        <v>0.81761246629726347</v>
+        <v>0.81761853203162671</v>
       </c>
       <c r="BA28" s="36">
         <v>323065</v>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="BC28" s="17">
         <f t="shared" si="20"/>
-        <v>82763</v>
+        <v>82764</v>
       </c>
       <c r="BD28" s="38">
-        <v>273173</v>
+        <v>273174</v>
       </c>
       <c r="BE28" s="18">
         <f t="shared" si="21"/>
-        <v>0.84556668162753623</v>
+        <v>0.84556977697986468</v>
       </c>
       <c r="BF28" s="9">
         <v>619161</v>
@@ -5189,14 +5189,14 @@
       </c>
       <c r="BH28" s="17">
         <f t="shared" si="22"/>
-        <v>148333</v>
+        <v>148335</v>
       </c>
       <c r="BI28" s="19">
-        <v>569188</v>
+        <v>569190</v>
       </c>
       <c r="BJ28" s="18">
         <f t="shared" si="23"/>
-        <v>0.91928916711485376</v>
+        <v>0.91929239729246515</v>
       </c>
       <c r="BK28" s="2"/>
       <c r="BL28" s="2"/>
@@ -5403,14 +5403,14 @@
       </c>
       <c r="BH29" s="17">
         <f t="shared" si="22"/>
-        <v>51523</v>
+        <v>51524</v>
       </c>
       <c r="BI29" s="19">
-        <v>149840</v>
+        <v>149841</v>
       </c>
       <c r="BJ29" s="18">
         <f t="shared" si="23"/>
-        <v>0.97898168656121576</v>
+        <v>0.97898822007487407</v>
       </c>
       <c r="BK29" s="2"/>
       <c r="BL29" s="2"/>
@@ -5430,14 +5430,14 @@
       </c>
       <c r="E30" s="17">
         <f t="shared" si="0"/>
-        <v>183091</v>
+        <v>183092</v>
       </c>
       <c r="F30" s="16">
-        <v>212366</v>
+        <v>212367</v>
       </c>
       <c r="G30" s="18">
         <f t="shared" si="1"/>
-        <v>0.95282235811935512</v>
+        <v>0.95282684481853541</v>
       </c>
       <c r="H30" s="7">
         <v>223846</v>
@@ -5447,14 +5447,14 @@
       </c>
       <c r="J30" s="17">
         <f t="shared" si="2"/>
-        <v>151619</v>
+        <v>151620</v>
       </c>
       <c r="K30" s="16">
-        <v>213097</v>
+        <v>213098</v>
       </c>
       <c r="L30" s="18">
         <f t="shared" si="3"/>
-        <v>0.95198037936795832</v>
+        <v>0.95198484672498052</v>
       </c>
       <c r="M30" s="7">
         <v>227236</v>
@@ -5464,14 +5464,14 @@
       </c>
       <c r="O30" s="17">
         <f t="shared" si="4"/>
-        <v>148653</v>
+        <v>148654</v>
       </c>
       <c r="P30" s="16">
-        <v>215564</v>
+        <v>215565</v>
       </c>
       <c r="Q30" s="18">
         <f t="shared" si="5"/>
-        <v>0.94863489939974299</v>
+        <v>0.94863930011089792</v>
       </c>
       <c r="R30" s="7">
         <v>232779</v>
@@ -5481,14 +5481,14 @@
       </c>
       <c r="T30" s="17">
         <f t="shared" si="6"/>
-        <v>146418</v>
+        <v>146419</v>
       </c>
       <c r="U30" s="16">
-        <v>218439</v>
+        <v>218440</v>
       </c>
       <c r="V30" s="18">
         <f t="shared" si="7"/>
-        <v>0.93839650483935411</v>
+        <v>0.93840080075951871</v>
       </c>
       <c r="W30" s="7">
         <v>236990</v>
@@ -5498,14 +5498,14 @@
       </c>
       <c r="Y30" s="17">
         <f t="shared" si="8"/>
-        <v>97442</v>
+        <v>97443</v>
       </c>
       <c r="Z30" s="16">
-        <v>220885</v>
+        <v>220886</v>
       </c>
       <c r="AA30" s="18">
         <f t="shared" si="9"/>
-        <v>0.93204354614118734</v>
+        <v>0.93204776572851178</v>
       </c>
       <c r="AB30" s="28">
         <v>242455</v>
@@ -5515,14 +5515,14 @@
       </c>
       <c r="AD30" s="17">
         <f t="shared" si="10"/>
-        <v>59885</v>
+        <v>59887</v>
       </c>
       <c r="AE30" s="40">
-        <v>223569</v>
+        <v>223571</v>
       </c>
       <c r="AF30" s="18">
         <f t="shared" si="11"/>
-        <v>0.92210513291126184</v>
+        <v>0.92211338186467595</v>
       </c>
       <c r="AG30" s="16">
         <v>245898</v>
@@ -5532,14 +5532,14 @@
       </c>
       <c r="AI30" s="17">
         <f t="shared" si="12"/>
-        <v>55598</v>
+        <v>55599</v>
       </c>
       <c r="AJ30" s="16">
-        <v>226478</v>
+        <v>226479</v>
       </c>
       <c r="AK30" s="18">
         <f t="shared" si="13"/>
-        <v>0.9210241644909678</v>
+        <v>0.92102823121782207</v>
       </c>
       <c r="AL30" s="30">
         <v>247799</v>
@@ -5549,14 +5549,14 @@
       </c>
       <c r="AN30" s="17">
         <f t="shared" si="14"/>
-        <v>51260</v>
+        <v>51261</v>
       </c>
       <c r="AO30" s="16">
-        <v>229605</v>
+        <v>229606</v>
       </c>
       <c r="AP30" s="18">
         <f t="shared" si="15"/>
-        <v>0.92657758909438703</v>
+        <v>0.9265816246231825</v>
       </c>
       <c r="AQ30" s="32">
         <v>248265</v>
@@ -5566,14 +5566,14 @@
       </c>
       <c r="AS30" s="17">
         <f t="shared" si="16"/>
-        <v>46753</v>
+        <v>46754</v>
       </c>
       <c r="AT30" s="16">
-        <v>232658</v>
+        <v>232659</v>
       </c>
       <c r="AU30" s="18">
         <f t="shared" si="17"/>
-        <v>0.93713572191005579</v>
+        <v>0.93713974986405657</v>
       </c>
       <c r="AV30" s="34">
         <v>136662</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="AX30" s="17">
         <f t="shared" si="18"/>
-        <v>48127</v>
+        <v>48128</v>
       </c>
       <c r="AY30" s="19">
-        <v>121217</v>
+        <v>121218</v>
       </c>
       <c r="AZ30" s="18">
         <f t="shared" si="19"/>
-        <v>0.886983945793271</v>
+        <v>0.8869912631163015</v>
       </c>
       <c r="BA30" s="36">
         <v>130439</v>
@@ -5600,14 +5600,14 @@
       </c>
       <c r="BC30" s="17">
         <f t="shared" si="20"/>
-        <v>39072</v>
+        <v>39073</v>
       </c>
       <c r="BD30" s="38">
-        <v>124155</v>
+        <v>124156</v>
       </c>
       <c r="BE30" s="18">
         <f t="shared" si="21"/>
-        <v>0.9518242243500793</v>
+        <v>0.9518318907688651</v>
       </c>
       <c r="BF30" s="9">
         <v>245647</v>
@@ -5617,14 +5617,14 @@
       </c>
       <c r="BH30" s="17">
         <f t="shared" si="22"/>
-        <v>73632</v>
+        <v>73633</v>
       </c>
       <c r="BI30" s="19">
-        <v>239375</v>
+        <v>239376</v>
       </c>
       <c r="BJ30" s="18">
         <f t="shared" si="23"/>
-        <v>0.97446742683606968</v>
+        <v>0.97447149771827057</v>
       </c>
       <c r="BK30" s="2"/>
       <c r="BL30" s="2"/>
@@ -5712,14 +5712,14 @@
       </c>
       <c r="Y31" s="17">
         <f t="shared" si="8"/>
-        <v>58149</v>
+        <v>58150</v>
       </c>
       <c r="Z31" s="16">
-        <v>105282</v>
+        <v>105283</v>
       </c>
       <c r="AA31" s="18">
         <f t="shared" si="9"/>
-        <v>0.9443941120011482</v>
+        <v>0.94440308213955737</v>
       </c>
       <c r="AB31" s="28">
         <v>113499</v>
@@ -5729,14 +5729,14 @@
       </c>
       <c r="AD31" s="17">
         <f t="shared" si="10"/>
-        <v>42489</v>
+        <v>42490</v>
       </c>
       <c r="AE31" s="40">
-        <v>106236</v>
+        <v>106237</v>
       </c>
       <c r="AF31" s="18">
         <f t="shared" si="11"/>
-        <v>0.93600824676869399</v>
+        <v>0.93601705741900809</v>
       </c>
       <c r="AG31" s="16">
         <v>114692</v>
@@ -5746,14 +5746,14 @@
       </c>
       <c r="AI31" s="17">
         <f t="shared" si="12"/>
-        <v>42963</v>
+        <v>42964</v>
       </c>
       <c r="AJ31" s="16">
-        <v>107134</v>
+        <v>107135</v>
       </c>
       <c r="AK31" s="18">
         <f t="shared" si="13"/>
-        <v>0.93410176821399926</v>
+        <v>0.93411048721794021</v>
       </c>
       <c r="AL31" s="30">
         <v>115249</v>
@@ -5763,14 +5763,14 @@
       </c>
       <c r="AN31" s="17">
         <f t="shared" si="14"/>
-        <v>37324</v>
+        <v>37326</v>
       </c>
       <c r="AO31" s="16">
-        <v>108065</v>
+        <v>108067</v>
       </c>
       <c r="AP31" s="18">
         <f t="shared" si="15"/>
-        <v>0.9376654027366832</v>
+        <v>0.93768275646643351</v>
       </c>
       <c r="AQ31" s="32">
         <v>115872</v>
@@ -5780,14 +5780,14 @@
       </c>
       <c r="AS31" s="17">
         <f t="shared" si="16"/>
-        <v>30094</v>
+        <v>30095</v>
       </c>
       <c r="AT31" s="16">
-        <v>109485</v>
+        <v>109486</v>
       </c>
       <c r="AU31" s="18">
         <f t="shared" si="17"/>
-        <v>0.9448788318144159</v>
+        <v>0.94488746202706431</v>
       </c>
       <c r="AV31" s="34">
         <v>66168</v>
@@ -5797,14 +5797,14 @@
       </c>
       <c r="AX31" s="17">
         <f t="shared" si="18"/>
-        <v>26440</v>
+        <v>26441</v>
       </c>
       <c r="AY31" s="19">
-        <v>61145</v>
+        <v>61146</v>
       </c>
       <c r="AZ31" s="18">
         <f t="shared" si="19"/>
-        <v>0.92408717204691093</v>
+        <v>0.92410228509249182</v>
       </c>
       <c r="BA31" s="36">
         <v>65704</v>
@@ -5858,14 +5858,14 @@
       </c>
       <c r="E32" s="17">
         <f t="shared" si="0"/>
-        <v>317971</v>
+        <v>317972</v>
       </c>
       <c r="F32" s="16">
-        <v>342987</v>
+        <v>342988</v>
       </c>
       <c r="G32" s="18">
         <f t="shared" si="1"/>
-        <v>0.97689818797031025</v>
+        <v>0.97690103617793322</v>
       </c>
       <c r="H32" s="7">
         <v>350849</v>
@@ -6072,14 +6072,14 @@
       </c>
       <c r="E33" s="17">
         <f t="shared" si="0"/>
-        <v>808066</v>
+        <v>808067</v>
       </c>
       <c r="F33" s="16">
-        <v>845887</v>
+        <v>845888</v>
       </c>
       <c r="G33" s="18">
         <f t="shared" si="1"/>
-        <v>0.94788512697306349</v>
+        <v>0.94788624755433137</v>
       </c>
       <c r="H33" s="7">
         <v>888497</v>
@@ -6089,14 +6089,14 @@
       </c>
       <c r="J33" s="17">
         <f t="shared" si="2"/>
-        <v>639077</v>
+        <v>639078</v>
       </c>
       <c r="K33" s="16">
-        <v>846056</v>
+        <v>846057</v>
       </c>
       <c r="L33" s="18">
         <f t="shared" si="3"/>
-        <v>0.95223281564259643</v>
+        <v>0.95223394113879956</v>
       </c>
       <c r="M33" s="7">
         <v>888717</v>
@@ -6106,14 +6106,14 @@
       </c>
       <c r="O33" s="17">
         <f t="shared" si="4"/>
-        <v>454203</v>
+        <v>454204</v>
       </c>
       <c r="P33" s="16">
-        <v>850266</v>
+        <v>850267</v>
       </c>
       <c r="Q33" s="18">
         <f t="shared" si="5"/>
-        <v>0.95673425848723492</v>
+        <v>0.95673538370482392</v>
       </c>
       <c r="R33" s="7">
         <v>899174</v>
@@ -6123,14 +6123,14 @@
       </c>
       <c r="T33" s="17">
         <f t="shared" si="6"/>
-        <v>425245</v>
+        <v>425246</v>
       </c>
       <c r="U33" s="16">
-        <v>858920</v>
+        <v>858921</v>
       </c>
       <c r="V33" s="18">
         <f t="shared" si="7"/>
-        <v>0.9552322464839953</v>
+        <v>0.95523335861579628</v>
       </c>
       <c r="W33" s="7">
         <v>909355</v>
@@ -6140,14 +6140,14 @@
       </c>
       <c r="Y33" s="17">
         <f t="shared" si="8"/>
-        <v>280855</v>
+        <v>280856</v>
       </c>
       <c r="Z33" s="16">
-        <v>867295</v>
+        <v>867296</v>
       </c>
       <c r="AA33" s="18">
         <f t="shared" si="9"/>
-        <v>0.95374743636973458</v>
+        <v>0.95374853605027743</v>
       </c>
       <c r="AB33" s="28">
         <v>919225</v>
@@ -6157,14 +6157,14 @@
       </c>
       <c r="AD33" s="17">
         <f t="shared" si="10"/>
-        <v>196756</v>
+        <v>196757</v>
       </c>
       <c r="AE33" s="40">
-        <v>876680</v>
+        <v>876681</v>
       </c>
       <c r="AF33" s="18">
         <f t="shared" si="11"/>
-        <v>0.95371644591911664</v>
+        <v>0.95371753379205304</v>
       </c>
       <c r="AG33" s="16">
         <v>928340</v>
@@ -6174,14 +6174,14 @@
       </c>
       <c r="AI33" s="17">
         <f t="shared" si="12"/>
-        <v>235382</v>
+        <v>235383</v>
       </c>
       <c r="AJ33" s="16">
-        <v>884847</v>
+        <v>884848</v>
       </c>
       <c r="AK33" s="18">
         <f t="shared" si="13"/>
-        <v>0.95314970808109101</v>
+        <v>0.95315078527263719</v>
       </c>
       <c r="AL33" s="30">
         <v>932930</v>
@@ -6191,14 +6191,14 @@
       </c>
       <c r="AN33" s="17">
         <f t="shared" si="14"/>
-        <v>167614</v>
+        <v>167615</v>
       </c>
       <c r="AO33" s="16">
-        <v>892490</v>
+        <v>892491</v>
       </c>
       <c r="AP33" s="18">
         <f t="shared" si="15"/>
-        <v>0.95665269634377714</v>
+        <v>0.95665376823555892</v>
       </c>
       <c r="AQ33" s="32">
         <v>933808</v>
@@ -6208,14 +6208,14 @@
       </c>
       <c r="AS33" s="17">
         <f t="shared" si="16"/>
-        <v>132954</v>
+        <v>132955</v>
       </c>
       <c r="AT33" s="16">
-        <v>901472</v>
+        <v>901473</v>
       </c>
       <c r="AU33" s="18">
         <f t="shared" si="17"/>
-        <v>0.96537189657831157</v>
+        <v>0.96537296746226209</v>
       </c>
       <c r="AV33" s="34">
         <v>471009</v>
@@ -6698,14 +6698,14 @@
       </c>
       <c r="E36" s="17">
         <f t="shared" si="0"/>
-        <v>1190285</v>
+        <v>1190288</v>
       </c>
       <c r="F36" s="16">
-        <v>1261900</v>
+        <v>1261903</v>
       </c>
       <c r="G36" s="18">
         <f t="shared" si="1"/>
-        <v>0.91463105266286004</v>
+        <v>0.91463322707696415</v>
       </c>
       <c r="H36" s="7">
         <v>1370063</v>
@@ -6715,14 +6715,14 @@
       </c>
       <c r="J36" s="17">
         <f t="shared" si="2"/>
-        <v>1054967</v>
+        <v>1054971</v>
       </c>
       <c r="K36" s="16">
-        <v>1261862</v>
+        <v>1261866</v>
       </c>
       <c r="L36" s="18">
         <f t="shared" si="3"/>
-        <v>0.92102479958950789</v>
+        <v>0.9210277191632793</v>
       </c>
       <c r="M36" s="7">
         <v>1376699</v>
@@ -6732,14 +6732,14 @@
       </c>
       <c r="O36" s="17">
         <f t="shared" si="4"/>
-        <v>909592</v>
+        <v>909595</v>
       </c>
       <c r="P36" s="16">
-        <v>1267349</v>
+        <v>1267352</v>
       </c>
       <c r="Q36" s="18">
         <f t="shared" si="5"/>
-        <v>0.92057087279063909</v>
+        <v>0.92057305191621408</v>
       </c>
       <c r="R36" s="7">
         <v>1386159</v>
@@ -6749,14 +6749,14 @@
       </c>
       <c r="T36" s="17">
         <f t="shared" si="6"/>
-        <v>856800</v>
+        <v>856805</v>
       </c>
       <c r="U36" s="16">
-        <v>1274717</v>
+        <v>1274722</v>
       </c>
       <c r="V36" s="18">
         <f t="shared" si="7"/>
-        <v>0.91960373954214492</v>
+        <v>0.91960734663195198</v>
       </c>
       <c r="W36" s="7">
         <v>1395892</v>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="Y36" s="17">
         <f t="shared" si="8"/>
-        <v>663042</v>
+        <v>663046</v>
       </c>
       <c r="Z36" s="16">
-        <v>1283925</v>
+        <v>1283929</v>
       </c>
       <c r="AA36" s="18">
         <f t="shared" si="9"/>
-        <v>0.91978820711057874</v>
+        <v>0.91979107266178184</v>
       </c>
       <c r="AB36" s="28">
         <v>1408098</v>
@@ -6783,14 +6783,14 @@
       </c>
       <c r="AD36" s="17">
         <f t="shared" si="10"/>
-        <v>434753</v>
+        <v>434758</v>
       </c>
       <c r="AE36" s="40">
-        <v>1290853</v>
+        <v>1290858</v>
       </c>
       <c r="AF36" s="18">
         <f t="shared" si="11"/>
-        <v>0.91673519882849064</v>
+        <v>0.9167387497177043</v>
       </c>
       <c r="AG36" s="16">
         <v>1413160</v>
@@ -6800,14 +6800,14 @@
       </c>
       <c r="AI36" s="17">
         <f t="shared" si="12"/>
-        <v>420936</v>
+        <v>420939</v>
       </c>
       <c r="AJ36" s="16">
-        <v>1299765</v>
+        <v>1299768</v>
       </c>
       <c r="AK36" s="18">
         <f t="shared" si="13"/>
-        <v>0.91975784766056212</v>
+        <v>0.91975997056242742</v>
       </c>
       <c r="AL36" s="30">
         <v>1410829</v>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="AN36" s="17">
         <f t="shared" si="14"/>
-        <v>358677</v>
+        <v>358682</v>
       </c>
       <c r="AO36" s="16">
-        <v>1310045</v>
+        <v>1310050</v>
       </c>
       <c r="AP36" s="18">
         <f t="shared" si="15"/>
-        <v>0.9285639861386461</v>
+        <v>0.92856753015425686</v>
       </c>
       <c r="AQ36" s="32">
         <v>1406326</v>
@@ -6834,14 +6834,14 @@
       </c>
       <c r="AS36" s="17">
         <f t="shared" si="16"/>
-        <v>299735</v>
+        <v>299739</v>
       </c>
       <c r="AT36" s="16">
-        <v>1321858</v>
+        <v>1321862</v>
       </c>
       <c r="AU36" s="18">
         <f t="shared" si="17"/>
-        <v>0.93993711273204084</v>
+        <v>0.93993995702276711</v>
       </c>
       <c r="AV36" s="34">
         <v>685252</v>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="AX36" s="17">
         <f t="shared" si="18"/>
-        <v>251677</v>
+        <v>251679</v>
       </c>
       <c r="AY36" s="19">
-        <v>635319</v>
+        <v>635321</v>
       </c>
       <c r="AZ36" s="18">
         <f t="shared" si="19"/>
-        <v>0.92713191643366233</v>
+        <v>0.927134835067975</v>
       </c>
       <c r="BA36" s="36">
         <v>667048</v>
@@ -6868,14 +6868,14 @@
       </c>
       <c r="BC36" s="17">
         <f t="shared" si="20"/>
-        <v>222478</v>
+        <v>222480</v>
       </c>
       <c r="BD36" s="38">
-        <v>648497</v>
+        <v>648499</v>
       </c>
       <c r="BE36" s="18">
         <f t="shared" si="21"/>
-        <v>0.97218940765881912</v>
+        <v>0.97219240594380019</v>
       </c>
       <c r="BF36" s="9">
         <v>1363993</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="BH36" s="17">
         <f t="shared" si="22"/>
-        <v>477183</v>
+        <v>477187</v>
       </c>
       <c r="BI36" s="19">
-        <v>1343308</v>
+        <v>1343312</v>
       </c>
       <c r="BJ36" s="18">
         <f t="shared" si="23"/>
-        <v>0.98483496616184985</v>
+        <v>0.98483789872821925</v>
       </c>
       <c r="BK36" s="2"/>
       <c r="BL36" s="2"/>
@@ -6912,14 +6912,14 @@
       </c>
       <c r="E37" s="17">
         <f t="shared" si="0"/>
-        <v>576554</v>
+        <v>576555</v>
       </c>
       <c r="F37" s="16">
-        <v>676214</v>
+        <v>676215</v>
       </c>
       <c r="G37" s="18">
         <f t="shared" si="1"/>
-        <v>0.92147334568843342</v>
+        <v>0.92147470838329881</v>
       </c>
       <c r="H37" s="7">
         <v>729493</v>
@@ -6929,14 +6929,14 @@
       </c>
       <c r="J37" s="17">
         <f t="shared" si="2"/>
-        <v>474088</v>
+        <v>474089</v>
       </c>
       <c r="K37" s="16">
-        <v>677781</v>
+        <v>677782</v>
       </c>
       <c r="L37" s="18">
         <f t="shared" si="3"/>
-        <v>0.92911241094842578</v>
+        <v>0.92911378176349879</v>
       </c>
       <c r="M37" s="7">
         <v>737436</v>
@@ -6946,14 +6946,14 @@
       </c>
       <c r="O37" s="17">
         <f t="shared" si="4"/>
-        <v>446525</v>
+        <v>446526</v>
       </c>
       <c r="P37" s="16">
-        <v>683925</v>
+        <v>683926</v>
       </c>
       <c r="Q37" s="18">
         <f t="shared" si="5"/>
-        <v>0.92743641482108274</v>
+        <v>0.92743777087096368</v>
       </c>
       <c r="R37" s="7">
         <v>746987</v>
@@ -6963,14 +6963,14 @@
       </c>
       <c r="T37" s="17">
         <f t="shared" si="6"/>
-        <v>392168</v>
+        <v>392170</v>
       </c>
       <c r="U37" s="16">
-        <v>689284</v>
+        <v>689286</v>
       </c>
       <c r="V37" s="18">
         <f t="shared" si="7"/>
-        <v>0.92275233705539716</v>
+        <v>0.92275501447816366</v>
       </c>
       <c r="W37" s="7">
         <v>758127</v>
@@ -6980,14 +6980,14 @@
       </c>
       <c r="Y37" s="17">
         <f t="shared" si="8"/>
-        <v>268432</v>
+        <v>268434</v>
       </c>
       <c r="Z37" s="16">
-        <v>695638</v>
+        <v>695640</v>
       </c>
       <c r="AA37" s="18">
         <f t="shared" si="9"/>
-        <v>0.91757449609366237</v>
+        <v>0.91757713417408959</v>
       </c>
       <c r="AB37" s="28">
         <v>768520</v>
@@ -6997,14 +6997,14 @@
       </c>
       <c r="AD37" s="17">
         <f t="shared" si="10"/>
-        <v>196240</v>
+        <v>196242</v>
       </c>
       <c r="AE37" s="40">
-        <v>701722</v>
+        <v>701724</v>
       </c>
       <c r="AF37" s="18">
         <f t="shared" si="11"/>
-        <v>0.9130822880341436</v>
+        <v>0.9130848904387654</v>
       </c>
       <c r="AG37" s="16">
         <v>770579</v>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="AI37" s="17">
         <f t="shared" si="12"/>
-        <v>189646</v>
+        <v>189648</v>
       </c>
       <c r="AJ37" s="16">
-        <v>707547</v>
+        <v>707549</v>
       </c>
       <c r="AK37" s="18">
         <f t="shared" si="13"/>
-        <v>0.91820176776164419</v>
+        <v>0.91820436321259724</v>
       </c>
       <c r="AL37" s="30">
         <v>769439</v>
@@ -7031,14 +7031,14 @@
       </c>
       <c r="AN37" s="17">
         <f t="shared" si="14"/>
-        <v>166238</v>
+        <v>166239</v>
       </c>
       <c r="AO37" s="16">
-        <v>715095</v>
+        <v>715096</v>
       </c>
       <c r="AP37" s="18">
         <f t="shared" si="15"/>
-        <v>0.92937191902152083</v>
+        <v>0.92937321866970612</v>
       </c>
       <c r="AQ37" s="32">
         <v>769503</v>
@@ -7048,14 +7048,14 @@
       </c>
       <c r="AS37" s="17">
         <f t="shared" si="16"/>
-        <v>134994</v>
+        <v>134996</v>
       </c>
       <c r="AT37" s="16">
-        <v>720387</v>
+        <v>720389</v>
       </c>
       <c r="AU37" s="18">
         <f t="shared" si="17"/>
-        <v>0.93617178880394225</v>
+        <v>0.93617438788412777</v>
       </c>
       <c r="AV37" s="34">
         <v>526548</v>
@@ -7082,14 +7082,14 @@
       </c>
       <c r="BC37" s="17">
         <f t="shared" si="20"/>
-        <v>117161</v>
+        <v>117162</v>
       </c>
       <c r="BD37" s="38">
-        <v>495941</v>
+        <v>495942</v>
       </c>
       <c r="BE37" s="18">
         <f t="shared" si="21"/>
-        <v>0.94450020282507718</v>
+        <v>0.94450210728589579</v>
       </c>
       <c r="BF37" s="9">
         <v>765317</v>
@@ -7099,14 +7099,14 @@
       </c>
       <c r="BH37" s="17">
         <f t="shared" si="22"/>
-        <v>198987</v>
+        <v>198990</v>
       </c>
       <c r="BI37" s="19">
-        <v>738860</v>
+        <v>738863</v>
       </c>
       <c r="BJ37" s="18">
         <f t="shared" si="23"/>
-        <v>0.96543001135477191</v>
+        <v>0.96543393129905652</v>
       </c>
       <c r="BK37" s="2"/>
       <c r="BL37" s="2"/>
@@ -7554,14 +7554,14 @@
       </c>
       <c r="E40" s="17">
         <f t="shared" si="0"/>
-        <v>254693</v>
+        <v>254695</v>
       </c>
       <c r="F40" s="16">
-        <v>278448</v>
+        <v>278450</v>
       </c>
       <c r="G40" s="18">
         <f t="shared" si="1"/>
-        <v>0.91725083012702258</v>
+        <v>0.91725741843672592</v>
       </c>
       <c r="H40" s="7">
         <v>301693</v>
@@ -7571,14 +7571,14 @@
       </c>
       <c r="J40" s="17">
         <f t="shared" si="2"/>
-        <v>226110</v>
+        <v>226112</v>
       </c>
       <c r="K40" s="16">
-        <v>278734</v>
+        <v>278736</v>
       </c>
       <c r="L40" s="18">
         <f t="shared" si="3"/>
-        <v>0.92389946071005957</v>
+        <v>0.92390608996562729</v>
       </c>
       <c r="M40" s="7">
         <v>303033</v>
@@ -7588,14 +7588,14 @@
       </c>
       <c r="O40" s="17">
         <f t="shared" si="4"/>
-        <v>207450</v>
+        <v>207452</v>
       </c>
       <c r="P40" s="16">
-        <v>280635</v>
+        <v>280637</v>
       </c>
       <c r="Q40" s="18">
         <f t="shared" si="5"/>
-        <v>0.9260872578234054</v>
+        <v>0.92609385776466591</v>
       </c>
       <c r="R40" s="7">
         <v>305881</v>
@@ -7605,14 +7605,14 @@
       </c>
       <c r="T40" s="17">
         <f t="shared" si="6"/>
-        <v>201464</v>
+        <v>201466</v>
       </c>
       <c r="U40" s="16">
-        <v>282760</v>
+        <v>282762</v>
       </c>
       <c r="V40" s="18">
         <f t="shared" si="7"/>
-        <v>0.92441178105210853</v>
+        <v>0.92441831954256726</v>
       </c>
       <c r="W40" s="7">
         <v>309941</v>
@@ -7622,14 +7622,14 @@
       </c>
       <c r="Y40" s="17">
         <f t="shared" si="8"/>
-        <v>162284</v>
+        <v>162286</v>
       </c>
       <c r="Z40" s="16">
-        <v>286101</v>
+        <v>286103</v>
       </c>
       <c r="AA40" s="18">
         <f t="shared" si="9"/>
-        <v>0.92308213498698144</v>
+        <v>0.92308858782800596</v>
       </c>
       <c r="AB40" s="28">
         <v>313197</v>
@@ -7639,14 +7639,14 @@
       </c>
       <c r="AD40" s="17">
         <f t="shared" si="10"/>
-        <v>108205</v>
+        <v>108207</v>
       </c>
       <c r="AE40" s="40">
-        <v>288284</v>
+        <v>288286</v>
       </c>
       <c r="AF40" s="18">
         <f t="shared" si="11"/>
-        <v>0.92045581534944465</v>
+        <v>0.92046220110665178</v>
       </c>
       <c r="AG40" s="16">
         <v>316872</v>
@@ -7656,14 +7656,14 @@
       </c>
       <c r="AI40" s="17">
         <f t="shared" si="12"/>
-        <v>93354</v>
+        <v>93357</v>
       </c>
       <c r="AJ40" s="16">
-        <v>291254</v>
+        <v>291257</v>
       </c>
       <c r="AK40" s="18">
         <f t="shared" si="13"/>
-        <v>0.91915347522027824</v>
+        <v>0.91916294276553312</v>
       </c>
       <c r="AL40" s="30">
         <v>319591</v>
@@ -7673,14 +7673,14 @@
       </c>
       <c r="AN40" s="17">
         <f t="shared" si="14"/>
-        <v>85454</v>
+        <v>85458</v>
       </c>
       <c r="AO40" s="16">
-        <v>294967</v>
+        <v>294971</v>
       </c>
       <c r="AP40" s="18">
         <f t="shared" si="15"/>
-        <v>0.92295152241458611</v>
+        <v>0.9229640384115948</v>
       </c>
       <c r="AQ40" s="32">
         <v>320883</v>
@@ -7690,14 +7690,14 @@
       </c>
       <c r="AS40" s="17">
         <f t="shared" si="16"/>
-        <v>70107</v>
+        <v>70110</v>
       </c>
       <c r="AT40" s="16">
-        <v>298154</v>
+        <v>298157</v>
       </c>
       <c r="AU40" s="18">
         <f t="shared" si="17"/>
-        <v>0.92916732890181153</v>
+        <v>0.92917667810385718</v>
       </c>
       <c r="AV40" s="34">
         <v>237285</v>
@@ -7707,14 +7707,14 @@
       </c>
       <c r="AX40" s="17">
         <f t="shared" si="18"/>
-        <v>72823</v>
+        <v>72825</v>
       </c>
       <c r="AY40" s="19">
-        <v>218385</v>
+        <v>218387</v>
       </c>
       <c r="AZ40" s="18">
         <f t="shared" si="19"/>
-        <v>0.92034894746823437</v>
+        <v>0.92035737615104196</v>
       </c>
       <c r="BA40" s="36">
         <v>231667</v>
@@ -7724,14 +7724,14 @@
       </c>
       <c r="BC40" s="17">
         <f t="shared" si="20"/>
-        <v>66785</v>
+        <v>66787</v>
       </c>
       <c r="BD40" s="38">
-        <v>220883</v>
+        <v>220885</v>
       </c>
       <c r="BE40" s="18">
         <f t="shared" si="21"/>
-        <v>0.95345042669003355</v>
+        <v>0.95345905977113699</v>
       </c>
       <c r="BF40" s="9">
         <v>314391</v>
@@ -7741,14 +7741,14 @@
       </c>
       <c r="BH40" s="17">
         <f t="shared" si="22"/>
-        <v>110212</v>
+        <v>110215</v>
       </c>
       <c r="BI40" s="19">
-        <v>305161</v>
+        <v>305164</v>
       </c>
       <c r="BJ40" s="18">
         <f t="shared" si="23"/>
-        <v>0.97064165322798679</v>
+        <v>0.97065119548587586</v>
       </c>
       <c r="BK40" s="2"/>
       <c r="BL40" s="2"/>
@@ -7768,14 +7768,14 @@
       </c>
       <c r="E41" s="17">
         <f t="shared" si="0"/>
-        <v>721650</v>
+        <v>721662</v>
       </c>
       <c r="F41" s="16">
-        <v>811832</v>
+        <v>811844</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="1"/>
-        <v>0.92692239186331693</v>
+        <v>0.92693609305851776</v>
       </c>
       <c r="H41" s="7">
         <v>872102</v>
@@ -7785,14 +7785,14 @@
       </c>
       <c r="J41" s="17">
         <f t="shared" si="2"/>
-        <v>601134</v>
+        <v>601140</v>
       </c>
       <c r="K41" s="16">
-        <v>812785</v>
+        <v>812791</v>
       </c>
       <c r="L41" s="18">
         <f t="shared" si="3"/>
-        <v>0.93198387344599598</v>
+        <v>0.93199075337517856</v>
       </c>
       <c r="M41" s="7">
         <v>879453</v>
@@ -7802,14 +7802,14 @@
       </c>
       <c r="O41" s="17">
         <f t="shared" si="4"/>
-        <v>529786</v>
+        <v>529797</v>
       </c>
       <c r="P41" s="16">
-        <v>817872</v>
+        <v>817883</v>
       </c>
       <c r="Q41" s="18">
         <f t="shared" si="5"/>
-        <v>0.92997806591142451</v>
+        <v>0.92999057368614357</v>
       </c>
       <c r="R41" s="7">
         <v>900135</v>
@@ -7819,14 +7819,14 @@
       </c>
       <c r="T41" s="17">
         <f t="shared" si="6"/>
-        <v>493867</v>
+        <v>493879</v>
       </c>
       <c r="U41" s="16">
-        <v>829332</v>
+        <v>829344</v>
       </c>
       <c r="V41" s="18">
         <f t="shared" si="7"/>
-        <v>0.92134179873019051</v>
+        <v>0.92135513006382375</v>
       </c>
       <c r="W41" s="7">
         <v>916182</v>
@@ -7836,14 +7836,14 @@
       </c>
       <c r="Y41" s="17">
         <f t="shared" si="8"/>
-        <v>333103</v>
+        <v>333120</v>
       </c>
       <c r="Z41" s="16">
-        <v>837149</v>
+        <v>837166</v>
       </c>
       <c r="AA41" s="18">
         <f t="shared" si="9"/>
-        <v>0.91373657199115454</v>
+        <v>0.91375512725637487</v>
       </c>
       <c r="AB41" s="28">
         <v>928683</v>
@@ -7853,14 +7853,14 @@
       </c>
       <c r="AD41" s="17">
         <f t="shared" si="10"/>
-        <v>228052</v>
+        <v>228068</v>
       </c>
       <c r="AE41" s="40">
-        <v>842839</v>
+        <v>842855</v>
       </c>
       <c r="AF41" s="18">
         <f t="shared" si="11"/>
-        <v>0.90756372195894619</v>
+        <v>0.90758095065808242</v>
       </c>
       <c r="AG41" s="16">
         <v>933135</v>
@@ -7870,14 +7870,14 @@
       </c>
       <c r="AI41" s="17">
         <f t="shared" si="12"/>
-        <v>223134</v>
+        <v>223150</v>
       </c>
       <c r="AJ41" s="16">
-        <v>851082</v>
+        <v>851098</v>
       </c>
       <c r="AK41" s="18">
         <f t="shared" si="13"/>
-        <v>0.91206738574804291</v>
+        <v>0.91208453224881714</v>
       </c>
       <c r="AL41" s="30">
         <v>933314</v>
@@ -7887,14 +7887,14 @@
       </c>
       <c r="AN41" s="17">
         <f t="shared" si="14"/>
-        <v>186854</v>
+        <v>186868</v>
       </c>
       <c r="AO41" s="16">
-        <v>858737</v>
+        <v>858751</v>
       </c>
       <c r="AP41" s="18">
         <f t="shared" si="15"/>
-        <v>0.92009441624147925</v>
+        <v>0.92010941655220002</v>
       </c>
       <c r="AQ41" s="32">
         <v>923873</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="AS41" s="17">
         <f t="shared" si="16"/>
-        <v>168473</v>
+        <v>168486</v>
       </c>
       <c r="AT41" s="16">
-        <v>867868</v>
+        <v>867881</v>
       </c>
       <c r="AU41" s="18">
         <f t="shared" si="17"/>
-        <v>0.93938019619579749</v>
+        <v>0.93939426739389509</v>
       </c>
       <c r="AV41" s="34">
         <v>726285</v>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="AX41" s="17">
         <f t="shared" si="18"/>
-        <v>161035</v>
+        <v>161046</v>
       </c>
       <c r="AY41" s="19">
-        <v>680672</v>
+        <v>680683</v>
       </c>
       <c r="AZ41" s="18">
         <f t="shared" si="19"/>
-        <v>0.93719683044534863</v>
+        <v>0.93721197601492523</v>
       </c>
       <c r="BA41" s="36">
         <v>715063</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="BC41" s="17">
         <f t="shared" si="20"/>
-        <v>142443</v>
+        <v>142455</v>
       </c>
       <c r="BD41" s="38">
-        <v>688350</v>
+        <v>688362</v>
       </c>
       <c r="BE41" s="18">
         <f t="shared" si="21"/>
-        <v>0.96264245248320779</v>
+        <v>0.96265923422132038</v>
       </c>
       <c r="BF41" s="9">
         <v>910875</v>
@@ -7955,14 +7955,14 @@
       </c>
       <c r="BH41" s="17">
         <f t="shared" si="22"/>
-        <v>228675</v>
+        <v>228687</v>
       </c>
       <c r="BI41" s="19">
-        <v>887984</v>
+        <v>887996</v>
       </c>
       <c r="BJ41" s="18">
         <f t="shared" si="23"/>
-        <v>0.97486921915740354</v>
+        <v>0.97488239330314264</v>
       </c>
       <c r="BK41" s="2"/>
       <c r="BL41" s="2"/>
@@ -8427,14 +8427,14 @@
       </c>
       <c r="J44" s="17">
         <f t="shared" si="2"/>
-        <v>218365</v>
+        <v>218366</v>
       </c>
       <c r="K44" s="16">
-        <v>302997</v>
+        <v>302998</v>
       </c>
       <c r="L44" s="18">
         <f t="shared" si="3"/>
-        <v>0.8523410072913854</v>
+        <v>0.85234382032586187</v>
       </c>
       <c r="M44" s="7">
         <v>358237</v>
@@ -8444,14 +8444,14 @@
       </c>
       <c r="O44" s="17">
         <f t="shared" si="4"/>
-        <v>188415</v>
+        <v>188416</v>
       </c>
       <c r="P44" s="16">
-        <v>305084</v>
+        <v>305085</v>
       </c>
       <c r="Q44" s="18">
         <f t="shared" si="5"/>
-        <v>0.85162615810203857</v>
+        <v>0.85162894955015811</v>
       </c>
       <c r="R44" s="7">
         <v>364550</v>
@@ -8597,14 +8597,14 @@
       </c>
       <c r="BH44" s="17">
         <f t="shared" si="22"/>
-        <v>115087</v>
+        <v>115088</v>
       </c>
       <c r="BI44" s="19">
-        <v>334885</v>
+        <v>334886</v>
       </c>
       <c r="BJ44" s="18">
         <f t="shared" si="23"/>
-        <v>0.89982937675493402</v>
+        <v>0.89983206373517122</v>
       </c>
       <c r="BK44" s="2"/>
       <c r="BL44" s="2"/>
@@ -8658,14 +8658,14 @@
       </c>
       <c r="O45" s="17">
         <f t="shared" si="4"/>
-        <v>162269</v>
+        <v>162270</v>
       </c>
       <c r="P45" s="16">
-        <v>254134</v>
+        <v>254135</v>
       </c>
       <c r="Q45" s="18">
         <f t="shared" si="5"/>
-        <v>0.90186879404938503</v>
+        <v>0.90187234284173101</v>
       </c>
       <c r="R45" s="7">
         <v>285895</v>
@@ -8675,14 +8675,14 @@
       </c>
       <c r="T45" s="17">
         <f t="shared" si="6"/>
-        <v>161920</v>
+        <v>161921</v>
       </c>
       <c r="U45" s="16">
-        <v>256512</v>
+        <v>256513</v>
       </c>
       <c r="V45" s="18">
         <f t="shared" si="7"/>
-        <v>0.89722450550027111</v>
+        <v>0.89722800328792041</v>
       </c>
       <c r="W45" s="7">
         <v>289101</v>
@@ -8692,14 +8692,14 @@
       </c>
       <c r="Y45" s="17">
         <f t="shared" si="8"/>
-        <v>106877</v>
+        <v>106878</v>
       </c>
       <c r="Z45" s="16">
-        <v>258050</v>
+        <v>258051</v>
       </c>
       <c r="AA45" s="18">
         <f t="shared" si="9"/>
-        <v>0.89259462955852797</v>
+        <v>0.89259808855728617</v>
       </c>
       <c r="AB45" s="28">
         <v>291802</v>
@@ -8709,14 +8709,14 @@
       </c>
       <c r="AD45" s="17">
         <f t="shared" si="10"/>
-        <v>82914</v>
+        <v>82915</v>
       </c>
       <c r="AE45" s="40">
-        <v>259335</v>
+        <v>259336</v>
       </c>
       <c r="AF45" s="18">
         <f t="shared" si="11"/>
-        <v>0.88873619783277702</v>
+        <v>0.8887396248140863</v>
       </c>
       <c r="AG45" s="16">
         <v>295238</v>
@@ -8726,14 +8726,14 @@
       </c>
       <c r="AI45" s="17">
         <f t="shared" si="12"/>
-        <v>74365</v>
+        <v>74368</v>
       </c>
       <c r="AJ45" s="16">
-        <v>261948</v>
+        <v>261951</v>
       </c>
       <c r="AK45" s="18">
         <f t="shared" si="13"/>
-        <v>0.88724351201403617</v>
+        <v>0.8872536733076366</v>
       </c>
       <c r="AL45" s="30">
         <v>296582</v>
@@ -8743,14 +8743,14 @@
       </c>
       <c r="AN45" s="17">
         <f t="shared" si="14"/>
-        <v>68836</v>
+        <v>68837</v>
       </c>
       <c r="AO45" s="16">
-        <v>264666</v>
+        <v>264667</v>
       </c>
       <c r="AP45" s="18">
         <f t="shared" si="15"/>
-        <v>0.89238726557916526</v>
+        <v>0.89239063732795654</v>
       </c>
       <c r="AQ45" s="32">
         <v>297340</v>
@@ -8760,14 +8760,14 @@
       </c>
       <c r="AS45" s="17">
         <f t="shared" si="16"/>
-        <v>61445</v>
+        <v>61446</v>
       </c>
       <c r="AT45" s="16">
-        <v>267851</v>
+        <v>267852</v>
       </c>
       <c r="AU45" s="18">
         <f t="shared" si="17"/>
-        <v>0.90082397255666913</v>
+        <v>0.90082733570996165</v>
       </c>
       <c r="AV45" s="34">
         <v>215259</v>
@@ -8777,14 +8777,14 @@
       </c>
       <c r="AX45" s="17">
         <f t="shared" si="18"/>
-        <v>55042</v>
+        <v>55043</v>
       </c>
       <c r="AY45" s="19">
-        <v>190306</v>
+        <v>190307</v>
       </c>
       <c r="AZ45" s="18">
         <f t="shared" si="19"/>
-        <v>0.88407917903548749</v>
+        <v>0.88408382460199109</v>
       </c>
       <c r="BA45" s="36">
         <v>211045</v>
@@ -8794,14 +8794,14 @@
       </c>
       <c r="BC45" s="17">
         <f t="shared" si="20"/>
-        <v>49614</v>
+        <v>49615</v>
       </c>
       <c r="BD45" s="38">
-        <v>192715</v>
+        <v>192716</v>
       </c>
       <c r="BE45" s="18">
         <f t="shared" si="21"/>
-        <v>0.91314648534672704</v>
+        <v>0.91315122367267643</v>
       </c>
       <c r="BF45" s="9">
         <v>290704</v>
@@ -8811,14 +8811,14 @@
       </c>
       <c r="BH45" s="17">
         <f t="shared" si="22"/>
-        <v>88682</v>
+        <v>88683</v>
       </c>
       <c r="BI45" s="19">
-        <v>272422</v>
+        <v>272423</v>
       </c>
       <c r="BJ45" s="18">
         <f t="shared" si="23"/>
-        <v>0.93711128845836311</v>
+        <v>0.9371147283835104</v>
       </c>
       <c r="BK45" s="2"/>
       <c r="BL45" s="2"/>
@@ -8974,14 +8974,14 @@
       </c>
       <c r="AS46" s="17">
         <f t="shared" si="16"/>
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AT46" s="16">
-        <v>3652</v>
+        <v>3653</v>
       </c>
       <c r="AU46" s="18">
         <f t="shared" si="17"/>
-        <v>0.95054659031754296</v>
+        <v>0.95080687142113485</v>
       </c>
       <c r="AV46" s="34">
         <v>1986</v>
@@ -8991,14 +8991,14 @@
       </c>
       <c r="AX46" s="17">
         <f t="shared" si="18"/>
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AY46" s="19">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="AZ46" s="18">
         <f t="shared" si="19"/>
-        <v>0.92044310171198385</v>
+        <v>0.92094662638469282</v>
       </c>
       <c r="BA46" s="36">
         <v>2072</v>
@@ -9008,14 +9008,14 @@
       </c>
       <c r="BC46" s="17">
         <f t="shared" si="20"/>
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="BD46" s="38">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="BE46" s="18">
         <f t="shared" si="21"/>
-        <v>1.0024131274131274</v>
+        <v>1.0028957528957529</v>
       </c>
       <c r="BF46" s="9">
         <v>4235</v>
@@ -9025,14 +9025,14 @@
       </c>
       <c r="BH46" s="17">
         <f t="shared" si="22"/>
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="BI46" s="19">
-        <v>4264</v>
+        <v>4265</v>
       </c>
       <c r="BJ46" s="18">
         <f t="shared" si="23"/>
-        <v>1.0068476977567886</v>
+        <v>1.0070838252656436</v>
       </c>
       <c r="BK46" s="2"/>
       <c r="BL46" s="2"/>
@@ -9252,10 +9252,10 @@
       <c r="BL47" s="2"/>
     </row>
     <row r="48" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A48" s="49" t="s">
+      <c r="A48" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="49"/>
+      <c r="B48" s="52"/>
       <c r="C48" s="27">
         <f>SUM(C10:C47)</f>
         <v>10414263</v>
@@ -9266,15 +9266,15 @@
       </c>
       <c r="E48" s="24">
         <f>F48-D48</f>
-        <v>8669671</v>
+        <v>8669698</v>
       </c>
       <c r="F48" s="25">
         <f>SUM(F10:F47)</f>
-        <v>9532840</v>
+        <v>9532867</v>
       </c>
       <c r="G48" s="26">
         <f>F48/C48</f>
-        <v>0.91536386204189391</v>
+        <v>0.9153664546401411</v>
       </c>
       <c r="H48" s="27">
         <f>SUM(H10:H47)</f>
@@ -9286,15 +9286,15 @@
       </c>
       <c r="J48" s="24">
         <f t="shared" si="2"/>
-        <v>7138757</v>
+        <v>7138779</v>
       </c>
       <c r="K48" s="25">
         <f>SUM(K10:K47)</f>
-        <v>9536269</v>
+        <v>9536291</v>
       </c>
       <c r="L48" s="26">
         <f t="shared" si="3"/>
-        <v>0.92201916113706039</v>
+        <v>0.92202128821857887</v>
       </c>
       <c r="M48" s="27">
         <f>SUM(M10:M47)</f>
@@ -9306,15 +9306,15 @@
       </c>
       <c r="O48" s="24">
         <f t="shared" si="4"/>
-        <v>6148798</v>
+        <v>6148828</v>
       </c>
       <c r="P48" s="25">
         <f>SUM(P10:P47)</f>
-        <v>9600079</v>
+        <v>9600109</v>
       </c>
       <c r="Q48" s="26">
         <f t="shared" si="5"/>
-        <v>0.92325327927729872</v>
+        <v>0.92325616442005409</v>
       </c>
       <c r="R48" s="27">
         <f>SUM(R10:R47)</f>
@@ -9326,15 +9326,15 @@
       </c>
       <c r="T48" s="24">
         <f t="shared" si="6"/>
-        <v>5911066</v>
+        <v>5911100</v>
       </c>
       <c r="U48" s="25">
         <f>SUM(U10:U47)</f>
-        <v>9713614</v>
+        <v>9713648</v>
       </c>
       <c r="V48" s="26">
         <f t="shared" si="7"/>
-        <v>0.91932790049588331</v>
+        <v>0.9193311183660412</v>
       </c>
       <c r="W48" s="27">
         <f>SUM(W10:W47)</f>
@@ -9346,15 +9346,15 @@
       </c>
       <c r="Y48" s="24">
         <f t="shared" si="8"/>
-        <v>4169201</v>
+        <v>4169242</v>
       </c>
       <c r="Z48" s="25">
         <f>SUM(Z10:Z47)</f>
-        <v>9814802</v>
+        <v>9814843</v>
       </c>
       <c r="AA48" s="26">
         <f t="shared" si="9"/>
-        <v>0.91688920634748627</v>
+        <v>0.91689303652739818</v>
       </c>
       <c r="AB48" s="27">
         <f>SUM(AB10:AB47)</f>
@@ -9366,15 +9366,15 @@
       </c>
       <c r="AD48" s="24">
         <f t="shared" si="10"/>
-        <v>2784132</v>
+        <v>2784174</v>
       </c>
       <c r="AE48" s="25">
         <f>SUM(AE10:AE47)</f>
-        <v>9901928</v>
+        <v>9901970</v>
       </c>
       <c r="AF48" s="26">
         <f t="shared" si="11"/>
-        <v>0.91253548288518138</v>
+        <v>0.91253935349404469</v>
       </c>
       <c r="AG48" s="23">
         <f>SUM(AG10:AG47)</f>
@@ -9386,15 +9386,15 @@
       </c>
       <c r="AI48" s="24">
         <f t="shared" si="12"/>
-        <v>2740639</v>
+        <v>2740683</v>
       </c>
       <c r="AJ48" s="25">
         <f>SUM(AJ10:AJ47)</f>
-        <v>10005609</v>
+        <v>10005653</v>
       </c>
       <c r="AK48" s="26">
         <f t="shared" si="13"/>
-        <v>0.91194102465855109</v>
+        <v>0.91194503494968726</v>
       </c>
       <c r="AL48" s="27">
         <f>SUM(AL10:AL47)</f>
@@ -9406,15 +9406,15 @@
       </c>
       <c r="AN48" s="24">
         <f t="shared" si="14"/>
-        <v>2318113</v>
+        <v>2318155</v>
       </c>
       <c r="AO48" s="25">
         <f>SUM(AO10:AO47)</f>
-        <v>10099874</v>
+        <v>10099916</v>
       </c>
       <c r="AP48" s="26">
         <f t="shared" si="15"/>
-        <v>0.91728909898199618</v>
+        <v>0.9172929134991038</v>
       </c>
       <c r="AQ48" s="27">
         <f>SUM(AQ10:AQ47)</f>
@@ -9426,15 +9426,15 @@
       </c>
       <c r="AS48" s="24">
         <f t="shared" si="16"/>
-        <v>1958683</v>
+        <v>1958722</v>
       </c>
       <c r="AT48" s="25">
         <f>SUM(AT10:AT47)</f>
-        <v>10194128</v>
+        <v>10194167</v>
       </c>
       <c r="AU48" s="26">
         <f t="shared" si="17"/>
-        <v>0.92807077502313773</v>
+        <v>0.92807432557304514</v>
       </c>
       <c r="AV48" s="27">
         <f>SUM(AV10:AV47)</f>
@@ -9446,15 +9446,15 @@
       </c>
       <c r="AX48" s="24">
         <f t="shared" si="18"/>
-        <v>1826787</v>
+        <v>1826821</v>
       </c>
       <c r="AY48" s="25">
         <f>SUM(AY10:AY47)</f>
-        <v>5622686</v>
+        <v>5622720</v>
       </c>
       <c r="AZ48" s="26">
         <f t="shared" si="19"/>
-        <v>0.89808318890205552</v>
+        <v>0.89808861955004526</v>
       </c>
       <c r="BA48" s="27">
         <f>SUM(BA10:BA47)</f>
@@ -9466,15 +9466,15 @@
       </c>
       <c r="BC48" s="24">
         <f t="shared" si="20"/>
-        <v>1571128</v>
+        <v>1571160</v>
       </c>
       <c r="BD48" s="25">
         <f>SUM(BD10:BD47)</f>
-        <v>5732000</v>
+        <v>5732032</v>
       </c>
       <c r="BE48" s="26">
         <f t="shared" si="21"/>
-        <v>0.93468047771760554</v>
+        <v>0.93468569575237292</v>
       </c>
       <c r="BF48" s="27">
         <f>SUM(BF10:BF47)</f>
@@ -9486,15 +9486,15 @@
       </c>
       <c r="BH48" s="24">
         <f t="shared" si="22"/>
-        <v>3236160</v>
+        <v>3236202</v>
       </c>
       <c r="BI48" s="25">
         <f>SUM(BI10:BI47)</f>
-        <v>10408084</v>
+        <v>10408126</v>
       </c>
       <c r="BJ48" s="26">
         <f t="shared" si="23"/>
-        <v>0.96553679302807915</v>
+        <v>0.96554068928269299</v>
       </c>
       <c r="BK48" s="10"/>
       <c r="BL48" s="10"/>
@@ -9504,25 +9504,17 @@
       <c r="AM57" s="4"/>
     </row>
     <row r="58" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A58" s="46" t="s">
+      <c r="A58" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="46"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="51"/>
       <c r="F58" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="BF8:BJ8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:L8"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9534,6 +9526,14 @@
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="BF8:BJ8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2020-2021.xlsx
+++ b/gstdatabase/GSTR-3B-2020-2021.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF21157-2E2A-40A5-8AC3-B87159334DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4A13C1-9E22-4FB9-BDEB-BD9713799451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,10 +188,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -487,8 +487,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -496,17 +496,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -799,7 +799,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BL58"/>
+  <dimension ref="A1:BL56"/>
   <sheetFormatPr defaultColWidth="12.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.44140625" bestFit="1" customWidth="1"/>
@@ -807,13 +807,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
     </row>
     <row r="2" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -823,10 +823,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="49"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -853,14 +853,14 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
     </row>
     <row r="8" spans="1:64" s="42" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="48" t="s">
@@ -952,7 +952,7 @@
       <c r="BJ8" s="48"/>
     </row>
     <row r="9" spans="1:64" s="42" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="50"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="48"/>
       <c r="C9" s="41" t="s">
         <v>3</v>
@@ -2142,14 +2142,14 @@
       </c>
       <c r="AS14" s="17">
         <f t="shared" si="16"/>
-        <v>25064</v>
+        <v>25066</v>
       </c>
       <c r="AT14" s="16">
-        <v>131362</v>
+        <v>131364</v>
       </c>
       <c r="AU14" s="18">
         <f t="shared" si="17"/>
-        <v>0.93664080771205294</v>
+        <v>0.93665506816496491</v>
       </c>
       <c r="AV14" s="34">
         <v>71169</v>
@@ -2159,14 +2159,14 @@
       </c>
       <c r="AX14" s="17">
         <f t="shared" si="18"/>
-        <v>24132</v>
+        <v>24134</v>
       </c>
       <c r="AY14" s="19">
-        <v>63726</v>
+        <v>63728</v>
       </c>
       <c r="AZ14" s="18">
         <f t="shared" si="19"/>
-        <v>0.89541794882603376</v>
+        <v>0.8954460509491492</v>
       </c>
       <c r="BA14" s="36">
         <v>69125</v>
@@ -2176,14 +2176,14 @@
       </c>
       <c r="BC14" s="17">
         <f t="shared" si="20"/>
-        <v>20954</v>
+        <v>20957</v>
       </c>
       <c r="BD14" s="38">
-        <v>65362</v>
+        <v>65365</v>
       </c>
       <c r="BE14" s="18">
         <f t="shared" si="21"/>
-        <v>0.94556238698010853</v>
+        <v>0.94560578661844485</v>
       </c>
       <c r="BF14" s="9">
         <v>138667</v>
@@ -2193,14 +2193,14 @@
       </c>
       <c r="BH14" s="17">
         <f t="shared" si="22"/>
-        <v>41161</v>
+        <v>41163</v>
       </c>
       <c r="BI14" s="19">
-        <v>134844</v>
+        <v>134846</v>
       </c>
       <c r="BJ14" s="18">
         <f t="shared" si="23"/>
-        <v>0.97243035473472417</v>
+        <v>0.97244477777697647</v>
       </c>
       <c r="BK14" s="2"/>
       <c r="BL14" s="2"/>
@@ -2648,14 +2648,14 @@
       </c>
       <c r="E17" s="17">
         <f t="shared" si="0"/>
-        <v>477733</v>
+        <v>477735</v>
       </c>
       <c r="F17" s="16">
-        <v>517790</v>
+        <v>517792</v>
       </c>
       <c r="G17" s="18">
         <f t="shared" si="1"/>
-        <v>0.93888260295632242</v>
+        <v>0.93888622945587996</v>
       </c>
       <c r="H17" s="7">
         <v>550123</v>
@@ -2665,14 +2665,14 @@
       </c>
       <c r="J17" s="17">
         <f t="shared" si="2"/>
-        <v>371933</v>
+        <v>371935</v>
       </c>
       <c r="K17" s="16">
-        <v>518975</v>
+        <v>518977</v>
       </c>
       <c r="L17" s="18">
         <f t="shared" si="3"/>
-        <v>0.94337993503271089</v>
+        <v>0.94338357058330591</v>
       </c>
       <c r="M17" s="7">
         <v>556868</v>
@@ -2682,14 +2682,14 @@
       </c>
       <c r="O17" s="17">
         <f t="shared" si="4"/>
-        <v>312464</v>
+        <v>312466</v>
       </c>
       <c r="P17" s="16">
-        <v>525546</v>
+        <v>525548</v>
       </c>
       <c r="Q17" s="18">
         <f t="shared" si="5"/>
-        <v>0.94375327725780611</v>
+        <v>0.94375686877321019</v>
       </c>
       <c r="R17" s="7">
         <v>565483</v>
@@ -2699,14 +2699,14 @@
       </c>
       <c r="T17" s="17">
         <f t="shared" si="6"/>
-        <v>303765</v>
+        <v>303767</v>
       </c>
       <c r="U17" s="16">
-        <v>534249</v>
+        <v>534251</v>
       </c>
       <c r="V17" s="18">
         <f t="shared" si="7"/>
-        <v>0.94476580197813198</v>
+        <v>0.94476933877764668</v>
       </c>
       <c r="W17" s="7">
         <v>572250</v>
@@ -2716,14 +2716,14 @@
       </c>
       <c r="Y17" s="17">
         <f t="shared" si="8"/>
-        <v>209897</v>
+        <v>209899</v>
       </c>
       <c r="Z17" s="16">
-        <v>540710</v>
+        <v>540712</v>
       </c>
       <c r="AA17" s="18">
         <f t="shared" si="9"/>
-        <v>0.94488422892092616</v>
+        <v>0.94488772389689824</v>
       </c>
       <c r="AB17" s="28">
         <v>582052</v>
@@ -2733,14 +2733,14 @@
       </c>
       <c r="AD17" s="17">
         <f t="shared" si="10"/>
-        <v>129251</v>
+        <v>129253</v>
       </c>
       <c r="AE17" s="40">
-        <v>547721</v>
+        <v>547723</v>
       </c>
       <c r="AF17" s="18">
         <f t="shared" si="11"/>
-        <v>0.94101729742359785</v>
+        <v>0.94102073354270754</v>
       </c>
       <c r="AG17" s="16">
         <v>590940</v>
@@ -2750,14 +2750,14 @@
       </c>
       <c r="AI17" s="17">
         <f t="shared" si="12"/>
-        <v>125629</v>
+        <v>125630</v>
       </c>
       <c r="AJ17" s="16">
-        <v>555070</v>
+        <v>555071</v>
       </c>
       <c r="AK17" s="18">
         <f t="shared" si="13"/>
-        <v>0.93930009814871218</v>
+        <v>0.93930179036788841</v>
       </c>
       <c r="AL17" s="30">
         <v>594928</v>
@@ -2767,14 +2767,14 @@
       </c>
       <c r="AN17" s="17">
         <f t="shared" si="14"/>
-        <v>105365</v>
+        <v>105366</v>
       </c>
       <c r="AO17" s="16">
-        <v>560904</v>
+        <v>560905</v>
       </c>
       <c r="AP17" s="18">
         <f t="shared" si="15"/>
-        <v>0.94280988623833473</v>
+        <v>0.94281156711400371</v>
       </c>
       <c r="AQ17" s="32">
         <v>594970</v>
@@ -2784,14 +2784,14 @@
       </c>
       <c r="AS17" s="17">
         <f t="shared" si="16"/>
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="AT17" s="16">
-        <v>566744</v>
+        <v>566746</v>
       </c>
       <c r="AU17" s="18">
         <f t="shared" si="17"/>
-        <v>0.95255895255222955</v>
+        <v>0.95256231406625547</v>
       </c>
       <c r="AV17" s="34">
         <v>254311</v>
@@ -2801,14 +2801,14 @@
       </c>
       <c r="AX17" s="17">
         <f t="shared" si="18"/>
-        <v>80419</v>
+        <v>80420</v>
       </c>
       <c r="AY17" s="19">
-        <v>233772</v>
+        <v>233773</v>
       </c>
       <c r="AZ17" s="18">
         <f t="shared" si="19"/>
-        <v>0.91923668264447866</v>
+        <v>0.919240614837738</v>
       </c>
       <c r="BA17" s="36">
         <v>253807</v>
@@ -2818,14 +2818,14 @@
       </c>
       <c r="BC17" s="17">
         <f t="shared" si="20"/>
-        <v>66016</v>
+        <v>66017</v>
       </c>
       <c r="BD17" s="38">
-        <v>242529</v>
+        <v>242530</v>
       </c>
       <c r="BE17" s="18">
         <f t="shared" si="21"/>
-        <v>0.95556466133715778</v>
+        <v>0.95556860133881261</v>
       </c>
       <c r="BF17" s="9">
         <v>590776</v>
@@ -2835,14 +2835,14 @@
       </c>
       <c r="BH17" s="17">
         <f t="shared" si="22"/>
-        <v>190042</v>
+        <v>190044</v>
       </c>
       <c r="BI17" s="19">
-        <v>582500</v>
+        <v>582502</v>
       </c>
       <c r="BJ17" s="18">
         <f t="shared" si="23"/>
-        <v>0.98599130634961474</v>
+        <v>0.98599469172749066</v>
       </c>
       <c r="BK17" s="2"/>
       <c r="BL17" s="2"/>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="T18" s="17">
         <f t="shared" si="6"/>
-        <v>637399</v>
+        <v>637400</v>
       </c>
       <c r="U18" s="16">
-        <v>1078360</v>
+        <v>1078361</v>
       </c>
       <c r="V18" s="18">
         <f t="shared" si="7"/>
-        <v>0.92671750739493686</v>
+        <v>0.92671836677168251</v>
       </c>
       <c r="W18" s="7">
         <v>1186115</v>
@@ -2981,14 +2981,14 @@
       </c>
       <c r="AN18" s="17">
         <f t="shared" si="14"/>
-        <v>215685</v>
+        <v>215686</v>
       </c>
       <c r="AO18" s="16">
-        <v>1138632</v>
+        <v>1138633</v>
       </c>
       <c r="AP18" s="18">
         <f t="shared" si="15"/>
-        <v>0.92137760935690682</v>
+        <v>0.92137841855391645</v>
       </c>
       <c r="AQ18" s="32">
         <v>1231355</v>
@@ -2998,14 +2998,14 @@
       </c>
       <c r="AS18" s="17">
         <f t="shared" si="16"/>
-        <v>183799</v>
+        <v>183800</v>
       </c>
       <c r="AT18" s="16">
-        <v>1149653</v>
+        <v>1149654</v>
       </c>
       <c r="AU18" s="18">
         <f t="shared" si="17"/>
-        <v>0.93364870406990674</v>
+        <v>0.93364951618339143</v>
       </c>
       <c r="AV18" s="34">
         <v>676084</v>
@@ -3015,14 +3015,14 @@
       </c>
       <c r="AX18" s="17">
         <f t="shared" si="18"/>
-        <v>184448</v>
+        <v>184449</v>
       </c>
       <c r="AY18" s="19">
-        <v>606980</v>
+        <v>606981</v>
       </c>
       <c r="AZ18" s="18">
         <f t="shared" si="19"/>
-        <v>0.89778784884718466</v>
+        <v>0.89778932795333122</v>
       </c>
       <c r="BA18" s="36">
         <v>651597</v>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="BC18" s="17">
         <f t="shared" si="20"/>
-        <v>154175</v>
+        <v>154177</v>
       </c>
       <c r="BD18" s="38">
-        <v>620516</v>
+        <v>620518</v>
       </c>
       <c r="BE18" s="18">
         <f t="shared" si="21"/>
-        <v>0.95230027148682395</v>
+        <v>0.95230334086866575</v>
       </c>
       <c r="BF18" s="9">
         <v>1203078</v>
@@ -3049,14 +3049,14 @@
       </c>
       <c r="BH18" s="17">
         <f t="shared" si="22"/>
-        <v>356598</v>
+        <v>356601</v>
       </c>
       <c r="BI18" s="19">
-        <v>1175746</v>
+        <v>1175749</v>
       </c>
       <c r="BJ18" s="18">
         <f t="shared" si="23"/>
-        <v>0.97728160601390768</v>
+        <v>0.9772840996178136</v>
       </c>
       <c r="BK18" s="2"/>
       <c r="BL18" s="2"/>
@@ -3110,14 +3110,14 @@
       </c>
       <c r="O19" s="17">
         <f t="shared" si="4"/>
-        <v>226819</v>
+        <v>226820</v>
       </c>
       <c r="P19" s="16">
-        <v>299515</v>
+        <v>299516</v>
       </c>
       <c r="Q19" s="18">
         <f t="shared" si="5"/>
-        <v>0.91652259061491148</v>
+        <v>0.91652565063724967</v>
       </c>
       <c r="R19" s="7">
         <v>336400</v>
@@ -3178,14 +3178,14 @@
       </c>
       <c r="AI19" s="17">
         <f t="shared" si="12"/>
-        <v>109289</v>
+        <v>109290</v>
       </c>
       <c r="AJ19" s="16">
-        <v>321346</v>
+        <v>321347</v>
       </c>
       <c r="AK19" s="18">
         <f t="shared" si="13"/>
-        <v>0.87887581263179204</v>
+        <v>0.87887854761468465</v>
       </c>
       <c r="AL19" s="30">
         <v>370137</v>
@@ -3195,14 +3195,14 @@
       </c>
       <c r="AN19" s="17">
         <f t="shared" si="14"/>
-        <v>84851</v>
+        <v>84853</v>
       </c>
       <c r="AO19" s="16">
-        <v>324812</v>
+        <v>324814</v>
       </c>
       <c r="AP19" s="18">
         <f t="shared" si="15"/>
-        <v>0.87754534131956541</v>
+        <v>0.87755074472425076</v>
       </c>
       <c r="AQ19" s="32">
         <v>372999</v>
@@ -3212,14 +3212,14 @@
       </c>
       <c r="AS19" s="17">
         <f t="shared" si="16"/>
-        <v>67757</v>
+        <v>67758</v>
       </c>
       <c r="AT19" s="16">
-        <v>329624</v>
+        <v>329625</v>
       </c>
       <c r="AU19" s="18">
         <f t="shared" si="17"/>
-        <v>0.88371282496735915</v>
+        <v>0.88371550593969417</v>
       </c>
       <c r="AV19" s="34">
         <v>223052</v>
@@ -3229,14 +3229,14 @@
       </c>
       <c r="AX19" s="17">
         <f t="shared" si="18"/>
-        <v>71736</v>
+        <v>71737</v>
       </c>
       <c r="AY19" s="19">
-        <v>180728</v>
+        <v>180729</v>
       </c>
       <c r="AZ19" s="18">
         <f t="shared" si="19"/>
-        <v>0.81025052454136259</v>
+        <v>0.81025500780087156</v>
       </c>
       <c r="BA19" s="36">
         <v>218640</v>
@@ -3246,14 +3246,14 @@
       </c>
       <c r="BC19" s="17">
         <f t="shared" si="20"/>
-        <v>58335</v>
+        <v>58336</v>
       </c>
       <c r="BD19" s="38">
-        <v>187542</v>
+        <v>187543</v>
       </c>
       <c r="BE19" s="18">
         <f t="shared" si="21"/>
-        <v>0.85776619099890228</v>
+        <v>0.85777076472740577</v>
       </c>
       <c r="BF19" s="9">
         <v>376756</v>
@@ -3263,14 +3263,14 @@
       </c>
       <c r="BH19" s="17">
         <f t="shared" si="22"/>
-        <v>121136</v>
+        <v>121137</v>
       </c>
       <c r="BI19" s="19">
-        <v>346119</v>
+        <v>346120</v>
       </c>
       <c r="BJ19" s="18">
         <f t="shared" si="23"/>
-        <v>0.91868211786939025</v>
+        <v>0.91868477210714627</v>
       </c>
       <c r="BK19" s="2"/>
       <c r="BL19" s="2"/>
@@ -3324,14 +3324,14 @@
       </c>
       <c r="O20" s="17">
         <f t="shared" si="4"/>
-        <v>4406</v>
+        <v>4407</v>
       </c>
       <c r="P20" s="16">
-        <v>6713</v>
+        <v>6714</v>
       </c>
       <c r="Q20" s="18">
         <f t="shared" si="5"/>
-        <v>0.88632162661737524</v>
+        <v>0.88645365724848169</v>
       </c>
       <c r="R20" s="7">
         <v>7650</v>
@@ -3504,14 +3504,14 @@
       </c>
       <c r="E21" s="17">
         <f t="shared" si="0"/>
-        <v>8230</v>
+        <v>8231</v>
       </c>
       <c r="F21" s="16">
-        <v>9548</v>
+        <v>9549</v>
       </c>
       <c r="G21" s="18">
         <f t="shared" si="1"/>
-        <v>0.76758581879572307</v>
+        <v>0.76766621111021782</v>
       </c>
       <c r="H21" s="7">
         <v>11980</v>
@@ -3521,14 +3521,14 @@
       </c>
       <c r="J21" s="17">
         <f t="shared" si="2"/>
-        <v>7503</v>
+        <v>7504</v>
       </c>
       <c r="K21" s="16">
-        <v>9527</v>
+        <v>9528</v>
       </c>
       <c r="L21" s="18">
         <f t="shared" si="3"/>
-        <v>0.79524207011686143</v>
+        <v>0.79532554257095156</v>
       </c>
       <c r="M21" s="7">
         <v>12071</v>
@@ -3538,14 +3538,14 @@
       </c>
       <c r="O21" s="17">
         <f t="shared" si="4"/>
-        <v>7109</v>
+        <v>7110</v>
       </c>
       <c r="P21" s="16">
-        <v>9573</v>
+        <v>9574</v>
       </c>
       <c r="Q21" s="18">
         <f t="shared" si="5"/>
-        <v>0.79305774169497145</v>
+        <v>0.79314058487283567</v>
       </c>
       <c r="R21" s="7">
         <v>12276</v>
@@ -3555,14 +3555,14 @@
       </c>
       <c r="T21" s="17">
         <f t="shared" si="6"/>
-        <v>6863</v>
+        <v>6864</v>
       </c>
       <c r="U21" s="16">
-        <v>9657</v>
+        <v>9658</v>
       </c>
       <c r="V21" s="18">
         <f t="shared" si="7"/>
-        <v>0.78665689149560114</v>
+        <v>0.78673835125448033</v>
       </c>
       <c r="W21" s="7">
         <v>12473</v>
@@ -3572,14 +3572,14 @@
       </c>
       <c r="Y21" s="17">
         <f t="shared" si="8"/>
-        <v>5673</v>
+        <v>5674</v>
       </c>
       <c r="Z21" s="16">
-        <v>9776</v>
+        <v>9777</v>
       </c>
       <c r="AA21" s="18">
         <f t="shared" si="9"/>
-        <v>0.78377294957107357</v>
+        <v>0.78385312274512953</v>
       </c>
       <c r="AB21" s="28">
         <v>12614</v>
@@ -3589,14 +3589,14 @@
       </c>
       <c r="AD21" s="17">
         <f t="shared" si="10"/>
-        <v>4748</v>
+        <v>4750</v>
       </c>
       <c r="AE21" s="40">
-        <v>9796</v>
+        <v>9798</v>
       </c>
       <c r="AF21" s="18">
         <f t="shared" si="11"/>
-        <v>0.77659743142540039</v>
+        <v>0.77675598541303315</v>
       </c>
       <c r="AG21" s="16">
         <v>12787</v>
@@ -3606,14 +3606,14 @@
       </c>
       <c r="AI21" s="17">
         <f t="shared" si="12"/>
-        <v>4522</v>
+        <v>4525</v>
       </c>
       <c r="AJ21" s="16">
-        <v>9911</v>
+        <v>9914</v>
       </c>
       <c r="AK21" s="18">
         <f t="shared" si="13"/>
-        <v>0.77508406975834832</v>
+        <v>0.77531868303745988</v>
       </c>
       <c r="AL21" s="30">
         <v>12973</v>
@@ -3623,14 +3623,14 @@
       </c>
       <c r="AN21" s="17">
         <f t="shared" si="14"/>
-        <v>4374</v>
+        <v>4377</v>
       </c>
       <c r="AO21" s="16">
-        <v>10026</v>
+        <v>10029</v>
       </c>
       <c r="AP21" s="18">
         <f t="shared" si="15"/>
-        <v>0.77283588992522934</v>
+        <v>0.77306713944345951</v>
       </c>
       <c r="AQ21" s="32">
         <v>13123</v>
@@ -3640,14 +3640,14 @@
       </c>
       <c r="AS21" s="17">
         <f t="shared" si="16"/>
-        <v>3834</v>
+        <v>3837</v>
       </c>
       <c r="AT21" s="16">
-        <v>10130</v>
+        <v>10133</v>
       </c>
       <c r="AU21" s="18">
         <f t="shared" si="17"/>
-        <v>0.77192715080393204</v>
+        <v>0.77215575706774364</v>
       </c>
       <c r="AV21" s="34">
         <v>9471</v>
@@ -3657,14 +3657,14 @@
       </c>
       <c r="AX21" s="17">
         <f t="shared" si="18"/>
-        <v>3521</v>
+        <v>3524</v>
       </c>
       <c r="AY21" s="19">
-        <v>6629</v>
+        <v>6632</v>
       </c>
       <c r="AZ21" s="18">
         <f t="shared" si="19"/>
-        <v>0.69992609016999263</v>
+        <v>0.70024284658431002</v>
       </c>
       <c r="BA21" s="36">
         <v>9338</v>
@@ -3674,14 +3674,14 @@
       </c>
       <c r="BC21" s="17">
         <f t="shared" si="20"/>
-        <v>3254</v>
+        <v>3257</v>
       </c>
       <c r="BD21" s="38">
-        <v>6745</v>
+        <v>6748</v>
       </c>
       <c r="BE21" s="18">
         <f t="shared" si="21"/>
-        <v>0.72231741272221028</v>
+        <v>0.72263868065967019</v>
       </c>
       <c r="BF21" s="9">
         <v>12705</v>
@@ -3691,14 +3691,14 @@
       </c>
       <c r="BH21" s="17">
         <f t="shared" si="22"/>
-        <v>5106</v>
+        <v>5108</v>
       </c>
       <c r="BI21" s="19">
-        <v>10389</v>
+        <v>10391</v>
       </c>
       <c r="BJ21" s="18">
         <f t="shared" si="23"/>
-        <v>0.81770956316410859</v>
+        <v>0.81786698150334514</v>
       </c>
       <c r="BK21" s="2"/>
       <c r="BL21" s="2"/>
@@ -3769,14 +3769,14 @@
       </c>
       <c r="T22" s="17">
         <f t="shared" si="6"/>
-        <v>3930</v>
+        <v>3931</v>
       </c>
       <c r="U22" s="16">
-        <v>5689</v>
+        <v>5690</v>
       </c>
       <c r="V22" s="18">
         <f t="shared" si="7"/>
-        <v>0.84531946508172362</v>
+        <v>0.84546805349182763</v>
       </c>
       <c r="W22" s="7">
         <v>6785</v>
@@ -4119,14 +4119,14 @@
       </c>
       <c r="BH23" s="17">
         <f t="shared" si="22"/>
-        <v>4114</v>
+        <v>4115</v>
       </c>
       <c r="BI23" s="19">
-        <v>8770</v>
+        <v>8771</v>
       </c>
       <c r="BJ23" s="18">
         <f t="shared" si="23"/>
-        <v>0.79799818016378521</v>
+        <v>0.79808917197452234</v>
       </c>
       <c r="BK23" s="2"/>
       <c r="BL23" s="2"/>
@@ -4146,14 +4146,14 @@
       </c>
       <c r="E24" s="17">
         <f t="shared" si="0"/>
-        <v>3475</v>
+        <v>3477</v>
       </c>
       <c r="F24" s="16">
-        <v>4789</v>
+        <v>4791</v>
       </c>
       <c r="G24" s="18">
         <f t="shared" si="1"/>
-        <v>0.76993569131832795</v>
+        <v>0.77025723472668806</v>
       </c>
       <c r="H24" s="7">
         <v>6236</v>
@@ -4163,14 +4163,14 @@
       </c>
       <c r="J24" s="17">
         <f t="shared" si="2"/>
-        <v>3105</v>
+        <v>3107</v>
       </c>
       <c r="K24" s="16">
-        <v>4806</v>
+        <v>4808</v>
       </c>
       <c r="L24" s="18">
         <f t="shared" si="3"/>
-        <v>0.77068633739576653</v>
+        <v>0.77100705580500317</v>
       </c>
       <c r="M24" s="7">
         <v>6293</v>
@@ -4180,14 +4180,14 @@
       </c>
       <c r="O24" s="17">
         <f t="shared" si="4"/>
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="P24" s="16">
-        <v>4835</v>
+        <v>4836</v>
       </c>
       <c r="Q24" s="18">
         <f t="shared" si="5"/>
-        <v>0.76831399968218661</v>
+        <v>0.76847290640394084</v>
       </c>
       <c r="R24" s="7">
         <v>6429</v>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="T24" s="17">
         <f t="shared" si="6"/>
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="U24" s="16">
-        <v>4911</v>
+        <v>4912</v>
       </c>
       <c r="V24" s="18">
         <f t="shared" si="7"/>
-        <v>0.76388240783947736</v>
+        <v>0.76403795302535382</v>
       </c>
       <c r="W24" s="7">
         <v>6586</v>
@@ -4214,14 +4214,14 @@
       </c>
       <c r="Y24" s="17">
         <f t="shared" si="8"/>
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="Z24" s="16">
-        <v>4974</v>
+        <v>4977</v>
       </c>
       <c r="AA24" s="18">
         <f t="shared" si="9"/>
-        <v>0.75523838445186764</v>
+        <v>0.75569389614333438</v>
       </c>
       <c r="AB24" s="28">
         <v>6663</v>
@@ -4231,14 +4231,14 @@
       </c>
       <c r="AD24" s="17">
         <f t="shared" si="10"/>
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="AE24" s="40">
-        <v>4974</v>
+        <v>4976</v>
       </c>
       <c r="AF24" s="18">
         <f t="shared" si="11"/>
-        <v>0.74651058081945065</v>
+        <v>0.74681074591025065</v>
       </c>
       <c r="AG24" s="16">
         <v>6801</v>
@@ -4248,14 +4248,14 @@
       </c>
       <c r="AI24" s="17">
         <f t="shared" si="12"/>
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="AJ24" s="16">
-        <v>5043</v>
+        <v>5044</v>
       </c>
       <c r="AK24" s="18">
         <f t="shared" si="13"/>
-        <v>0.74150860167622412</v>
+        <v>0.74165563887663577</v>
       </c>
       <c r="AL24" s="30">
         <v>6877</v>
@@ -4265,14 +4265,14 @@
       </c>
       <c r="AN24" s="17">
         <f t="shared" si="14"/>
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="AO24" s="16">
-        <v>5146</v>
+        <v>5148</v>
       </c>
       <c r="AP24" s="18">
         <f t="shared" si="15"/>
-        <v>0.74829140613639666</v>
+        <v>0.74858223062381857</v>
       </c>
       <c r="AQ24" s="32">
         <v>6826</v>
@@ -4282,14 +4282,14 @@
       </c>
       <c r="AS24" s="17">
         <f t="shared" si="16"/>
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="AT24" s="16">
-        <v>5270</v>
+        <v>5271</v>
       </c>
       <c r="AU24" s="18">
         <f t="shared" si="17"/>
-        <v>0.77204805156753586</v>
+        <v>0.77219455024904771</v>
       </c>
       <c r="AV24" s="34">
         <v>5390</v>
@@ -4299,14 +4299,14 @@
       </c>
       <c r="AX24" s="17">
         <f t="shared" si="18"/>
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="AY24" s="19">
-        <v>3933</v>
+        <v>3934</v>
       </c>
       <c r="AZ24" s="18">
         <f t="shared" si="19"/>
-        <v>0.72968460111317257</v>
+        <v>0.72987012987012989</v>
       </c>
       <c r="BA24" s="36">
         <v>5128</v>
@@ -4316,14 +4316,14 @@
       </c>
       <c r="BC24" s="17">
         <f t="shared" si="20"/>
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="BD24" s="38">
-        <v>4023</v>
+        <v>4024</v>
       </c>
       <c r="BE24" s="18">
         <f t="shared" si="21"/>
-        <v>0.78451638065522622</v>
+        <v>0.78471138845553823</v>
       </c>
       <c r="BF24" s="9">
         <v>6600</v>
@@ -4333,14 +4333,14 @@
       </c>
       <c r="BH24" s="17">
         <f t="shared" si="22"/>
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="BI24" s="19">
-        <v>5462</v>
+        <v>5463</v>
       </c>
       <c r="BJ24" s="18">
         <f t="shared" si="23"/>
-        <v>0.82757575757575763</v>
+        <v>0.82772727272727276</v>
       </c>
       <c r="BK24" s="2"/>
       <c r="BL24" s="2"/>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="E27" s="17">
         <f t="shared" si="0"/>
-        <v>115193</v>
+        <v>115195</v>
       </c>
       <c r="F27" s="16">
-        <v>129451</v>
+        <v>129453</v>
       </c>
       <c r="G27" s="18">
         <f t="shared" si="1"/>
-        <v>0.88859219802170497</v>
+        <v>0.88860592664795002</v>
       </c>
       <c r="H27" s="7">
         <v>145010</v>
@@ -4805,14 +4805,14 @@
       </c>
       <c r="J27" s="17">
         <f t="shared" si="2"/>
-        <v>98113</v>
+        <v>98116</v>
       </c>
       <c r="K27" s="16">
-        <v>129425</v>
+        <v>129428</v>
       </c>
       <c r="L27" s="18">
         <f t="shared" si="3"/>
-        <v>0.89252465347217436</v>
+        <v>0.89254534170057243</v>
       </c>
       <c r="M27" s="7">
         <v>146684</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="O27" s="17">
         <f t="shared" si="4"/>
-        <v>98018</v>
+        <v>98020</v>
       </c>
       <c r="P27" s="16">
-        <v>130614</v>
+        <v>130616</v>
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="5"/>
-        <v>0.89044476561860875</v>
+        <v>0.89045840037086521</v>
       </c>
       <c r="R27" s="7">
         <v>151002</v>
@@ -4839,14 +4839,14 @@
       </c>
       <c r="T27" s="17">
         <f t="shared" si="6"/>
-        <v>96122</v>
+        <v>96124</v>
       </c>
       <c r="U27" s="16">
-        <v>133163</v>
+        <v>133165</v>
       </c>
       <c r="V27" s="18">
         <f t="shared" si="7"/>
-        <v>0.88186249188752464</v>
+        <v>0.88187573674520869</v>
       </c>
       <c r="W27" s="7">
         <v>153079</v>
@@ -4856,14 +4856,14 @@
       </c>
       <c r="Y27" s="17">
         <f t="shared" si="8"/>
-        <v>73995</v>
+        <v>73997</v>
       </c>
       <c r="Z27" s="16">
-        <v>135048</v>
+        <v>135050</v>
       </c>
       <c r="AA27" s="18">
         <f t="shared" si="9"/>
-        <v>0.88221114587892524</v>
+        <v>0.88222421102829263</v>
       </c>
       <c r="AB27" s="28">
         <v>156081</v>
@@ -4873,14 +4873,14 @@
       </c>
       <c r="AD27" s="17">
         <f t="shared" si="10"/>
-        <v>52683</v>
+        <v>52686</v>
       </c>
       <c r="AE27" s="40">
-        <v>135658</v>
+        <v>135661</v>
       </c>
       <c r="AF27" s="18">
         <f t="shared" si="11"/>
-        <v>0.86915127401797787</v>
+        <v>0.86917049480718345</v>
       </c>
       <c r="AG27" s="16">
         <v>159400</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="AI27" s="17">
         <f t="shared" si="12"/>
-        <v>49918</v>
+        <v>49922</v>
       </c>
       <c r="AJ27" s="16">
-        <v>137429</v>
+        <v>137433</v>
       </c>
       <c r="AK27" s="18">
         <f t="shared" si="13"/>
-        <v>0.86216436637390215</v>
+        <v>0.86218946047678791</v>
       </c>
       <c r="AL27" s="30">
         <v>161009</v>
@@ -4907,14 +4907,14 @@
       </c>
       <c r="AN27" s="17">
         <f t="shared" si="14"/>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="AO27" s="16">
-        <v>138966</v>
+        <v>138970</v>
       </c>
       <c r="AP27" s="18">
         <f t="shared" si="15"/>
-        <v>0.86309460961809592</v>
+        <v>0.86311945294983505</v>
       </c>
       <c r="AQ27" s="32">
         <v>161396</v>
@@ -4924,14 +4924,14 @@
       </c>
       <c r="AS27" s="17">
         <f t="shared" si="16"/>
-        <v>42501</v>
+        <v>42505</v>
       </c>
       <c r="AT27" s="16">
-        <v>140875</v>
+        <v>140879</v>
       </c>
       <c r="AU27" s="18">
         <f t="shared" si="17"/>
-        <v>0.87285310664452653</v>
+        <v>0.87287789040620589</v>
       </c>
       <c r="AV27" s="34">
         <v>108346</v>
@@ -4941,14 +4941,14 @@
       </c>
       <c r="AX27" s="17">
         <f t="shared" si="18"/>
-        <v>41827</v>
+        <v>41832</v>
       </c>
       <c r="AY27" s="19">
-        <v>89128</v>
+        <v>89133</v>
       </c>
       <c r="AZ27" s="18">
         <f t="shared" si="19"/>
-        <v>0.8226238162922489</v>
+        <v>0.82266996474258391</v>
       </c>
       <c r="BA27" s="36">
         <v>101792</v>
@@ -4958,14 +4958,14 @@
       </c>
       <c r="BC27" s="17">
         <f t="shared" si="20"/>
-        <v>36649</v>
+        <v>36654</v>
       </c>
       <c r="BD27" s="38">
-        <v>91023</v>
+        <v>91028</v>
       </c>
       <c r="BE27" s="18">
         <f t="shared" si="21"/>
-        <v>0.89420583149952848</v>
+        <v>0.89425495127318455</v>
       </c>
       <c r="BF27" s="9">
         <v>155251</v>
@@ -4975,14 +4975,14 @@
       </c>
       <c r="BH27" s="17">
         <f t="shared" si="22"/>
-        <v>64494</v>
+        <v>64498</v>
       </c>
       <c r="BI27" s="19">
-        <v>145219</v>
+        <v>145223</v>
       </c>
       <c r="BJ27" s="18">
         <f t="shared" si="23"/>
-        <v>0.93538205873070057</v>
+        <v>0.93540782346007434</v>
       </c>
       <c r="BK27" s="2"/>
       <c r="BL27" s="2"/>
@@ -5002,14 +5002,14 @@
       </c>
       <c r="E28" s="17">
         <f t="shared" si="0"/>
-        <v>501101</v>
+        <v>501102</v>
       </c>
       <c r="F28" s="16">
-        <v>545525</v>
+        <v>545526</v>
       </c>
       <c r="G28" s="18">
         <f t="shared" si="1"/>
-        <v>0.89257811541299681</v>
+        <v>0.89257975159486824</v>
       </c>
       <c r="H28" s="7">
         <v>606429</v>
@@ -5019,14 +5019,14 @@
       </c>
       <c r="J28" s="17">
         <f t="shared" si="2"/>
-        <v>399819</v>
+        <v>399820</v>
       </c>
       <c r="K28" s="16">
-        <v>544361</v>
+        <v>544362</v>
       </c>
       <c r="L28" s="18">
         <f t="shared" si="3"/>
-        <v>0.89765001343933093</v>
+        <v>0.89765166243698769</v>
       </c>
       <c r="M28" s="7">
         <v>606073</v>
@@ -5036,14 +5036,14 @@
       </c>
       <c r="O28" s="17">
         <f t="shared" si="4"/>
-        <v>359411</v>
+        <v>359413</v>
       </c>
       <c r="P28" s="16">
-        <v>545061</v>
+        <v>545063</v>
       </c>
       <c r="Q28" s="18">
         <f t="shared" si="5"/>
-        <v>0.89933225865531052</v>
+        <v>0.89933555858782688</v>
       </c>
       <c r="R28" s="7">
         <v>610188</v>
@@ -5053,14 +5053,14 @@
       </c>
       <c r="T28" s="17">
         <f t="shared" si="6"/>
-        <v>358945</v>
+        <v>358947</v>
       </c>
       <c r="U28" s="16">
-        <v>548644</v>
+        <v>548646</v>
       </c>
       <c r="V28" s="18">
         <f t="shared" si="7"/>
-        <v>0.8991392816640118</v>
+        <v>0.89914255934236664</v>
       </c>
       <c r="W28" s="7">
         <v>613926</v>
@@ -5070,14 +5070,14 @@
       </c>
       <c r="Y28" s="17">
         <f t="shared" si="8"/>
-        <v>240227</v>
+        <v>240229</v>
       </c>
       <c r="Z28" s="16">
-        <v>551015</v>
+        <v>551017</v>
       </c>
       <c r="AA28" s="18">
         <f t="shared" si="9"/>
-        <v>0.89752673775015235</v>
+        <v>0.89752999547176693</v>
       </c>
       <c r="AB28" s="28">
         <v>616763</v>
@@ -5087,14 +5087,14 @@
       </c>
       <c r="AD28" s="17">
         <f t="shared" si="10"/>
-        <v>147650</v>
+        <v>147652</v>
       </c>
       <c r="AE28" s="40">
-        <v>552218</v>
+        <v>552220</v>
       </c>
       <c r="AF28" s="18">
         <f t="shared" si="11"/>
-        <v>0.89534878064994172</v>
+        <v>0.8953520233866169</v>
       </c>
       <c r="AG28" s="16">
         <v>621241</v>
@@ -5104,14 +5104,14 @@
       </c>
       <c r="AI28" s="17">
         <f t="shared" si="12"/>
-        <v>134845</v>
+        <v>134848</v>
       </c>
       <c r="AJ28" s="16">
-        <v>554817</v>
+        <v>554820</v>
       </c>
       <c r="AK28" s="18">
         <f t="shared" si="13"/>
-        <v>0.89307853151997374</v>
+        <v>0.8930833605637748</v>
       </c>
       <c r="AL28" s="30">
         <v>624748</v>
@@ -5121,14 +5121,14 @@
       </c>
       <c r="AN28" s="17">
         <f t="shared" si="14"/>
-        <v>120282</v>
+        <v>120284</v>
       </c>
       <c r="AO28" s="16">
-        <v>558526</v>
+        <v>558528</v>
       </c>
       <c r="AP28" s="18">
         <f t="shared" si="15"/>
-        <v>0.89400206163124973</v>
+        <v>0.8940052629220101</v>
       </c>
       <c r="AQ28" s="32">
         <v>625592</v>
@@ -5138,14 +5138,14 @@
       </c>
       <c r="AS28" s="17">
         <f t="shared" si="16"/>
-        <v>106904</v>
+        <v>106906</v>
       </c>
       <c r="AT28" s="16">
-        <v>561985</v>
+        <v>561987</v>
       </c>
       <c r="AU28" s="18">
         <f t="shared" si="17"/>
-        <v>0.89832510645916186</v>
+        <v>0.89832830343099013</v>
       </c>
       <c r="AV28" s="34">
         <v>329721</v>
@@ -5155,14 +5155,14 @@
       </c>
       <c r="AX28" s="17">
         <f t="shared" si="18"/>
-        <v>102398</v>
+        <v>102399</v>
       </c>
       <c r="AY28" s="19">
-        <v>269586</v>
+        <v>269587</v>
       </c>
       <c r="AZ28" s="18">
         <f t="shared" si="19"/>
-        <v>0.81761853203162671</v>
+        <v>0.81762156489880844</v>
       </c>
       <c r="BA28" s="36">
         <v>323065</v>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="BC28" s="17">
         <f t="shared" si="20"/>
-        <v>82764</v>
+        <v>82765</v>
       </c>
       <c r="BD28" s="38">
-        <v>273174</v>
+        <v>273175</v>
       </c>
       <c r="BE28" s="18">
         <f t="shared" si="21"/>
-        <v>0.84556977697986468</v>
+        <v>0.84557287233219325</v>
       </c>
       <c r="BF28" s="9">
         <v>619161</v>
@@ -5189,14 +5189,14 @@
       </c>
       <c r="BH28" s="17">
         <f t="shared" si="22"/>
-        <v>148335</v>
+        <v>148336</v>
       </c>
       <c r="BI28" s="19">
-        <v>569190</v>
+        <v>569191</v>
       </c>
       <c r="BJ28" s="18">
         <f t="shared" si="23"/>
-        <v>0.91929239729246515</v>
+        <v>0.91929401238127073</v>
       </c>
       <c r="BK28" s="2"/>
       <c r="BL28" s="2"/>
@@ -5233,14 +5233,14 @@
       </c>
       <c r="J29" s="17">
         <f t="shared" si="2"/>
-        <v>99271</v>
+        <v>99272</v>
       </c>
       <c r="K29" s="16">
-        <v>136273</v>
+        <v>136274</v>
       </c>
       <c r="L29" s="18">
         <f t="shared" si="3"/>
-        <v>0.9514609879560133</v>
+        <v>0.95146796997730843</v>
       </c>
       <c r="M29" s="7">
         <v>144577</v>
@@ -5250,14 +5250,14 @@
       </c>
       <c r="O29" s="17">
         <f t="shared" si="4"/>
-        <v>89075</v>
+        <v>89076</v>
       </c>
       <c r="P29" s="16">
-        <v>137276</v>
+        <v>137277</v>
       </c>
       <c r="Q29" s="18">
         <f t="shared" si="5"/>
-        <v>0.94950095796703482</v>
+        <v>0.94950787469652853</v>
       </c>
       <c r="R29" s="7">
         <v>147922</v>
@@ -5267,14 +5267,14 @@
       </c>
       <c r="T29" s="17">
         <f t="shared" si="6"/>
-        <v>88486</v>
+        <v>88487</v>
       </c>
       <c r="U29" s="16">
-        <v>139450</v>
+        <v>139451</v>
       </c>
       <c r="V29" s="18">
         <f t="shared" si="7"/>
-        <v>0.94272657211232946</v>
+        <v>0.94273333243195734</v>
       </c>
       <c r="W29" s="7">
         <v>150500</v>
@@ -5284,14 +5284,14 @@
       </c>
       <c r="Y29" s="17">
         <f t="shared" si="8"/>
-        <v>62366</v>
+        <v>62367</v>
       </c>
       <c r="Z29" s="16">
-        <v>141021</v>
+        <v>141022</v>
       </c>
       <c r="AA29" s="18">
         <f t="shared" si="9"/>
-        <v>0.93701661129568103</v>
+        <v>0.93702325581395352</v>
       </c>
       <c r="AB29" s="28">
         <v>153397</v>
@@ -5301,14 +5301,14 @@
       </c>
       <c r="AD29" s="17">
         <f t="shared" si="10"/>
-        <v>41367</v>
+        <v>41368</v>
       </c>
       <c r="AE29" s="40">
-        <v>142312</v>
+        <v>142313</v>
       </c>
       <c r="AF29" s="18">
         <f t="shared" si="11"/>
-        <v>0.92773652678996332</v>
+        <v>0.92774304582227818</v>
       </c>
       <c r="AG29" s="16">
         <v>155748</v>
@@ -5318,14 +5318,14 @@
       </c>
       <c r="AI29" s="17">
         <f t="shared" si="12"/>
-        <v>43500</v>
+        <v>43501</v>
       </c>
       <c r="AJ29" s="16">
-        <v>143736</v>
+        <v>143737</v>
       </c>
       <c r="AK29" s="18">
         <f t="shared" si="13"/>
-        <v>0.92287541413051855</v>
+        <v>0.92288183475871277</v>
       </c>
       <c r="AL29" s="30">
         <v>156900</v>
@@ -5335,14 +5335,14 @@
       </c>
       <c r="AN29" s="17">
         <f t="shared" si="14"/>
-        <v>34159</v>
+        <v>34160</v>
       </c>
       <c r="AO29" s="16">
-        <v>145141</v>
+        <v>145142</v>
       </c>
       <c r="AP29" s="18">
         <f t="shared" si="15"/>
-        <v>0.92505417463352457</v>
+        <v>0.92506054811982152</v>
       </c>
       <c r="AQ29" s="32">
         <v>155521</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="AS29" s="17">
         <f t="shared" si="16"/>
-        <v>29251</v>
+        <v>29252</v>
       </c>
       <c r="AT29" s="16">
-        <v>146580</v>
+        <v>146581</v>
       </c>
       <c r="AU29" s="18">
         <f t="shared" si="17"/>
-        <v>0.94250937172471883</v>
+        <v>0.94251580172452598</v>
       </c>
       <c r="AV29" s="34">
         <v>96011</v>
@@ -5369,14 +5369,14 @@
       </c>
       <c r="AX29" s="17">
         <f t="shared" si="18"/>
-        <v>30576</v>
+        <v>30577</v>
       </c>
       <c r="AY29" s="19">
-        <v>88073</v>
+        <v>88074</v>
       </c>
       <c r="AZ29" s="18">
         <f t="shared" si="19"/>
-        <v>0.91732197352386702</v>
+        <v>0.91733238899709413</v>
       </c>
       <c r="BA29" s="36">
         <v>92769</v>
@@ -5386,14 +5386,14 @@
       </c>
       <c r="BC29" s="17">
         <f t="shared" si="20"/>
-        <v>25150</v>
+        <v>25151</v>
       </c>
       <c r="BD29" s="38">
-        <v>89472</v>
+        <v>89473</v>
       </c>
       <c r="BE29" s="18">
         <f t="shared" si="21"/>
-        <v>0.96446011059729009</v>
+        <v>0.96447089006025721</v>
       </c>
       <c r="BF29" s="9">
         <v>153057</v>
@@ -5403,14 +5403,14 @@
       </c>
       <c r="BH29" s="17">
         <f t="shared" si="22"/>
-        <v>51524</v>
+        <v>51525</v>
       </c>
       <c r="BI29" s="19">
-        <v>149841</v>
+        <v>149842</v>
       </c>
       <c r="BJ29" s="18">
         <f t="shared" si="23"/>
-        <v>0.97898822007487407</v>
+        <v>0.97899475358853238</v>
       </c>
       <c r="BK29" s="2"/>
       <c r="BL29" s="2"/>
@@ -5430,14 +5430,14 @@
       </c>
       <c r="E30" s="17">
         <f t="shared" si="0"/>
-        <v>183092</v>
+        <v>183094</v>
       </c>
       <c r="F30" s="16">
-        <v>212367</v>
+        <v>212369</v>
       </c>
       <c r="G30" s="18">
         <f t="shared" si="1"/>
-        <v>0.95282684481853541</v>
+        <v>0.952835818216896</v>
       </c>
       <c r="H30" s="7">
         <v>223846</v>
@@ -5447,14 +5447,14 @@
       </c>
       <c r="J30" s="17">
         <f t="shared" si="2"/>
-        <v>151620</v>
+        <v>151622</v>
       </c>
       <c r="K30" s="16">
-        <v>213098</v>
+        <v>213100</v>
       </c>
       <c r="L30" s="18">
         <f t="shared" si="3"/>
-        <v>0.95198484672498052</v>
+        <v>0.95199378143902502</v>
       </c>
       <c r="M30" s="7">
         <v>227236</v>
@@ -5464,14 +5464,14 @@
       </c>
       <c r="O30" s="17">
         <f t="shared" si="4"/>
-        <v>148654</v>
+        <v>148656</v>
       </c>
       <c r="P30" s="16">
-        <v>215565</v>
+        <v>215567</v>
       </c>
       <c r="Q30" s="18">
         <f t="shared" si="5"/>
-        <v>0.94863930011089792</v>
+        <v>0.94864810153320778</v>
       </c>
       <c r="R30" s="7">
         <v>232779</v>
@@ -5481,14 +5481,14 @@
       </c>
       <c r="T30" s="17">
         <f t="shared" si="6"/>
-        <v>146419</v>
+        <v>146421</v>
       </c>
       <c r="U30" s="16">
-        <v>218440</v>
+        <v>218442</v>
       </c>
       <c r="V30" s="18">
         <f t="shared" si="7"/>
-        <v>0.93840080075951871</v>
+        <v>0.9384093925998479</v>
       </c>
       <c r="W30" s="7">
         <v>236990</v>
@@ -5498,14 +5498,14 @@
       </c>
       <c r="Y30" s="17">
         <f t="shared" si="8"/>
-        <v>97443</v>
+        <v>97446</v>
       </c>
       <c r="Z30" s="16">
-        <v>220886</v>
+        <v>220889</v>
       </c>
       <c r="AA30" s="18">
         <f t="shared" si="9"/>
-        <v>0.93204776572851178</v>
+        <v>0.93206042449048487</v>
       </c>
       <c r="AB30" s="28">
         <v>242455</v>
@@ -5515,14 +5515,14 @@
       </c>
       <c r="AD30" s="17">
         <f t="shared" si="10"/>
-        <v>59887</v>
+        <v>59890</v>
       </c>
       <c r="AE30" s="40">
-        <v>223571</v>
+        <v>223574</v>
       </c>
       <c r="AF30" s="18">
         <f t="shared" si="11"/>
-        <v>0.92211338186467595</v>
+        <v>0.92212575529479701</v>
       </c>
       <c r="AG30" s="16">
         <v>245898</v>
@@ -5532,14 +5532,14 @@
       </c>
       <c r="AI30" s="17">
         <f t="shared" si="12"/>
-        <v>55599</v>
+        <v>55602</v>
       </c>
       <c r="AJ30" s="16">
-        <v>226479</v>
+        <v>226482</v>
       </c>
       <c r="AK30" s="18">
         <f t="shared" si="13"/>
-        <v>0.92102823121782207</v>
+        <v>0.92104043139838465</v>
       </c>
       <c r="AL30" s="30">
         <v>247799</v>
@@ -5549,14 +5549,14 @@
       </c>
       <c r="AN30" s="17">
         <f t="shared" si="14"/>
-        <v>51261</v>
+        <v>51263</v>
       </c>
       <c r="AO30" s="16">
-        <v>229606</v>
+        <v>229608</v>
       </c>
       <c r="AP30" s="18">
         <f t="shared" si="15"/>
-        <v>0.9265816246231825</v>
+        <v>0.92658969568077354</v>
       </c>
       <c r="AQ30" s="32">
         <v>248265</v>
@@ -5566,14 +5566,14 @@
       </c>
       <c r="AS30" s="17">
         <f t="shared" si="16"/>
-        <v>46754</v>
+        <v>46756</v>
       </c>
       <c r="AT30" s="16">
-        <v>232659</v>
+        <v>232661</v>
       </c>
       <c r="AU30" s="18">
         <f t="shared" si="17"/>
-        <v>0.93713974986405657</v>
+        <v>0.93714780577205803</v>
       </c>
       <c r="AV30" s="34">
         <v>136662</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="AX30" s="17">
         <f t="shared" si="18"/>
-        <v>48128</v>
+        <v>48129</v>
       </c>
       <c r="AY30" s="19">
-        <v>121218</v>
+        <v>121219</v>
       </c>
       <c r="AZ30" s="18">
         <f t="shared" si="19"/>
-        <v>0.8869912631163015</v>
+        <v>0.88699858043933211</v>
       </c>
       <c r="BA30" s="36">
         <v>130439</v>
@@ -5644,14 +5644,14 @@
       </c>
       <c r="E31" s="17">
         <f t="shared" si="0"/>
-        <v>91678</v>
+        <v>91679</v>
       </c>
       <c r="F31" s="16">
-        <v>101336</v>
+        <v>101337</v>
       </c>
       <c r="G31" s="18">
         <f t="shared" si="1"/>
-        <v>0.9478272256205923</v>
+        <v>0.94783657893259998</v>
       </c>
       <c r="H31" s="7">
         <v>106827</v>
@@ -5661,14 +5661,14 @@
       </c>
       <c r="J31" s="17">
         <f t="shared" si="2"/>
-        <v>81396</v>
+        <v>81397</v>
       </c>
       <c r="K31" s="16">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="L31" s="18">
         <f t="shared" si="3"/>
-        <v>0.95033090885263094</v>
+        <v>0.95034026978198394</v>
       </c>
       <c r="M31" s="7">
         <v>107995</v>
@@ -5678,14 +5678,14 @@
       </c>
       <c r="O31" s="17">
         <f t="shared" si="4"/>
-        <v>67608</v>
+        <v>67609</v>
       </c>
       <c r="P31" s="16">
-        <v>102503</v>
+        <v>102504</v>
       </c>
       <c r="Q31" s="18">
         <f t="shared" si="5"/>
-        <v>0.94914579378674935</v>
+        <v>0.94915505347469786</v>
       </c>
       <c r="R31" s="7">
         <v>110315</v>
@@ -5695,14 +5695,14 @@
       </c>
       <c r="T31" s="17">
         <f t="shared" si="6"/>
-        <v>69318</v>
+        <v>69319</v>
       </c>
       <c r="U31" s="16">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="V31" s="18">
         <f t="shared" si="7"/>
-        <v>0.94406019127045282</v>
+        <v>0.94406925622082216</v>
       </c>
       <c r="W31" s="7">
         <v>111481</v>
@@ -5712,14 +5712,14 @@
       </c>
       <c r="Y31" s="17">
         <f t="shared" si="8"/>
-        <v>58150</v>
+        <v>58151</v>
       </c>
       <c r="Z31" s="16">
-        <v>105283</v>
+        <v>105284</v>
       </c>
       <c r="AA31" s="18">
         <f t="shared" si="9"/>
-        <v>0.94440308213955737</v>
+        <v>0.94441205227796665</v>
       </c>
       <c r="AB31" s="28">
         <v>113499</v>
@@ -5729,14 +5729,14 @@
       </c>
       <c r="AD31" s="17">
         <f t="shared" si="10"/>
-        <v>42490</v>
+        <v>42491</v>
       </c>
       <c r="AE31" s="40">
-        <v>106237</v>
+        <v>106238</v>
       </c>
       <c r="AF31" s="18">
         <f t="shared" si="11"/>
-        <v>0.93601705741900809</v>
+        <v>0.9360258680693222</v>
       </c>
       <c r="AG31" s="16">
         <v>114692</v>
@@ -5746,14 +5746,14 @@
       </c>
       <c r="AI31" s="17">
         <f t="shared" si="12"/>
-        <v>42964</v>
+        <v>42965</v>
       </c>
       <c r="AJ31" s="16">
-        <v>107135</v>
+        <v>107136</v>
       </c>
       <c r="AK31" s="18">
         <f t="shared" si="13"/>
-        <v>0.93411048721794021</v>
+        <v>0.93411920622188116</v>
       </c>
       <c r="AL31" s="30">
         <v>115249</v>
@@ -5763,14 +5763,14 @@
       </c>
       <c r="AN31" s="17">
         <f t="shared" si="14"/>
-        <v>37326</v>
+        <v>37327</v>
       </c>
       <c r="AO31" s="16">
-        <v>108067</v>
+        <v>108068</v>
       </c>
       <c r="AP31" s="18">
         <f t="shared" si="15"/>
-        <v>0.93768275646643351</v>
+        <v>0.93769143333130878</v>
       </c>
       <c r="AQ31" s="32">
         <v>115872</v>
@@ -5858,14 +5858,14 @@
       </c>
       <c r="E32" s="17">
         <f t="shared" si="0"/>
-        <v>317972</v>
+        <v>317973</v>
       </c>
       <c r="F32" s="16">
-        <v>342988</v>
+        <v>342989</v>
       </c>
       <c r="G32" s="18">
         <f t="shared" si="1"/>
-        <v>0.97690103617793322</v>
+        <v>0.9769038843855562</v>
       </c>
       <c r="H32" s="7">
         <v>350849</v>
@@ -5875,14 +5875,14 @@
       </c>
       <c r="J32" s="17">
         <f t="shared" si="2"/>
-        <v>270151</v>
+        <v>270152</v>
       </c>
       <c r="K32" s="16">
-        <v>343247</v>
+        <v>343248</v>
       </c>
       <c r="L32" s="18">
         <f t="shared" si="3"/>
-        <v>0.97833255902111738</v>
+        <v>0.97833540925013329</v>
       </c>
       <c r="M32" s="7">
         <v>353115</v>
@@ -5892,14 +5892,14 @@
       </c>
       <c r="O32" s="17">
         <f t="shared" si="4"/>
-        <v>225960</v>
+        <v>225961</v>
       </c>
       <c r="P32" s="16">
-        <v>345638</v>
+        <v>345639</v>
       </c>
       <c r="Q32" s="18">
         <f t="shared" si="5"/>
-        <v>0.97882559506109912</v>
+        <v>0.97882842699970263</v>
       </c>
       <c r="R32" s="7">
         <v>360296</v>
@@ -5909,14 +5909,14 @@
       </c>
       <c r="T32" s="17">
         <f t="shared" si="6"/>
-        <v>217457</v>
+        <v>217458</v>
       </c>
       <c r="U32" s="16">
-        <v>350015</v>
+        <v>350016</v>
       </c>
       <c r="V32" s="18">
         <f t="shared" si="7"/>
-        <v>0.97146512867198087</v>
+        <v>0.97146790416768436</v>
       </c>
       <c r="W32" s="7">
         <v>365792</v>
@@ -5943,14 +5943,14 @@
       </c>
       <c r="AD32" s="17">
         <f t="shared" si="10"/>
-        <v>102607</v>
+        <v>102608</v>
       </c>
       <c r="AE32" s="40">
-        <v>357463</v>
+        <v>357464</v>
       </c>
       <c r="AF32" s="18">
         <f t="shared" si="11"/>
-        <v>0.95495103198816</v>
+        <v>0.95495370345634556</v>
       </c>
       <c r="AG32" s="16">
         <v>378033</v>
@@ -6072,14 +6072,14 @@
       </c>
       <c r="E33" s="17">
         <f t="shared" si="0"/>
-        <v>808067</v>
+        <v>808071</v>
       </c>
       <c r="F33" s="16">
-        <v>845888</v>
+        <v>845892</v>
       </c>
       <c r="G33" s="18">
         <f t="shared" si="1"/>
-        <v>0.94788624755433137</v>
+        <v>0.94789072987940304</v>
       </c>
       <c r="H33" s="7">
         <v>888497</v>
@@ -6089,14 +6089,14 @@
       </c>
       <c r="J33" s="17">
         <f t="shared" si="2"/>
-        <v>639078</v>
+        <v>639082</v>
       </c>
       <c r="K33" s="16">
-        <v>846057</v>
+        <v>846061</v>
       </c>
       <c r="L33" s="18">
         <f t="shared" si="3"/>
-        <v>0.95223394113879956</v>
+        <v>0.95223844312361217</v>
       </c>
       <c r="M33" s="7">
         <v>888717</v>
@@ -6106,14 +6106,14 @@
       </c>
       <c r="O33" s="17">
         <f t="shared" si="4"/>
-        <v>454204</v>
+        <v>454208</v>
       </c>
       <c r="P33" s="16">
-        <v>850267</v>
+        <v>850271</v>
       </c>
       <c r="Q33" s="18">
         <f t="shared" si="5"/>
-        <v>0.95673538370482392</v>
+        <v>0.95673988457517978</v>
       </c>
       <c r="R33" s="7">
         <v>899174</v>
@@ -6123,14 +6123,14 @@
       </c>
       <c r="T33" s="17">
         <f t="shared" si="6"/>
-        <v>425246</v>
+        <v>425251</v>
       </c>
       <c r="U33" s="16">
-        <v>858921</v>
+        <v>858926</v>
       </c>
       <c r="V33" s="18">
         <f t="shared" si="7"/>
-        <v>0.95523335861579628</v>
+        <v>0.95523891927480109</v>
       </c>
       <c r="W33" s="7">
         <v>909355</v>
@@ -6140,14 +6140,14 @@
       </c>
       <c r="Y33" s="17">
         <f t="shared" si="8"/>
-        <v>280856</v>
+        <v>280860</v>
       </c>
       <c r="Z33" s="16">
-        <v>867296</v>
+        <v>867300</v>
       </c>
       <c r="AA33" s="18">
         <f t="shared" si="9"/>
-        <v>0.95374853605027743</v>
+        <v>0.9537529347724486</v>
       </c>
       <c r="AB33" s="28">
         <v>919225</v>
@@ -6157,14 +6157,14 @@
       </c>
       <c r="AD33" s="17">
         <f t="shared" si="10"/>
-        <v>196757</v>
+        <v>196760</v>
       </c>
       <c r="AE33" s="40">
-        <v>876681</v>
+        <v>876684</v>
       </c>
       <c r="AF33" s="18">
         <f t="shared" si="11"/>
-        <v>0.95371753379205304</v>
+        <v>0.95372079741086246</v>
       </c>
       <c r="AG33" s="16">
         <v>928340</v>
@@ -6174,14 +6174,14 @@
       </c>
       <c r="AI33" s="17">
         <f t="shared" si="12"/>
-        <v>235383</v>
+        <v>235386</v>
       </c>
       <c r="AJ33" s="16">
-        <v>884848</v>
+        <v>884851</v>
       </c>
       <c r="AK33" s="18">
         <f t="shared" si="13"/>
-        <v>0.95315078527263719</v>
+        <v>0.95315401684727574</v>
       </c>
       <c r="AL33" s="30">
         <v>932930</v>
@@ -6191,14 +6191,14 @@
       </c>
       <c r="AN33" s="17">
         <f t="shared" si="14"/>
-        <v>167615</v>
+        <v>167617</v>
       </c>
       <c r="AO33" s="16">
-        <v>892491</v>
+        <v>892493</v>
       </c>
       <c r="AP33" s="18">
         <f t="shared" si="15"/>
-        <v>0.95665376823555892</v>
+        <v>0.95665591201912259</v>
       </c>
       <c r="AQ33" s="32">
         <v>933808</v>
@@ -6208,14 +6208,14 @@
       </c>
       <c r="AS33" s="17">
         <f t="shared" si="16"/>
-        <v>132955</v>
+        <v>132958</v>
       </c>
       <c r="AT33" s="16">
-        <v>901473</v>
+        <v>901476</v>
       </c>
       <c r="AU33" s="18">
         <f t="shared" si="17"/>
-        <v>0.96537296746226209</v>
+        <v>0.96537618011411341</v>
       </c>
       <c r="AV33" s="34">
         <v>471009</v>
@@ -6225,14 +6225,14 @@
       </c>
       <c r="AX33" s="17">
         <f t="shared" si="18"/>
-        <v>112008</v>
+        <v>112010</v>
       </c>
       <c r="AY33" s="19">
-        <v>443842</v>
+        <v>443844</v>
       </c>
       <c r="AZ33" s="18">
         <f t="shared" si="19"/>
-        <v>0.9423216966130159</v>
+        <v>0.94232594281637927</v>
       </c>
       <c r="BA33" s="36">
         <v>469149</v>
@@ -6242,14 +6242,14 @@
       </c>
       <c r="BC33" s="17">
         <f t="shared" si="20"/>
-        <v>98007</v>
+        <v>98010</v>
       </c>
       <c r="BD33" s="38">
-        <v>454670</v>
+        <v>454673</v>
       </c>
       <c r="BE33" s="18">
         <f t="shared" si="21"/>
-        <v>0.96913773662525127</v>
+        <v>0.96914413118220433</v>
       </c>
       <c r="BF33" s="9">
         <v>935950</v>
@@ -6259,14 +6259,14 @@
       </c>
       <c r="BH33" s="17">
         <f t="shared" si="22"/>
-        <v>222957</v>
+        <v>222961</v>
       </c>
       <c r="BI33" s="19">
-        <v>922573</v>
+        <v>922577</v>
       </c>
       <c r="BJ33" s="18">
         <f t="shared" si="23"/>
-        <v>0.98570756984881669</v>
+        <v>0.98571184358138786</v>
       </c>
       <c r="BK33" s="2"/>
       <c r="BL33" s="2"/>
@@ -6698,14 +6698,14 @@
       </c>
       <c r="E36" s="17">
         <f t="shared" si="0"/>
-        <v>1190288</v>
+        <v>1190292</v>
       </c>
       <c r="F36" s="16">
-        <v>1261903</v>
+        <v>1261907</v>
       </c>
       <c r="G36" s="18">
         <f t="shared" si="1"/>
-        <v>0.91463322707696415</v>
+        <v>0.91463612629576962</v>
       </c>
       <c r="H36" s="7">
         <v>1370063</v>
@@ -6715,14 +6715,14 @@
       </c>
       <c r="J36" s="17">
         <f t="shared" si="2"/>
-        <v>1054971</v>
+        <v>1054975</v>
       </c>
       <c r="K36" s="16">
-        <v>1261866</v>
+        <v>1261870</v>
       </c>
       <c r="L36" s="18">
         <f t="shared" si="3"/>
-        <v>0.9210277191632793</v>
+        <v>0.92103063873705082</v>
       </c>
       <c r="M36" s="7">
         <v>1376699</v>
@@ -6732,14 +6732,14 @@
       </c>
       <c r="O36" s="17">
         <f t="shared" si="4"/>
-        <v>909595</v>
+        <v>909598</v>
       </c>
       <c r="P36" s="16">
-        <v>1267352</v>
+        <v>1267355</v>
       </c>
       <c r="Q36" s="18">
         <f t="shared" si="5"/>
-        <v>0.92057305191621408</v>
+        <v>0.92057523104178907</v>
       </c>
       <c r="R36" s="7">
         <v>1386159</v>
@@ -6749,14 +6749,14 @@
       </c>
       <c r="T36" s="17">
         <f t="shared" si="6"/>
-        <v>856805</v>
+        <v>856808</v>
       </c>
       <c r="U36" s="16">
-        <v>1274722</v>
+        <v>1274725</v>
       </c>
       <c r="V36" s="18">
         <f t="shared" si="7"/>
-        <v>0.91960734663195198</v>
+        <v>0.91960951088583631</v>
       </c>
       <c r="W36" s="7">
         <v>1395892</v>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="Y36" s="17">
         <f t="shared" si="8"/>
-        <v>663046</v>
+        <v>663049</v>
       </c>
       <c r="Z36" s="16">
-        <v>1283929</v>
+        <v>1283932</v>
       </c>
       <c r="AA36" s="18">
         <f t="shared" si="9"/>
-        <v>0.91979107266178184</v>
+        <v>0.91979322182518419</v>
       </c>
       <c r="AB36" s="28">
         <v>1408098</v>
@@ -6783,14 +6783,14 @@
       </c>
       <c r="AD36" s="17">
         <f t="shared" si="10"/>
-        <v>434758</v>
+        <v>434762</v>
       </c>
       <c r="AE36" s="40">
-        <v>1290858</v>
+        <v>1290862</v>
       </c>
       <c r="AF36" s="18">
         <f t="shared" si="11"/>
-        <v>0.9167387497177043</v>
+        <v>0.91674159042907521</v>
       </c>
       <c r="AG36" s="16">
         <v>1413160</v>
@@ -6800,14 +6800,14 @@
       </c>
       <c r="AI36" s="17">
         <f t="shared" si="12"/>
-        <v>420939</v>
+        <v>420944</v>
       </c>
       <c r="AJ36" s="16">
-        <v>1299768</v>
+        <v>1299773</v>
       </c>
       <c r="AK36" s="18">
         <f t="shared" si="13"/>
-        <v>0.91975997056242742</v>
+        <v>0.91976350873220303</v>
       </c>
       <c r="AL36" s="30">
         <v>1410829</v>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="AN36" s="17">
         <f t="shared" si="14"/>
-        <v>358682</v>
+        <v>358687</v>
       </c>
       <c r="AO36" s="16">
-        <v>1310050</v>
+        <v>1310055</v>
       </c>
       <c r="AP36" s="18">
         <f t="shared" si="15"/>
-        <v>0.92856753015425686</v>
+        <v>0.92857107416986751</v>
       </c>
       <c r="AQ36" s="32">
         <v>1406326</v>
@@ -6834,14 +6834,14 @@
       </c>
       <c r="AS36" s="17">
         <f t="shared" si="16"/>
-        <v>299739</v>
+        <v>299744</v>
       </c>
       <c r="AT36" s="16">
-        <v>1321862</v>
+        <v>1321867</v>
       </c>
       <c r="AU36" s="18">
         <f t="shared" si="17"/>
-        <v>0.93993995702276711</v>
+        <v>0.93994351238617502</v>
       </c>
       <c r="AV36" s="34">
         <v>685252</v>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="AX36" s="17">
         <f t="shared" si="18"/>
-        <v>251679</v>
+        <v>251684</v>
       </c>
       <c r="AY36" s="19">
-        <v>635321</v>
+        <v>635326</v>
       </c>
       <c r="AZ36" s="18">
         <f t="shared" si="19"/>
-        <v>0.927134835067975</v>
+        <v>0.92714213165375658</v>
       </c>
       <c r="BA36" s="36">
         <v>667048</v>
@@ -6868,14 +6868,14 @@
       </c>
       <c r="BC36" s="17">
         <f t="shared" si="20"/>
-        <v>222480</v>
+        <v>222486</v>
       </c>
       <c r="BD36" s="38">
-        <v>648499</v>
+        <v>648505</v>
       </c>
       <c r="BE36" s="18">
         <f t="shared" si="21"/>
-        <v>0.97219240594380019</v>
+        <v>0.97220140079874307</v>
       </c>
       <c r="BF36" s="9">
         <v>1363993</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="BH36" s="17">
         <f t="shared" si="22"/>
-        <v>477187</v>
+        <v>477192</v>
       </c>
       <c r="BI36" s="19">
-        <v>1343312</v>
+        <v>1343317</v>
       </c>
       <c r="BJ36" s="18">
         <f t="shared" si="23"/>
-        <v>0.98483789872821925</v>
+        <v>0.98484156443618109</v>
       </c>
       <c r="BK36" s="2"/>
       <c r="BL36" s="2"/>
@@ -6963,14 +6963,14 @@
       </c>
       <c r="T37" s="17">
         <f t="shared" si="6"/>
-        <v>392170</v>
+        <v>392171</v>
       </c>
       <c r="U37" s="16">
-        <v>689286</v>
+        <v>689287</v>
       </c>
       <c r="V37" s="18">
         <f t="shared" si="7"/>
-        <v>0.92275501447816366</v>
+        <v>0.92275635318954685</v>
       </c>
       <c r="W37" s="7">
         <v>758127</v>
@@ -6997,14 +6997,14 @@
       </c>
       <c r="AD37" s="17">
         <f t="shared" si="10"/>
-        <v>196242</v>
+        <v>196243</v>
       </c>
       <c r="AE37" s="40">
-        <v>701724</v>
+        <v>701725</v>
       </c>
       <c r="AF37" s="18">
         <f t="shared" si="11"/>
-        <v>0.9130848904387654</v>
+        <v>0.91308619164107641</v>
       </c>
       <c r="AG37" s="16">
         <v>770579</v>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="AI37" s="17">
         <f t="shared" si="12"/>
-        <v>189648</v>
+        <v>189649</v>
       </c>
       <c r="AJ37" s="16">
-        <v>707549</v>
+        <v>707550</v>
       </c>
       <c r="AK37" s="18">
         <f t="shared" si="13"/>
-        <v>0.91820436321259724</v>
+        <v>0.91820566093807388</v>
       </c>
       <c r="AL37" s="30">
         <v>769439</v>
@@ -7031,14 +7031,14 @@
       </c>
       <c r="AN37" s="17">
         <f t="shared" si="14"/>
-        <v>166239</v>
+        <v>166240</v>
       </c>
       <c r="AO37" s="16">
-        <v>715096</v>
+        <v>715097</v>
       </c>
       <c r="AP37" s="18">
         <f t="shared" si="15"/>
-        <v>0.92937321866970612</v>
+        <v>0.92937451831789131</v>
       </c>
       <c r="AQ37" s="32">
         <v>769503</v>
@@ -7065,14 +7065,14 @@
       </c>
       <c r="AX37" s="17">
         <f t="shared" si="18"/>
-        <v>135681</v>
+        <v>135682</v>
       </c>
       <c r="AY37" s="19">
-        <v>487948</v>
+        <v>487949</v>
       </c>
       <c r="AZ37" s="18">
         <f t="shared" si="19"/>
-        <v>0.92669234333811923</v>
+        <v>0.92669424250020893</v>
       </c>
       <c r="BA37" s="36">
         <v>525083</v>
@@ -7554,14 +7554,14 @@
       </c>
       <c r="E40" s="17">
         <f t="shared" si="0"/>
-        <v>254695</v>
+        <v>254696</v>
       </c>
       <c r="F40" s="16">
-        <v>278450</v>
+        <v>278451</v>
       </c>
       <c r="G40" s="18">
         <f t="shared" si="1"/>
-        <v>0.91725741843672592</v>
+        <v>0.91726071259157749</v>
       </c>
       <c r="H40" s="7">
         <v>301693</v>
@@ -7571,14 +7571,14 @@
       </c>
       <c r="J40" s="17">
         <f t="shared" si="2"/>
-        <v>226112</v>
+        <v>226113</v>
       </c>
       <c r="K40" s="16">
-        <v>278736</v>
+        <v>278737</v>
       </c>
       <c r="L40" s="18">
         <f t="shared" si="3"/>
-        <v>0.92390608996562729</v>
+        <v>0.9239094045934112</v>
       </c>
       <c r="M40" s="7">
         <v>303033</v>
@@ -7588,14 +7588,14 @@
       </c>
       <c r="O40" s="17">
         <f t="shared" si="4"/>
-        <v>207452</v>
+        <v>207453</v>
       </c>
       <c r="P40" s="16">
-        <v>280637</v>
+        <v>280638</v>
       </c>
       <c r="Q40" s="18">
         <f t="shared" si="5"/>
-        <v>0.92609385776466591</v>
+        <v>0.92609715773529611</v>
       </c>
       <c r="R40" s="7">
         <v>305881</v>
@@ -7605,14 +7605,14 @@
       </c>
       <c r="T40" s="17">
         <f t="shared" si="6"/>
-        <v>201466</v>
+        <v>201467</v>
       </c>
       <c r="U40" s="16">
-        <v>282762</v>
+        <v>282763</v>
       </c>
       <c r="V40" s="18">
         <f t="shared" si="7"/>
-        <v>0.92441831954256726</v>
+        <v>0.92442158878779657</v>
       </c>
       <c r="W40" s="7">
         <v>309941</v>
@@ -7622,14 +7622,14 @@
       </c>
       <c r="Y40" s="17">
         <f t="shared" si="8"/>
-        <v>162286</v>
+        <v>162287</v>
       </c>
       <c r="Z40" s="16">
-        <v>286103</v>
+        <v>286104</v>
       </c>
       <c r="AA40" s="18">
         <f t="shared" si="9"/>
-        <v>0.92308858782800596</v>
+        <v>0.92309181424851827</v>
       </c>
       <c r="AB40" s="28">
         <v>313197</v>
@@ -7639,14 +7639,14 @@
       </c>
       <c r="AD40" s="17">
         <f t="shared" si="10"/>
-        <v>108207</v>
+        <v>108208</v>
       </c>
       <c r="AE40" s="40">
-        <v>288286</v>
+        <v>288287</v>
       </c>
       <c r="AF40" s="18">
         <f t="shared" si="11"/>
-        <v>0.92046220110665178</v>
+        <v>0.92046539398525529</v>
       </c>
       <c r="AG40" s="16">
         <v>316872</v>
@@ -7656,14 +7656,14 @@
       </c>
       <c r="AI40" s="17">
         <f t="shared" si="12"/>
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="AJ40" s="16">
-        <v>291257</v>
+        <v>291258</v>
       </c>
       <c r="AK40" s="18">
         <f t="shared" si="13"/>
-        <v>0.91916294276553312</v>
+        <v>0.91916609861395138</v>
       </c>
       <c r="AL40" s="30">
         <v>319591</v>
@@ -7673,14 +7673,14 @@
       </c>
       <c r="AN40" s="17">
         <f t="shared" si="14"/>
-        <v>85458</v>
+        <v>85459</v>
       </c>
       <c r="AO40" s="16">
-        <v>294971</v>
+        <v>294972</v>
       </c>
       <c r="AP40" s="18">
         <f t="shared" si="15"/>
-        <v>0.9229640384115948</v>
+        <v>0.92296716741084694</v>
       </c>
       <c r="AQ40" s="32">
         <v>320883</v>
@@ -7690,14 +7690,14 @@
       </c>
       <c r="AS40" s="17">
         <f t="shared" si="16"/>
-        <v>70110</v>
+        <v>70111</v>
       </c>
       <c r="AT40" s="16">
-        <v>298157</v>
+        <v>298158</v>
       </c>
       <c r="AU40" s="18">
         <f t="shared" si="17"/>
-        <v>0.92917667810385718</v>
+        <v>0.92917979450453903</v>
       </c>
       <c r="AV40" s="34">
         <v>237285</v>
@@ -7707,14 +7707,14 @@
       </c>
       <c r="AX40" s="17">
         <f t="shared" si="18"/>
-        <v>72825</v>
+        <v>72826</v>
       </c>
       <c r="AY40" s="19">
-        <v>218387</v>
+        <v>218388</v>
       </c>
       <c r="AZ40" s="18">
         <f t="shared" si="19"/>
-        <v>0.92035737615104196</v>
+        <v>0.92036159049244581</v>
       </c>
       <c r="BA40" s="36">
         <v>231667</v>
@@ -7724,14 +7724,14 @@
       </c>
       <c r="BC40" s="17">
         <f t="shared" si="20"/>
-        <v>66787</v>
+        <v>66788</v>
       </c>
       <c r="BD40" s="38">
-        <v>220885</v>
+        <v>220886</v>
       </c>
       <c r="BE40" s="18">
         <f t="shared" si="21"/>
-        <v>0.95345905977113699</v>
+        <v>0.95346337631168876</v>
       </c>
       <c r="BF40" s="9">
         <v>314391</v>
@@ -7741,14 +7741,14 @@
       </c>
       <c r="BH40" s="17">
         <f t="shared" si="22"/>
-        <v>110215</v>
+        <v>110216</v>
       </c>
       <c r="BI40" s="19">
-        <v>305164</v>
+        <v>305165</v>
       </c>
       <c r="BJ40" s="18">
         <f t="shared" si="23"/>
-        <v>0.97065119548587586</v>
+        <v>0.97065437623850559</v>
       </c>
       <c r="BK40" s="2"/>
       <c r="BL40" s="2"/>
@@ -7768,14 +7768,14 @@
       </c>
       <c r="E41" s="17">
         <f t="shared" si="0"/>
-        <v>721662</v>
+        <v>721682</v>
       </c>
       <c r="F41" s="16">
-        <v>811844</v>
+        <v>811864</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="1"/>
-        <v>0.92693609305851776</v>
+        <v>0.92695892838385263</v>
       </c>
       <c r="H41" s="7">
         <v>872102</v>
@@ -7785,14 +7785,14 @@
       </c>
       <c r="J41" s="17">
         <f t="shared" si="2"/>
-        <v>601140</v>
+        <v>601156</v>
       </c>
       <c r="K41" s="16">
-        <v>812791</v>
+        <v>812807</v>
       </c>
       <c r="L41" s="18">
         <f t="shared" si="3"/>
-        <v>0.93199075337517856</v>
+        <v>0.93200909985299885</v>
       </c>
       <c r="M41" s="7">
         <v>879453</v>
@@ -7802,14 +7802,14 @@
       </c>
       <c r="O41" s="17">
         <f t="shared" si="4"/>
-        <v>529797</v>
+        <v>529817</v>
       </c>
       <c r="P41" s="16">
-        <v>817883</v>
+        <v>817903</v>
       </c>
       <c r="Q41" s="18">
         <f t="shared" si="5"/>
-        <v>0.92999057368614357</v>
+        <v>0.93001331509472362</v>
       </c>
       <c r="R41" s="7">
         <v>900135</v>
@@ -7819,14 +7819,14 @@
       </c>
       <c r="T41" s="17">
         <f t="shared" si="6"/>
-        <v>493879</v>
+        <v>493899</v>
       </c>
       <c r="U41" s="16">
-        <v>829344</v>
+        <v>829364</v>
       </c>
       <c r="V41" s="18">
         <f t="shared" si="7"/>
-        <v>0.92135513006382375</v>
+        <v>0.92137734895321255</v>
       </c>
       <c r="W41" s="7">
         <v>916182</v>
@@ -7836,14 +7836,14 @@
       </c>
       <c r="Y41" s="17">
         <f t="shared" si="8"/>
-        <v>333120</v>
+        <v>333137</v>
       </c>
       <c r="Z41" s="16">
-        <v>837166</v>
+        <v>837183</v>
       </c>
       <c r="AA41" s="18">
         <f t="shared" si="9"/>
-        <v>0.91375512725637487</v>
+        <v>0.91377368252159508</v>
       </c>
       <c r="AB41" s="28">
         <v>928683</v>
@@ -7853,14 +7853,14 @@
       </c>
       <c r="AD41" s="17">
         <f t="shared" si="10"/>
-        <v>228068</v>
+        <v>228087</v>
       </c>
       <c r="AE41" s="40">
-        <v>842855</v>
+        <v>842874</v>
       </c>
       <c r="AF41" s="18">
         <f t="shared" si="11"/>
-        <v>0.90758095065808242</v>
+        <v>0.90760140973830683</v>
       </c>
       <c r="AG41" s="16">
         <v>933135</v>
@@ -7870,14 +7870,14 @@
       </c>
       <c r="AI41" s="17">
         <f t="shared" si="12"/>
-        <v>223150</v>
+        <v>223169</v>
       </c>
       <c r="AJ41" s="16">
-        <v>851098</v>
+        <v>851117</v>
       </c>
       <c r="AK41" s="18">
         <f t="shared" si="13"/>
-        <v>0.91208453224881714</v>
+        <v>0.91210489371848658</v>
       </c>
       <c r="AL41" s="30">
         <v>933314</v>
@@ -7887,14 +7887,14 @@
       </c>
       <c r="AN41" s="17">
         <f t="shared" si="14"/>
-        <v>186868</v>
+        <v>186885</v>
       </c>
       <c r="AO41" s="16">
-        <v>858751</v>
+        <v>858768</v>
       </c>
       <c r="AP41" s="18">
         <f t="shared" si="15"/>
-        <v>0.92010941655220002</v>
+        <v>0.92012763121521801</v>
       </c>
       <c r="AQ41" s="32">
         <v>923873</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="AS41" s="17">
         <f t="shared" si="16"/>
-        <v>168486</v>
+        <v>168501</v>
       </c>
       <c r="AT41" s="16">
-        <v>867881</v>
+        <v>867896</v>
       </c>
       <c r="AU41" s="18">
         <f t="shared" si="17"/>
-        <v>0.93939426739389509</v>
+        <v>0.93941050339169996</v>
       </c>
       <c r="AV41" s="34">
         <v>726285</v>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="AX41" s="17">
         <f t="shared" si="18"/>
-        <v>161046</v>
+        <v>161063</v>
       </c>
       <c r="AY41" s="19">
-        <v>680683</v>
+        <v>680700</v>
       </c>
       <c r="AZ41" s="18">
         <f t="shared" si="19"/>
-        <v>0.93721197601492523</v>
+        <v>0.9372353828042711</v>
       </c>
       <c r="BA41" s="36">
         <v>715063</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="BC41" s="17">
         <f t="shared" si="20"/>
-        <v>142455</v>
+        <v>142471</v>
       </c>
       <c r="BD41" s="38">
-        <v>688362</v>
+        <v>688378</v>
       </c>
       <c r="BE41" s="18">
         <f t="shared" si="21"/>
-        <v>0.96265923422132038</v>
+        <v>0.96268160987213713</v>
       </c>
       <c r="BF41" s="9">
         <v>910875</v>
@@ -7955,14 +7955,14 @@
       </c>
       <c r="BH41" s="17">
         <f t="shared" si="22"/>
-        <v>228687</v>
+        <v>228695</v>
       </c>
       <c r="BI41" s="19">
-        <v>887996</v>
+        <v>888004</v>
       </c>
       <c r="BJ41" s="18">
         <f t="shared" si="23"/>
-        <v>0.97488239330314264</v>
+        <v>0.97489117606696862</v>
       </c>
       <c r="BK41" s="2"/>
       <c r="BL41" s="2"/>
@@ -8118,14 +8118,14 @@
       </c>
       <c r="AS42" s="17">
         <f t="shared" si="16"/>
-        <v>4029</v>
+        <v>4030</v>
       </c>
       <c r="AT42" s="16">
-        <v>18459</v>
+        <v>18460</v>
       </c>
       <c r="AU42" s="18">
         <f t="shared" si="17"/>
-        <v>0.91612486972058171</v>
+        <v>0.91617449997518485</v>
       </c>
       <c r="AV42" s="34">
         <v>15727</v>
@@ -8410,14 +8410,14 @@
       </c>
       <c r="E44" s="17">
         <f t="shared" si="0"/>
-        <v>260726</v>
+        <v>260727</v>
       </c>
       <c r="F44" s="16">
-        <v>302638</v>
+        <v>302639</v>
       </c>
       <c r="G44" s="18">
         <f t="shared" si="1"/>
-        <v>0.84689757072217919</v>
+        <v>0.84690036910695143</v>
       </c>
       <c r="H44" s="7">
         <v>355488</v>
@@ -8427,14 +8427,14 @@
       </c>
       <c r="J44" s="17">
         <f t="shared" si="2"/>
-        <v>218366</v>
+        <v>218367</v>
       </c>
       <c r="K44" s="16">
-        <v>302998</v>
+        <v>302999</v>
       </c>
       <c r="L44" s="18">
         <f t="shared" si="3"/>
-        <v>0.85234382032586187</v>
+        <v>0.85234663336033845</v>
       </c>
       <c r="M44" s="7">
         <v>358237</v>
@@ -8444,14 +8444,14 @@
       </c>
       <c r="O44" s="17">
         <f t="shared" si="4"/>
-        <v>188416</v>
+        <v>188417</v>
       </c>
       <c r="P44" s="16">
-        <v>305085</v>
+        <v>305086</v>
       </c>
       <c r="Q44" s="18">
         <f t="shared" si="5"/>
-        <v>0.85162894955015811</v>
+        <v>0.85163174099827765</v>
       </c>
       <c r="R44" s="7">
         <v>364550</v>
@@ -8461,14 +8461,14 @@
       </c>
       <c r="T44" s="17">
         <f t="shared" si="6"/>
-        <v>191972</v>
+        <v>191973</v>
       </c>
       <c r="U44" s="16">
-        <v>309030</v>
+        <v>309031</v>
       </c>
       <c r="V44" s="18">
         <f t="shared" si="7"/>
-        <v>0.84770264709916332</v>
+        <v>0.84770539020710467</v>
       </c>
       <c r="W44" s="7">
         <v>368236</v>
@@ -8478,14 +8478,14 @@
       </c>
       <c r="Y44" s="17">
         <f t="shared" si="8"/>
-        <v>140614</v>
+        <v>140616</v>
       </c>
       <c r="Z44" s="16">
-        <v>311931</v>
+        <v>311933</v>
       </c>
       <c r="AA44" s="18">
         <f t="shared" si="9"/>
-        <v>0.84709534103129513</v>
+        <v>0.84710077233078784</v>
       </c>
       <c r="AB44" s="28">
         <v>371659</v>
@@ -8495,14 +8495,14 @@
       </c>
       <c r="AD44" s="17">
         <f t="shared" si="10"/>
-        <v>118501</v>
+        <v>118502</v>
       </c>
       <c r="AE44" s="40">
-        <v>314150</v>
+        <v>314151</v>
       </c>
       <c r="AF44" s="18">
         <f t="shared" si="11"/>
-        <v>0.84526407271181381</v>
+        <v>0.8452667633502754</v>
       </c>
       <c r="AG44" s="16">
         <v>376783</v>
@@ -8512,14 +8512,14 @@
       </c>
       <c r="AI44" s="17">
         <f t="shared" si="12"/>
-        <v>113633</v>
+        <v>113634</v>
       </c>
       <c r="AJ44" s="16">
-        <v>317577</v>
+        <v>317578</v>
       </c>
       <c r="AK44" s="18">
         <f t="shared" si="13"/>
-        <v>0.84286446044540231</v>
+        <v>0.84286711449295748</v>
       </c>
       <c r="AL44" s="30">
         <v>379786</v>
@@ -8529,14 +8529,14 @@
       </c>
       <c r="AN44" s="17">
         <f t="shared" si="14"/>
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="AO44" s="16">
-        <v>321779</v>
+        <v>321780</v>
       </c>
       <c r="AP44" s="18">
         <f t="shared" si="15"/>
-        <v>0.84726398550762794</v>
+        <v>0.84726661856940488</v>
       </c>
       <c r="AQ44" s="32">
         <v>381213</v>
@@ -8546,14 +8546,14 @@
       </c>
       <c r="AS44" s="17">
         <f t="shared" si="16"/>
-        <v>84197</v>
+        <v>84199</v>
       </c>
       <c r="AT44" s="16">
-        <v>325856</v>
+        <v>325858</v>
       </c>
       <c r="AU44" s="18">
         <f t="shared" si="17"/>
-        <v>0.85478721869401098</v>
+        <v>0.85479246510481022</v>
       </c>
       <c r="AV44" s="34">
         <v>286191</v>
@@ -8563,14 +8563,14 @@
       </c>
       <c r="AX44" s="17">
         <f t="shared" si="18"/>
-        <v>80536</v>
+        <v>80539</v>
       </c>
       <c r="AY44" s="19">
-        <v>240007</v>
+        <v>240010</v>
       </c>
       <c r="AZ44" s="18">
         <f t="shared" si="19"/>
-        <v>0.83862525376409458</v>
+        <v>0.83863573627402677</v>
       </c>
       <c r="BA44" s="36">
         <v>282649</v>
@@ -8580,14 +8580,14 @@
       </c>
       <c r="BC44" s="17">
         <f t="shared" si="20"/>
-        <v>73134</v>
+        <v>73137</v>
       </c>
       <c r="BD44" s="38">
-        <v>244081</v>
+        <v>244084</v>
       </c>
       <c r="BE44" s="18">
         <f t="shared" si="21"/>
-        <v>0.86354807552830537</v>
+        <v>0.86355868939921954</v>
       </c>
       <c r="BF44" s="9">
         <v>372165</v>
@@ -8597,14 +8597,14 @@
       </c>
       <c r="BH44" s="17">
         <f t="shared" si="22"/>
-        <v>115088</v>
+        <v>115090</v>
       </c>
       <c r="BI44" s="19">
-        <v>334886</v>
+        <v>334888</v>
       </c>
       <c r="BJ44" s="18">
         <f t="shared" si="23"/>
-        <v>0.89983206373517122</v>
+        <v>0.89983743769564573</v>
       </c>
       <c r="BK44" s="2"/>
       <c r="BL44" s="2"/>
@@ -9252,10 +9252,10 @@
       <c r="BL47" s="2"/>
     </row>
     <row r="48" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A48" s="52" t="s">
+      <c r="A48" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="52"/>
+      <c r="B48" s="49"/>
       <c r="C48" s="27">
         <f>SUM(C10:C47)</f>
         <v>10414263</v>
@@ -9266,15 +9266,15 @@
       </c>
       <c r="E48" s="24">
         <f>F48-D48</f>
-        <v>8669698</v>
+        <v>8669740</v>
       </c>
       <c r="F48" s="25">
         <f>SUM(F10:F47)</f>
-        <v>9532867</v>
+        <v>9532909</v>
       </c>
       <c r="G48" s="26">
         <f>F48/C48</f>
-        <v>0.9153664546401411</v>
+        <v>0.9153704875707479</v>
       </c>
       <c r="H48" s="27">
         <f>SUM(H10:H47)</f>
@@ -9286,15 +9286,15 @@
       </c>
       <c r="J48" s="24">
         <f t="shared" si="2"/>
-        <v>7138779</v>
+        <v>7138819</v>
       </c>
       <c r="K48" s="25">
         <f>SUM(K10:K47)</f>
-        <v>9536291</v>
+        <v>9536331</v>
       </c>
       <c r="L48" s="26">
         <f t="shared" si="3"/>
-        <v>0.92202128821857887</v>
+        <v>0.92202515563952159</v>
       </c>
       <c r="M48" s="27">
         <f>SUM(M10:M47)</f>
@@ -9306,15 +9306,15 @@
       </c>
       <c r="O48" s="24">
         <f t="shared" si="4"/>
-        <v>6148828</v>
+        <v>6148872</v>
       </c>
       <c r="P48" s="25">
         <f>SUM(P10:P47)</f>
-        <v>9600109</v>
+        <v>9600153</v>
       </c>
       <c r="Q48" s="26">
         <f t="shared" si="5"/>
-        <v>0.92325616442005409</v>
+        <v>0.92326039596276199</v>
       </c>
       <c r="R48" s="27">
         <f>SUM(R10:R47)</f>
@@ -9326,15 +9326,15 @@
       </c>
       <c r="T48" s="24">
         <f t="shared" si="6"/>
-        <v>5911100</v>
+        <v>5911146</v>
       </c>
       <c r="U48" s="25">
         <f>SUM(U10:U47)</f>
-        <v>9713648</v>
+        <v>9713694</v>
       </c>
       <c r="V48" s="26">
         <f t="shared" si="7"/>
-        <v>0.9193311183660412</v>
+        <v>0.91933547195507859</v>
       </c>
       <c r="W48" s="27">
         <f>SUM(W10:W47)</f>
@@ -9346,15 +9346,15 @@
       </c>
       <c r="Y48" s="24">
         <f t="shared" si="8"/>
-        <v>4169242</v>
+        <v>4169284</v>
       </c>
       <c r="Z48" s="25">
         <f>SUM(Z10:Z47)</f>
-        <v>9814843</v>
+        <v>9814885</v>
       </c>
       <c r="AA48" s="26">
         <f t="shared" si="9"/>
-        <v>0.91689303652739818</v>
+        <v>0.91689696012633237</v>
       </c>
       <c r="AB48" s="27">
         <f>SUM(AB10:AB47)</f>
@@ -9366,15 +9366,15 @@
       </c>
       <c r="AD48" s="24">
         <f t="shared" si="10"/>
-        <v>2784174</v>
+        <v>2784220</v>
       </c>
       <c r="AE48" s="25">
         <f>SUM(AE10:AE47)</f>
-        <v>9901970</v>
+        <v>9902016</v>
       </c>
       <c r="AF48" s="26">
         <f t="shared" si="11"/>
-        <v>0.91253935349404469</v>
+        <v>0.91254359273232366</v>
       </c>
       <c r="AG48" s="23">
         <f>SUM(AG10:AG47)</f>
@@ -9386,15 +9386,15 @@
       </c>
       <c r="AI48" s="24">
         <f t="shared" si="12"/>
-        <v>2740683</v>
+        <v>2740731</v>
       </c>
       <c r="AJ48" s="25">
         <f>SUM(AJ10:AJ47)</f>
-        <v>10005653</v>
+        <v>10005701</v>
       </c>
       <c r="AK48" s="26">
         <f t="shared" si="13"/>
-        <v>0.91194503494968726</v>
+        <v>0.91194940981274497</v>
       </c>
       <c r="AL48" s="27">
         <f>SUM(AL10:AL47)</f>
@@ -9406,15 +9406,15 @@
       </c>
       <c r="AN48" s="24">
         <f t="shared" si="14"/>
-        <v>2318155</v>
+        <v>2318201</v>
       </c>
       <c r="AO48" s="25">
         <f>SUM(AO10:AO47)</f>
-        <v>10099916</v>
+        <v>10099962</v>
       </c>
       <c r="AP48" s="26">
         <f t="shared" si="15"/>
-        <v>0.9172929134991038</v>
+        <v>0.91729709130355486</v>
       </c>
       <c r="AQ48" s="27">
         <f>SUM(AQ10:AQ47)</f>
@@ -9426,15 +9426,15 @@
       </c>
       <c r="AS48" s="24">
         <f t="shared" si="16"/>
-        <v>1958722</v>
+        <v>1958768</v>
       </c>
       <c r="AT48" s="25">
         <f>SUM(AT10:AT47)</f>
-        <v>10194167</v>
+        <v>10194213</v>
       </c>
       <c r="AU48" s="26">
         <f t="shared" si="17"/>
-        <v>0.92807432557304514</v>
+        <v>0.92807851340114089</v>
       </c>
       <c r="AV48" s="27">
         <f>SUM(AV10:AV47)</f>
@@ -9446,15 +9446,15 @@
       </c>
       <c r="AX48" s="24">
         <f t="shared" si="18"/>
-        <v>1826821</v>
+        <v>1826867</v>
       </c>
       <c r="AY48" s="25">
         <f>SUM(AY10:AY47)</f>
-        <v>5622720</v>
+        <v>5622766</v>
       </c>
       <c r="AZ48" s="26">
         <f t="shared" si="19"/>
-        <v>0.89808861955004526</v>
+        <v>0.8980959668973254</v>
       </c>
       <c r="BA48" s="27">
         <f>SUM(BA10:BA47)</f>
@@ -9466,15 +9466,15 @@
       </c>
       <c r="BC48" s="24">
         <f t="shared" si="20"/>
-        <v>1571160</v>
+        <v>1571207</v>
       </c>
       <c r="BD48" s="25">
         <f>SUM(BD10:BD47)</f>
-        <v>5732032</v>
+        <v>5732079</v>
       </c>
       <c r="BE48" s="26">
         <f t="shared" si="21"/>
-        <v>0.93468569575237292</v>
+        <v>0.93469335974093759</v>
       </c>
       <c r="BF48" s="27">
         <f>SUM(BF10:BF47)</f>
@@ -9486,36 +9486,44 @@
       </c>
       <c r="BH48" s="24">
         <f t="shared" si="22"/>
-        <v>3236202</v>
+        <v>3236240</v>
       </c>
       <c r="BI48" s="25">
         <f>SUM(BI10:BI47)</f>
-        <v>10408126</v>
+        <v>10408164</v>
       </c>
       <c r="BJ48" s="26">
         <f t="shared" si="23"/>
-        <v>0.96554068928269299</v>
+        <v>0.96554421446543892</v>
       </c>
       <c r="BK48" s="10"/>
       <c r="BL48" s="10"/>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="AL57" s="4"/>
-      <c r="AM57" s="4"/>
+    <row r="55" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AL55" s="4"/>
+      <c r="AM55" s="4"/>
     </row>
-    <row r="58" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A58" s="51" t="s">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A56" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="3"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="BF8:BJ8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="A56:E56"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="BA8:BE8"/>
@@ -9526,14 +9534,6 @@
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="BF8:BJ8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
